--- a/Översikt DALS-ED.xlsx
+++ b/Översikt DALS-ED.xlsx
@@ -601,7 +601,7 @@
         <v>44601</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>45954</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
         <v>46153</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>45897</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         <v>46160</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>46160</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         <v>45331</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         <v>44907</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>44833</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         <v>45643</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         <v>45790</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         <v>45833</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
         <v>46160</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
         <v>44835</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2326,7 +2326,7 @@
         <v>45817</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
         <v>46160</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v>45422</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2667,7 +2667,7 @@
         <v>44494</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2777,7 +2777,7 @@
         <v>45188</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2891,7 +2891,7 @@
         <v>45265</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3004,7 +3004,7 @@
         <v>46048</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3115,7 +3115,7 @@
         <v>46160</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         <v>45151</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3337,7 +3337,7 @@
         <v>45422</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3448,7 +3448,7 @@
         <v>45937</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3562,7 +3562,7 @@
         <v>45588</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3672,7 +3672,7 @@
         <v>45569</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
         <v>44601</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3884,7 +3884,7 @@
         <v>45572</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         <v>46245</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4100,7 +4100,7 @@
         <v>46251</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4210,7 +4210,7 @@
         <v>45281</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         <v>45799</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4425,7 +4425,7 @@
         <v>45803</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4534,7 +4534,7 @@
         <v>45930</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4639,7 +4639,7 @@
         <v>45075</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4744,7 +4744,7 @@
         <v>45475</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4849,7 +4849,7 @@
         <v>45014</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4954,7 +4954,7 @@
         <v>45588</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5063,7 +5063,7 @@
         <v>45120</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         <v>44818</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5278,7 +5278,7 @@
         <v>45402</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5383,7 +5383,7 @@
         <v>45237</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5493,7 +5493,7 @@
         <v>44952</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5598,7 +5598,7 @@
         <v>45183</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5707,7 +5707,7 @@
         <v>45687</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5812,7 +5812,7 @@
         <v>44781</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         <v>44533</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
         <v>44536</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6031,7 +6031,7 @@
         <v>44615</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6104,7 +6104,7 @@
         <v>44536</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6177,7 +6177,7 @@
         <v>44588</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>44690</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6323,7 +6323,7 @@
         <v>44487</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6396,7 +6396,7 @@
         <v>44865</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6474,7 +6474,7 @@
         <v>44733</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6547,7 +6547,7 @@
         <v>44781</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6620,7 +6620,7 @@
         <v>44676</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6693,7 +6693,7 @@
         <v>44578</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
         <v>44799</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6839,7 +6839,7 @@
         <v>44705</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6912,7 +6912,7 @@
         <v>44743</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6985,7 +6985,7 @@
         <v>44615</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7058,7 +7058,7 @@
         <v>44608</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7131,7 +7131,7 @@
         <v>44823</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7204,7 +7204,7 @@
         <v>44837</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7277,7 +7277,7 @@
         <v>44657</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7355,7 +7355,7 @@
         <v>44685</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7428,7 +7428,7 @@
         <v>44685</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7501,7 +7501,7 @@
         <v>44705</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         <v>44705</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7647,7 +7647,7 @@
         <v>45702</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7720,7 +7720,7 @@
         <v>44825</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7793,7 +7793,7 @@
         <v>45257</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7866,7 +7866,7 @@
         <v>45187</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7939,7 +7939,7 @@
         <v>45412</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8012,7 +8012,7 @@
         <v>45531</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8085,7 +8085,7 @@
         <v>45412</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8158,7 +8158,7 @@
         <v>45359</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8231,7 +8231,7 @@
         <v>45393</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8304,7 +8304,7 @@
         <v>45440</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         <v>45440</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8450,7 +8450,7 @@
         <v>45217</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8528,7 +8528,7 @@
         <v>45428</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8601,7 +8601,7 @@
         <v>44895</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8679,7 +8679,7 @@
         <v>44823</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8752,7 +8752,7 @@
         <v>45119</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8825,7 +8825,7 @@
         <v>45400</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8898,7 +8898,7 @@
         <v>45478</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8971,7 +8971,7 @@
         <v>45796</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9044,7 +9044,7 @@
         <v>45279</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9122,7 +9122,7 @@
         <v>45346</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9195,7 +9195,7 @@
         <v>44855</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9268,7 +9268,7 @@
         <v>45796</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
         <v>45883</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9414,7 +9414,7 @@
         <v>46028</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9487,7 +9487,7 @@
         <v>44942</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9560,7 +9560,7 @@
         <v>45342</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9633,7 +9633,7 @@
         <v>45798</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9706,7 +9706,7 @@
         <v>44659</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9779,7 +9779,7 @@
         <v>44895</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9852,7 +9852,7 @@
         <v>45666</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9925,7 +9925,7 @@
         <v>45798</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9998,7 +9998,7 @@
         <v>45328</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10071,7 +10071,7 @@
         <v>45671</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10144,7 +10144,7 @@
         <v>45887</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10217,7 +10217,7 @@
         <v>46031</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10290,7 +10290,7 @@
         <v>46031</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10363,7 +10363,7 @@
         <v>46035</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10436,7 +10436,7 @@
         <v>46035</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10509,7 +10509,7 @@
         <v>45773</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10582,7 +10582,7 @@
         <v>45475</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10655,7 +10655,7 @@
         <v>45246</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10728,7 +10728,7 @@
         <v>44601</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10801,7 +10801,7 @@
         <v>45895</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10874,7 +10874,7 @@
         <v>44875</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10947,7 +10947,7 @@
         <v>44902</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11020,7 +11020,7 @@
         <v>44901</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11093,7 +11093,7 @@
         <v>45833</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11166,7 +11166,7 @@
         <v>44909</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11239,7 +11239,7 @@
         <v>45597</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11312,7 +11312,7 @@
         <v>44648</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11385,7 +11385,7 @@
         <v>45902</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11458,7 +11458,7 @@
         <v>46048</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11531,7 +11531,7 @@
         <v>45903</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11604,7 +11604,7 @@
         <v>45904</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11677,7 +11677,7 @@
         <v>45904</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11750,7 +11750,7 @@
         <v>45902</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11823,7 +11823,7 @@
         <v>45908</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11901,7 +11901,7 @@
         <v>45646</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11974,7 +11974,7 @@
         <v>45908</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12052,7 +12052,7 @@
         <v>45202</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12125,7 +12125,7 @@
         <v>45909</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12198,7 +12198,7 @@
         <v>46056</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12271,7 +12271,7 @@
         <v>45909</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12349,7 +12349,7 @@
         <v>46055</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12422,7 +12422,7 @@
         <v>46056</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12495,7 +12495,7 @@
         <v>45603</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12568,7 +12568,7 @@
         <v>46060</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12641,7 +12641,7 @@
         <v>45922</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12714,7 +12714,7 @@
         <v>44952</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12787,7 +12787,7 @@
         <v>45803</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12860,7 +12860,7 @@
         <v>45804</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12933,7 +12933,7 @@
         <v>44600</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13011,7 +13011,7 @@
         <v>45118</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13084,7 +13084,7 @@
         <v>45925</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13157,7 +13157,7 @@
         <v>46073</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13230,7 +13230,7 @@
         <v>46073</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13303,7 +13303,7 @@
         <v>46073</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13376,7 +13376,7 @@
         <v>46073</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13449,7 +13449,7 @@
         <v>45925</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13527,7 +13527,7 @@
         <v>45358</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13605,7 +13605,7 @@
         <v>45047</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13678,7 +13678,7 @@
         <v>45929</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13751,7 +13751,7 @@
         <v>45929</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13824,7 +13824,7 @@
         <v>46080</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13902,7 +13902,7 @@
         <v>45541</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13975,7 +13975,7 @@
         <v>46083</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14048,7 +14048,7 @@
         <v>45470</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14121,7 +14121,7 @@
         <v>45632</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14194,7 +14194,7 @@
         <v>44705</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14267,7 +14267,7 @@
         <v>45932</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14340,7 +14340,7 @@
         <v>46087</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14413,7 +14413,7 @@
         <v>45932</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14486,7 +14486,7 @@
         <v>45150</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14559,7 +14559,7 @@
         <v>45595</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14632,7 +14632,7 @@
         <v>46093</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14705,7 +14705,7 @@
         <v>45940</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14778,7 +14778,7 @@
         <v>46101</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14851,7 +14851,7 @@
         <v>45946</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14924,7 +14924,7 @@
         <v>45588</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14997,7 +14997,7 @@
         <v>46100</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15070,7 +15070,7 @@
         <v>45189</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15143,7 +15143,7 @@
         <v>45951</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15216,7 +15216,7 @@
         <v>45951</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15294,7 +15294,7 @@
         <v>45812</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15367,7 +15367,7 @@
         <v>45624</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15440,7 +15440,7 @@
         <v>45951</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15518,7 +15518,7 @@
         <v>45762</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15591,7 +15591,7 @@
         <v>46113</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15664,7 +15664,7 @@
         <v>45958</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15737,7 +15737,7 @@
         <v>45811</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15810,7 +15810,7 @@
         <v>46113</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15883,7 +15883,7 @@
         <v>45624</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15956,7 +15956,7 @@
         <v>45006</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16029,7 +16029,7 @@
         <v>45037</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16102,7 +16102,7 @@
         <v>44952</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16175,7 +16175,7 @@
         <v>44958</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16248,7 +16248,7 @@
         <v>46126</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16321,7 +16321,7 @@
         <v>44952</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16394,7 +16394,7 @@
         <v>45974</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16472,7 +16472,7 @@
         <v>45973</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16545,7 +16545,7 @@
         <v>45974</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16618,7 +16618,7 @@
         <v>45974</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16691,7 +16691,7 @@
         <v>46126</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16764,7 +16764,7 @@
         <v>45973</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16837,7 +16837,7 @@
         <v>45974</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16910,7 +16910,7 @@
         <v>45761</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16983,7 +16983,7 @@
         <v>45978</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17056,7 +17056,7 @@
         <v>45978</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17129,7 +17129,7 @@
         <v>45161</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17207,7 +17207,7 @@
         <v>45162</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17280,7 +17280,7 @@
         <v>45590</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17353,7 +17353,7 @@
         <v>45981</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17426,7 +17426,7 @@
         <v>45615</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17499,7 +17499,7 @@
         <v>45002</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17572,7 +17572,7 @@
         <v>45986</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17645,7 +17645,7 @@
         <v>45982</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17718,7 +17718,7 @@
         <v>45825</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17791,7 +17791,7 @@
         <v>45621</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17864,7 +17864,7 @@
         <v>45590</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17937,7 +17937,7 @@
         <v>45062</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18010,7 +18010,7 @@
         <v>45632</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18083,7 +18083,7 @@
         <v>45698</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18156,7 +18156,7 @@
         <v>45994</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18229,7 +18229,7 @@
         <v>45693</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18302,7 +18302,7 @@
         <v>45189</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18375,7 +18375,7 @@
         <v>45995</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18448,7 +18448,7 @@
         <v>45995</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18521,7 +18521,7 @@
         <v>45995</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18594,7 +18594,7 @@
         <v>45915</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18667,7 +18667,7 @@
         <v>45181</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18740,7 +18740,7 @@
         <v>45832</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18818,7 +18818,7 @@
         <v>45150</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18891,7 +18891,7 @@
         <v>45929</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18964,7 +18964,7 @@
         <v>46000</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19037,7 +19037,7 @@
         <v>44720</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19110,7 +19110,7 @@
         <v>46003</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19183,7 +19183,7 @@
         <v>46003</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19256,7 +19256,7 @@
         <v>45896</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19329,7 +19329,7 @@
         <v>45530</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19402,7 +19402,7 @@
         <v>45825</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19475,7 +19475,7 @@
         <v>45994</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19548,7 +19548,7 @@
         <v>45217</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19626,7 +19626,7 @@
         <v>45966</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19699,7 +19699,7 @@
         <v>45443</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19777,7 +19777,7 @@
         <v>45197</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19850,7 +19850,7 @@
         <v>45904</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19928,7 +19928,7 @@
         <v>45845</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20001,7 +20001,7 @@
         <v>45547</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20074,7 +20074,7 @@
         <v>45348</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20147,7 +20147,7 @@
         <v>45734</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20220,7 +20220,7 @@
         <v>45834</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20293,7 +20293,7 @@
         <v>45825</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20366,7 +20366,7 @@
         <v>45602</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20439,7 +20439,7 @@
         <v>46080</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20517,7 +20517,7 @@
         <v>45825</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20590,7 +20590,7 @@
         <v>44511</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20663,7 +20663,7 @@
         <v>45825</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20736,7 +20736,7 @@
         <v>45418</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20809,7 +20809,7 @@
         <v>45911</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20882,7 +20882,7 @@
         <v>45644</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20955,7 +20955,7 @@
         <v>45831</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21028,7 +21028,7 @@
         <v>45425</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21101,7 +21101,7 @@
         <v>46148</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21174,7 +21174,7 @@
         <v>45467</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21247,7 +21247,7 @@
         <v>46153</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21320,7 +21320,7 @@
         <v>45272</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21393,7 +21393,7 @@
         <v>46153</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21466,7 +21466,7 @@
         <v>46153</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21539,7 +21539,7 @@
         <v>44858</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21612,7 +21612,7 @@
         <v>45092</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21685,7 +21685,7 @@
         <v>46160</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21758,7 +21758,7 @@
         <v>44468</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21831,7 +21831,7 @@
         <v>45273</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21904,7 +21904,7 @@
         <v>45546</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21977,7 +21977,7 @@
         <v>45737</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22050,7 +22050,7 @@
         <v>45940</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22123,7 +22123,7 @@
         <v>45015</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22196,7 +22196,7 @@
         <v>44959</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22269,7 +22269,7 @@
         <v>44902</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22342,7 +22342,7 @@
         <v>44959</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22415,7 +22415,7 @@
         <v>45994</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22488,7 +22488,7 @@
         <v>45103</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22561,7 +22561,7 @@
         <v>45842</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22634,7 +22634,7 @@
         <v>45121</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22707,7 +22707,7 @@
         <v>44545</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22780,7 +22780,7 @@
         <v>45075</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22853,7 +22853,7 @@
         <v>46167</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22931,7 +22931,7 @@
         <v>45355</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23004,7 +23004,7 @@
         <v>45713</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23077,7 +23077,7 @@
         <v>45849</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23150,7 +23150,7 @@
         <v>45994</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23223,7 +23223,7 @@
         <v>46006</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23296,7 +23296,7 @@
         <v>44949</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23369,7 +23369,7 @@
         <v>45254</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23442,7 +23442,7 @@
         <v>44776</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23515,7 +23515,7 @@
         <v>44621</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23593,7 +23593,7 @@
         <v>44781</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23666,7 +23666,7 @@
         <v>45348</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23739,7 +23739,7 @@
         <v>46177</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23812,7 +23812,7 @@
         <v>45384</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23885,7 +23885,7 @@
         <v>45734</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23958,7 +23958,7 @@
         <v>46177</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24031,7 +24031,7 @@
         <v>46177</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24104,7 +24104,7 @@
         <v>45404</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24177,7 +24177,7 @@
         <v>45104</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24250,7 +24250,7 @@
         <v>45566</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24323,7 +24323,7 @@
         <v>44621</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24401,7 +24401,7 @@
         <v>45162</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24474,7 +24474,7 @@
         <v>46184</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24547,7 +24547,7 @@
         <v>46188</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24620,7 +24620,7 @@
         <v>45621</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24693,7 +24693,7 @@
         <v>46184</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24766,7 +24766,7 @@
         <v>45587</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24839,7 +24839,7 @@
         <v>45616</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24912,7 +24912,7 @@
         <v>46198</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24985,7 +24985,7 @@
         <v>45636</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25058,7 +25058,7 @@
         <v>46048</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25131,7 +25131,7 @@
         <v>45639</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25204,7 +25204,7 @@
         <v>45639</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25277,7 +25277,7 @@
         <v>45162</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25350,7 +25350,7 @@
         <v>45882</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25428,7 +25428,7 @@
         <v>45078</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25501,7 +25501,7 @@
         <v>44743</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25574,7 +25574,7 @@
         <v>45182</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25647,7 +25647,7 @@
         <v>45674</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25720,7 +25720,7 @@
         <v>46205</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25793,7 +25793,7 @@
         <v>44601</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25866,7 +25866,7 @@
         <v>45763</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25939,7 +25939,7 @@
         <v>44643</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26012,7 +26012,7 @@
         <v>45196</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26090,7 +26090,7 @@
         <v>45609</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26163,7 +26163,7 @@
         <v>44858</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26236,7 +26236,7 @@
         <v>44701</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26309,7 +26309,7 @@
         <v>45162</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26382,7 +26382,7 @@
         <v>46254</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26460,7 +26460,7 @@
         <v>45755</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26533,7 +26533,7 @@
         <v>45686</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26606,7 +26606,7 @@
         <v>44743</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26679,7 +26679,7 @@
         <v>45773</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26752,7 +26752,7 @@
         <v>46212</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26825,7 +26825,7 @@
         <v>44614</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26898,7 +26898,7 @@
         <v>46260</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26971,7 +26971,7 @@
         <v>44659</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27044,7 +27044,7 @@
         <v>44823</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27117,7 +27117,7 @@
         <v>45705</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27190,7 +27190,7 @@
         <v>45201</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27263,7 +27263,7 @@
         <v>46265</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27341,7 +27341,7 @@
         <v>44823</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27414,7 +27414,7 @@
         <v>46265</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27492,7 +27492,7 @@
         <v>45272</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27565,7 +27565,7 @@
         <v>44742</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27638,7 +27638,7 @@
         <v>46272</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27711,7 +27711,7 @@
         <v>46274</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27789,7 +27789,7 @@
         <v>45763</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27862,7 +27862,7 @@
         <v>45763</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27935,7 +27935,7 @@
         <v>44952</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28008,7 +28008,7 @@
         <v>44952</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28081,7 +28081,7 @@
         <v>44952</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28154,7 +28154,7 @@
         <v>45326</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28227,7 +28227,7 @@
         <v>46276</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28300,7 +28300,7 @@
         <v>45609</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28373,7 +28373,7 @@
         <v>46279</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28446,7 +28446,7 @@
         <v>44504</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28519,7 +28519,7 @@
         <v>46279</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28592,7 +28592,7 @@
         <v>45538</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28665,7 +28665,7 @@
         <v>46239</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28738,7 +28738,7 @@
         <v>45446</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28811,7 +28811,7 @@
         <v>45533</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28884,7 +28884,7 @@
         <v>44966</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28957,7 +28957,7 @@
         <v>44627</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29030,7 +29030,7 @@
         <v>46244</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29103,7 +29103,7 @@
         <v>44952</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29176,7 +29176,7 @@
         <v>45561</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29249,7 +29249,7 @@
         <v>45443</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29327,7 +29327,7 @@
         <v>44592</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29400,7 +29400,7 @@
         <v>46252</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29473,7 +29473,7 @@
         <v>45387</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29546,7 +29546,7 @@
         <v>44970</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29624,7 +29624,7 @@
         <v>45593</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29697,7 +29697,7 @@
         <v>44916</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29770,7 +29770,7 @@
         <v>44823</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29843,7 +29843,7 @@
         <v>45600</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29916,7 +29916,7 @@
         <v>45600</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29989,7 +29989,7 @@
         <v>44685</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30062,7 +30062,7 @@
         <v>45151</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30135,7 +30135,7 @@
         <v>45049</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30208,7 +30208,7 @@
         <v>44942</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30281,7 +30281,7 @@
         <v>45327</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30354,7 +30354,7 @@
         <v>45351</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30432,7 +30432,7 @@
         <v>45762</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30505,7 +30505,7 @@
         <v>45609</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30578,7 +30578,7 @@
         <v>44952</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30651,7 +30651,7 @@
         <v>44952</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30724,7 +30724,7 @@
         <v>45675</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30797,7 +30797,7 @@
         <v>45672</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30870,7 +30870,7 @@
         <v>45561</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30943,7 +30943,7 @@
         <v>45152</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31016,7 +31016,7 @@
         <v>45085</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31089,7 +31089,7 @@
         <v>45415</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31162,7 +31162,7 @@
         <v>44901</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31235,7 +31235,7 @@
         <v>45326</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31308,7 +31308,7 @@
         <v>45673</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31381,7 +31381,7 @@
         <v>45068</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31454,7 +31454,7 @@
         <v>45139</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31527,7 +31527,7 @@
         <v>45112</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31600,7 +31600,7 @@
         <v>44592</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31673,7 +31673,7 @@
         <v>44960</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31746,7 +31746,7 @@
         <v>44503</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31824,7 +31824,7 @@
         <v>45008</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31897,7 +31897,7 @@
         <v>45182</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31970,7 +31970,7 @@
         <v>45124</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32043,7 +32043,7 @@
         <v>45103</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32116,7 +32116,7 @@
         <v>45544</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32189,7 +32189,7 @@
         <v>45616</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32262,7 +32262,7 @@
         <v>44907</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32335,7 +32335,7 @@
         <v>45384</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32408,7 +32408,7 @@
         <v>45265</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32481,7 +32481,7 @@
         <v>45198</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32554,7 +32554,7 @@
         <v>44812</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32627,7 +32627,7 @@
         <v>45151</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32700,7 +32700,7 @@
         <v>45731</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32773,7 +32773,7 @@
         <v>45566</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32846,7 +32846,7 @@
         <v>45777</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32919,7 +32919,7 @@
         <v>44910</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32997,7 +32997,7 @@
         <v>45782</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33070,7 +33070,7 @@
         <v>45786</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33143,7 +33143,7 @@
         <v>45000</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33216,7 +33216,7 @@
         <v>45785</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33289,7 +33289,7 @@
         <v>45785</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33367,7 +33367,7 @@
         <v>45790</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33440,7 +33440,7 @@
         <v>45790</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33513,7 +33513,7 @@
         <v>45713</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33586,7 +33586,7 @@
         <v>45743</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33659,7 +33659,7 @@
         <v>45723</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33732,7 +33732,7 @@
         <v>45792</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33805,7 +33805,7 @@
         <v>45719</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33878,7 +33878,7 @@
         <v>45713</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33951,7 +33951,7 @@
         <v>45743</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34024,7 +34024,7 @@
         <v>44613</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34102,7 +34102,7 @@
         <v>44812</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34180,7 +34180,7 @@
         <v>45670</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34253,7 +34253,7 @@
         <v>45483</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34326,7 +34326,7 @@
         <v>45717</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>

--- a/Översikt DALS-ED.xlsx
+++ b/Översikt DALS-ED.xlsx
@@ -601,7 +601,7 @@
         <v>44601</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>45954</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
         <v>46153</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -924,10 +924,10 @@
         <v>26</v>
       </c>
       <c r="T4" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="U4" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>45897</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         <v>46160</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1167,10 +1167,10 @@
         <v>2</v>
       </c>
       <c r="K6" t="n">
+        <v>14</v>
+      </c>
+      <c r="L6" t="n">
         <v>7</v>
-      </c>
-      <c r="L6" t="n">
-        <v>6</v>
       </c>
       <c r="M6" t="n">
         <v>2</v>
@@ -1185,19 +1185,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R6" t="n">
         <v>2</v>
       </c>
       <c r="S6" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="T6" t="n">
-        <v>38</v>
+        <v>135</v>
       </c>
       <c r="U6" t="n">
-        <v>38</v>
+        <v>135</v>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
@@ -1206,13 +1206,21 @@
 Blanksvart spiklav
 Dropptaggsvamp
 Kattfotslav
+Motaggsvamp
 Svartvit taggsvamp
 Tallfingersvamp
 Vedtrappmossa
+Barkticka
+Björksplintborre
+Blomkålssvamp
 Blåmossa
 Bronshjon
+Granbarkgnagare
+Korallblylav
+Kornknutmossa
 Skuggmossa
 Stor revmossa
+Stuplav
 Thomsons trägnagare
 Vedticka
 Vågbandad barkbock
@@ -1272,7 +1280,7 @@
         <v>46160</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1388,7 +1396,7 @@
         <v>45331</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1508,7 +1516,7 @@
         <v>44907</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1631,7 +1639,7 @@
         <v>44833</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1749,7 +1757,7 @@
         <v>45643</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1850,7 +1858,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 23017-2025</t>
+          <t>A 22922-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1864,10 +1872,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45790</v>
+        <v>46160</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1880,19 +1888,19 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>9.300000000000001</v>
+        <v>13.6</v>
       </c>
       <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
         <v>3</v>
       </c>
-      <c r="K12" t="n">
-        <v>1</v>
-      </c>
       <c r="L12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1907,18 +1915,132 @@
         <v>7</v>
       </c>
       <c r="R12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
       </c>
       <c r="T12" t="n">
+        <v>33</v>
+      </c>
+      <c r="U12" t="n">
+        <v>33</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Jättemusseron
+Raggbock
+Dropptaggsvamp
+Motaggsvamp
+Talltagel
+Vedskivlav
+Vedtrappmossa
+Bronshjon
+Mindre märgborre
+Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/artfynd/A 22922-2026 artfynd.xlsx", "A 22922-2026")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/kartor/A 22922-2026 karta.png", "A 22922-2026")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/kartor_geotiff/A 22922-2026 georefererad karta.tif", "A 22922-2026")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/klagomål/A 22922-2026 FSC-klagomål.docx", "A 22922-2026")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/klagomålsmail/A 22922-2026 FSC-klagomål mail.docx", "A 22922-2026")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/tillsyn/A 22922-2026 tillsynsbegäran.docx", "A 22922-2026")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/tillsynsmail/A 22922-2026 tillsynsbegäran mail.docx", "A 22922-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 23017-2025</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45790</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>DALS-ED</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>6</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>7</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="n">
         <v>14</v>
       </c>
-      <c r="U12" t="n">
+      <c r="U13" t="n">
         <v>5</v>
       </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Apelsinticka
@@ -1932,111 +2054,111 @@
 Orre</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1438/artfynd/A 23017-2025 artfynd.xlsx", "A 23017-2025")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1438/kartor/A 23017-2025 karta.png", "A 23017-2025")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1438/kartor_geotiff/A 23017-2025 georefererad karta.tif", "A 23017-2025")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1438/klagomål/A 23017-2025 FSC-klagomål.docx", "A 23017-2025")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1438/klagomålsmail/A 23017-2025 FSC-klagomål mail.docx", "A 23017-2025")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1438/tillsyn/A 23017-2025 tillsynsbegäran.docx", "A 23017-2025")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1438/tillsynsmail/A 23017-2025 tillsynsbegäran mail.docx", "A 23017-2025")</f>
         <v/>
       </c>
-      <c r="AE12">
+      <c r="AE13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1438/fåglar/A 23017-2025 prioriterade fågelarter.docx", "A 23017-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>A 31268-2025</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
         <v>45833</v>
       </c>
-      <c r="E13" s="1" t="n">
-        <v>46292</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>DALS-ED</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
+      <c r="E14" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>DALS-ED</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
         <v>11.8</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J14" t="n">
         <v>1</v>
       </c>
-      <c r="K13" t="n">
+      <c r="K14" t="n">
         <v>3</v>
       </c>
-      <c r="L13" t="n">
+      <c r="L14" t="n">
         <v>3</v>
       </c>
-      <c r="M13" t="n">
+      <c r="M14" t="n">
         <v>1</v>
       </c>
-      <c r="N13" t="n">
+      <c r="N14" t="n">
         <v>1</v>
       </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
         <v>5</v>
       </c>
-      <c r="R13" t="n">
+      <c r="R14" t="n">
         <v>2</v>
       </c>
-      <c r="S13" t="n">
+      <c r="S14" t="n">
         <v>9</v>
       </c>
-      <c r="T13" t="n">
+      <c r="T14" t="n">
         <v>12</v>
       </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Spricktaggsvamp
 Gul taggsvamp
@@ -2049,107 +2171,224 @@
 Blåsippa</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1438/artfynd/A 31268-2025 artfynd.xlsx", "A 31268-2025")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1438/kartor/A 31268-2025 karta.png", "A 31268-2025")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1438/kartor_geotiff/A 31268-2025 georefererad karta.tif", "A 31268-2025")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1438/klagomål/A 31268-2025 FSC-klagomål.docx", "A 31268-2025")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1438/klagomålsmail/A 31268-2025 FSC-klagomål mail.docx", "A 31268-2025")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1438/tillsyn/A 31268-2025 tillsynsbegäran.docx", "A 31268-2025")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1438/tillsynsmail/A 31268-2025 tillsynsbegäran mail.docx", "A 31268-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 22939-2026</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>46160</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>DALS-ED</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>3</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3</v>
+      </c>
+      <c r="L15" t="n">
+        <v>5</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>6</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1</v>
+      </c>
+      <c r="S15" t="n">
+        <v>9</v>
+      </c>
+      <c r="T15" t="n">
+        <v>22</v>
+      </c>
+      <c r="U15" t="n">
+        <v>22</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Garnlav
+Dropptaggsvamp
+Kandelabersvamp
+Kortskaftad ärgspik
+Motaggsvamp
+Talltita
+Rävticka
+Thomsons trägnagare
+Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/artfynd/A 22939-2026 artfynd.xlsx", "A 22939-2026")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/kartor/A 22939-2026 karta.png", "A 22939-2026")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/kartor_geotiff/A 22939-2026 georefererad karta.tif", "A 22939-2026")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/klagomål/A 22939-2026 FSC-klagomål.docx", "A 22939-2026")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/klagomålsmail/A 22939-2026 FSC-klagomål mail.docx", "A 22939-2026")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/tillsyn/A 22939-2026 tillsynsbegäran.docx", "A 22939-2026")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/tillsynsmail/A 22939-2026 tillsynsbegäran mail.docx", "A 22939-2026")</f>
+        <v/>
+      </c>
+      <c r="AE15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/fåglar/A 22939-2026 prioriterade fågelarter.docx", "A 22939-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
         <is>
           <t>A 22947-2026</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
         <v>46160</v>
       </c>
-      <c r="E14" s="1" t="n">
-        <v>46292</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>DALS-ED</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
+      <c r="E16" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>DALS-ED</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
         <v>5.4</v>
       </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
         <v>5</v>
       </c>
-      <c r="L14" t="n">
+      <c r="L16" t="n">
         <v>3</v>
       </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
         <v>3</v>
       </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
         <v>8</v>
       </c>
-      <c r="T14" t="n">
+      <c r="T16" t="n">
         <v>14</v>
       </c>
-      <c r="U14" t="n">
+      <c r="U16" t="n">
         <v>14</v>
       </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Dropptaggsvamp
 Tallriska
@@ -2161,107 +2400,107 @@
 Vågbandad barkbock</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1438/artfynd/A 22947-2026 artfynd.xlsx", "A 22947-2026")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1438/kartor/A 22947-2026 karta.png", "A 22947-2026")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1438/kartor_geotiff/A 22947-2026 georefererad karta.tif", "A 22947-2026")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1438/klagomål/A 22947-2026 FSC-klagomål.docx", "A 22947-2026")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1438/klagomålsmail/A 22947-2026 FSC-klagomål mail.docx", "A 22947-2026")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1438/tillsyn/A 22947-2026 tillsynsbegäran.docx", "A 22947-2026")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1438/tillsynsmail/A 22947-2026 tillsynsbegäran mail.docx", "A 22947-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>A 43450-2022</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
         <v>44835</v>
       </c>
-      <c r="E15" s="1" t="n">
-        <v>46292</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>DALS-ED</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
+      <c r="E17" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>DALS-ED</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
         <v>12.8</v>
       </c>
-      <c r="J15" t="n">
+      <c r="J17" t="n">
         <v>3</v>
       </c>
-      <c r="K15" t="n">
+      <c r="K17" t="n">
         <v>3</v>
       </c>
-      <c r="L15" t="n">
+      <c r="L17" t="n">
         <v>3</v>
       </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
         <v>3</v>
       </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
         <v>8</v>
       </c>
-      <c r="T15" t="n">
+      <c r="T17" t="n">
         <v>24</v>
       </c>
-      <c r="U15" t="n">
+      <c r="U17" t="n">
         <v>24</v>
       </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Dropptaggsvamp
 Kattfotslav
@@ -2273,111 +2512,111 @@
 Tjäder</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1438/artfynd/A 43450-2022 artfynd.xlsx", "A 43450-2022")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1438/kartor/A 43450-2022 karta.png", "A 43450-2022")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1438/kartor_geotiff/A 43450-2022 georefererad karta.tif", "A 43450-2022")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1438/klagomål/A 43450-2022 FSC-klagomål.docx", "A 43450-2022")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1438/klagomålsmail/A 43450-2022 FSC-klagomål mail.docx", "A 43450-2022")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1438/tillsyn/A 43450-2022 tillsynsbegäran.docx", "A 43450-2022")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1438/tillsynsmail/A 43450-2022 tillsynsbegäran mail.docx", "A 43450-2022")</f>
         <v/>
       </c>
-      <c r="AE15">
+      <c r="AE17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1438/fåglar/A 43450-2022 prioriterade fågelarter.docx", "A 43450-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>A 28013-2025</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
         <v>45817</v>
       </c>
-      <c r="E16" s="1" t="n">
-        <v>46292</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>DALS-ED</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
+      <c r="E18" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>DALS-ED</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
         <v>6.5</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J18" t="n">
         <v>1</v>
       </c>
-      <c r="K16" t="n">
+      <c r="K18" t="n">
         <v>4</v>
       </c>
-      <c r="L16" t="n">
+      <c r="L18" t="n">
         <v>3</v>
       </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
         <v>3</v>
       </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
         <v>7</v>
       </c>
-      <c r="T16" t="n">
+      <c r="T18" t="n">
         <v>9</v>
       </c>
-      <c r="U16" t="n">
+      <c r="U18" t="n">
         <v>9</v>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>Kådvaxskinn
 Nordtagging
@@ -2388,222 +2627,111 @@
 Mindre märgborre</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1438/artfynd/A 28013-2025 artfynd.xlsx", "A 28013-2025")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1438/kartor/A 28013-2025 karta.png", "A 28013-2025")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1438/kartor_geotiff/A 28013-2025 georefererad karta.tif", "A 28013-2025")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1438/klagomål/A 28013-2025 FSC-klagomål.docx", "A 28013-2025")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1438/klagomålsmail/A 28013-2025 FSC-klagomål mail.docx", "A 28013-2025")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1438/tillsyn/A 28013-2025 tillsynsbegäran.docx", "A 28013-2025")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1438/tillsynsmail/A 28013-2025 tillsynsbegäran mail.docx", "A 28013-2025")</f>
         <v/>
       </c>
-      <c r="AE16">
+      <c r="AE18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1438/fåglar/A 28013-2025 prioriterade fågelarter.docx", "A 28013-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 22922-2026</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>46160</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46292</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>DALS-ED</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>2</v>
-      </c>
-      <c r="L17" t="n">
-        <v>4</v>
-      </c>
-      <c r="M17" t="n">
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 18326-2024</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>45422</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>DALS-ED</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J19" t="n">
         <v>1</v>
       </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
+      <c r="K19" t="n">
         <v>5</v>
       </c>
-      <c r="R17" t="n">
+      <c r="L19" t="n">
         <v>1</v>
       </c>
-      <c r="S17" t="n">
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
         <v>7</v>
       </c>
-      <c r="T17" t="n">
-        <v>15</v>
-      </c>
-      <c r="U17" t="n">
-        <v>15</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Raggbock
-Dropptaggsvamp
-Talltagel
-Vedskivlav
-Vedtrappmossa
-Bronshjon
-Thomsons trägnagare</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/artfynd/A 22922-2026 artfynd.xlsx", "A 22922-2026")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/kartor/A 22922-2026 karta.png", "A 22922-2026")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/kartor_geotiff/A 22922-2026 georefererad karta.tif", "A 22922-2026")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/klagomål/A 22922-2026 FSC-klagomål.docx", "A 22922-2026")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/klagomålsmail/A 22922-2026 FSC-klagomål mail.docx", "A 22922-2026")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/tillsyn/A 22922-2026 tillsynsbegäran.docx", "A 22922-2026")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/tillsynsmail/A 22922-2026 tillsynsbegäran mail.docx", "A 22922-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 18326-2024</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>45422</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46292</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>DALS-ED</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1</v>
-      </c>
-      <c r="K18" t="n">
-        <v>5</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>7</v>
-      </c>
-      <c r="T18" t="n">
+      <c r="T19" t="n">
         <v>9</v>
       </c>
-      <c r="U18" t="n">
+      <c r="U19" t="n">
         <v>9</v>
       </c>
-      <c r="V18" s="2" t="inlineStr">
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Dropptaggsvamp
 Barkticka
@@ -2614,111 +2742,111 @@
 Spillkråka</t>
         </is>
       </c>
-      <c r="W18">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1438/artfynd/A 18326-2024 artfynd.xlsx", "A 18326-2024")</f>
         <v/>
       </c>
-      <c r="X18">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1438/kartor/A 18326-2024 karta.png", "A 18326-2024")</f>
         <v/>
       </c>
-      <c r="Y18">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1438/kartor_geotiff/A 18326-2024 georefererad karta.tif", "A 18326-2024")</f>
         <v/>
       </c>
-      <c r="AA18">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1438/klagomål/A 18326-2024 FSC-klagomål.docx", "A 18326-2024")</f>
         <v/>
       </c>
-      <c r="AB18">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1438/klagomålsmail/A 18326-2024 FSC-klagomål mail.docx", "A 18326-2024")</f>
         <v/>
       </c>
-      <c r="AC18">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1438/tillsyn/A 18326-2024 tillsynsbegäran.docx", "A 18326-2024")</f>
         <v/>
       </c>
-      <c r="AD18">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1438/tillsynsmail/A 18326-2024 tillsynsbegäran mail.docx", "A 18326-2024")</f>
         <v/>
       </c>
-      <c r="AE18">
+      <c r="AE19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1438/fåglar/A 18326-2024 prioriterade fågelarter.docx", "A 18326-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
         <is>
           <t>A 59931-2021</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
         <v>44494</v>
       </c>
-      <c r="E19" s="1" t="n">
-        <v>46292</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>DALS-ED</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
+      <c r="E20" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>DALS-ED</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
         <v>1</v>
       </c>
-      <c r="J19" t="n">
+      <c r="J20" t="n">
         <v>1</v>
       </c>
-      <c r="K19" t="n">
+      <c r="K20" t="n">
         <v>2</v>
       </c>
-      <c r="L19" t="n">
+      <c r="L20" t="n">
         <v>2</v>
       </c>
-      <c r="M19" t="n">
+      <c r="M20" t="n">
         <v>1</v>
       </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
         <v>3</v>
       </c>
-      <c r="R19" t="n">
+      <c r="R20" t="n">
         <v>1</v>
       </c>
-      <c r="S19" t="n">
+      <c r="S20" t="n">
         <v>6</v>
       </c>
-      <c r="T19" t="n">
+      <c r="T20" t="n">
         <v>6</v>
       </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>Västlig njurlav
 Grynig filtlav
@@ -2728,107 +2856,107 @@
 Blåsippa</t>
         </is>
       </c>
-      <c r="W19">
+      <c r="W20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1438/artfynd/A 59931-2021 artfynd.xlsx", "A 59931-2021")</f>
         <v/>
       </c>
-      <c r="X19">
+      <c r="X20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1438/kartor/A 59931-2021 karta.png", "A 59931-2021")</f>
         <v/>
       </c>
-      <c r="Y19">
+      <c r="Y20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1438/kartor_geotiff/A 59931-2021 georefererad karta.tif", "A 59931-2021")</f>
         <v/>
       </c>
-      <c r="AA19">
+      <c r="AA20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1438/klagomål/A 59931-2021 FSC-klagomål.docx", "A 59931-2021")</f>
         <v/>
       </c>
-      <c r="AB19">
+      <c r="AB20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1438/klagomålsmail/A 59931-2021 FSC-klagomål mail.docx", "A 59931-2021")</f>
         <v/>
       </c>
-      <c r="AC19">
+      <c r="AC20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1438/tillsyn/A 59931-2021 tillsynsbegäran.docx", "A 59931-2021")</f>
         <v/>
       </c>
-      <c r="AD19">
+      <c r="AD20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1438/tillsynsmail/A 59931-2021 tillsynsbegäran mail.docx", "A 59931-2021")</f>
         <v/>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
         <is>
           <t>A 44363-2023</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
         <v>45188</v>
       </c>
-      <c r="E20" s="1" t="n">
-        <v>46292</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>DALS-ED</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
+      <c r="E21" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>DALS-ED</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
         <v>3.5</v>
       </c>
-      <c r="J20" t="n">
+      <c r="J21" t="n">
         <v>1</v>
       </c>
-      <c r="K20" t="n">
+      <c r="K21" t="n">
         <v>3</v>
       </c>
-      <c r="L20" t="n">
+      <c r="L21" t="n">
         <v>2</v>
       </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
         <v>2</v>
       </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
         <v>6</v>
       </c>
-      <c r="T20" t="n">
+      <c r="T21" t="n">
         <v>12</v>
       </c>
-      <c r="U20" t="n">
+      <c r="U21" t="n">
         <v>12</v>
       </c>
-      <c r="V20" s="2" t="inlineStr">
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>Kattfotslav
 Vedtrappmossa
@@ -2838,111 +2966,111 @@
 Spillkråka</t>
         </is>
       </c>
-      <c r="W20">
+      <c r="W21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1438/artfynd/A 44363-2023 artfynd.xlsx", "A 44363-2023")</f>
         <v/>
       </c>
-      <c r="X20">
+      <c r="X21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1438/kartor/A 44363-2023 karta.png", "A 44363-2023")</f>
         <v/>
       </c>
-      <c r="Y20">
+      <c r="Y21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1438/kartor_geotiff/A 44363-2023 georefererad karta.tif", "A 44363-2023")</f>
         <v/>
       </c>
-      <c r="AA20">
+      <c r="AA21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1438/klagomål/A 44363-2023 FSC-klagomål.docx", "A 44363-2023")</f>
         <v/>
       </c>
-      <c r="AB20">
+      <c r="AB21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1438/klagomålsmail/A 44363-2023 FSC-klagomål mail.docx", "A 44363-2023")</f>
         <v/>
       </c>
-      <c r="AC20">
+      <c r="AC21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1438/tillsyn/A 44363-2023 tillsynsbegäran.docx", "A 44363-2023")</f>
         <v/>
       </c>
-      <c r="AD20">
+      <c r="AD21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1438/tillsynsmail/A 44363-2023 tillsynsbegäran mail.docx", "A 44363-2023")</f>
         <v/>
       </c>
-      <c r="AE20">
+      <c r="AE21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1438/fåglar/A 44363-2023 prioriterade fågelarter.docx", "A 44363-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
         <is>
           <t>A 61742-2023</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
         <is>
           <t>Avverkning för annat ändamål</t>
         </is>
       </c>
-      <c r="D21" s="1" t="n">
+      <c r="D22" s="1" t="n">
         <v>45265</v>
       </c>
-      <c r="E21" s="1" t="n">
-        <v>46292</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>DALS-ED</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
+      <c r="E22" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>DALS-ED</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
         <v>0.6</v>
       </c>
-      <c r="J21" t="n">
+      <c r="J22" t="n">
         <v>1</v>
       </c>
-      <c r="K21" t="n">
+      <c r="K22" t="n">
         <v>2</v>
       </c>
-      <c r="L21" t="n">
+      <c r="L22" t="n">
         <v>2</v>
       </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
         <v>2</v>
       </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
         <v>5</v>
       </c>
-      <c r="T21" t="n">
+      <c r="T22" t="n">
         <v>6</v>
       </c>
-      <c r="U21" t="n">
+      <c r="U22" t="n">
         <v>6</v>
       </c>
-      <c r="V21" s="2" t="inlineStr">
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>Dropptaggsvamp
 Nordtagging
@@ -2951,254 +3079,147 @@
 Tjäder</t>
         </is>
       </c>
-      <c r="W21">
+      <c r="W22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1438/artfynd/A 61742-2023 artfynd.xlsx", "A 61742-2023")</f>
         <v/>
       </c>
-      <c r="X21">
+      <c r="X22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1438/kartor/A 61742-2023 karta.png", "A 61742-2023")</f>
         <v/>
       </c>
-      <c r="Y21">
+      <c r="Y22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1438/kartor_geotiff/A 61742-2023 georefererad karta.tif", "A 61742-2023")</f>
         <v/>
       </c>
-      <c r="AA21">
+      <c r="AA22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1438/klagomål/A 61742-2023 FSC-klagomål.docx", "A 61742-2023")</f>
         <v/>
       </c>
-      <c r="AB21">
+      <c r="AB22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1438/klagomålsmail/A 61742-2023 FSC-klagomål mail.docx", "A 61742-2023")</f>
         <v/>
       </c>
-      <c r="AC21">
+      <c r="AC22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1438/tillsyn/A 61742-2023 tillsynsbegäran.docx", "A 61742-2023")</f>
         <v/>
       </c>
-      <c r="AD21">
+      <c r="AD22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1438/tillsynsmail/A 61742-2023 tillsynsbegäran mail.docx", "A 61742-2023")</f>
         <v/>
       </c>
-      <c r="AE21">
+      <c r="AE22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1438/fåglar/A 61742-2023 prioriterade fågelarter.docx", "A 61742-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
         <is>
           <t>A 4645-2026</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="n">
         <v>46048</v>
       </c>
-      <c r="E22" s="1" t="n">
-        <v>46292</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>DALS-ED</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
+      <c r="E23" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>DALS-ED</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="J22" t="n">
+      <c r="J23" t="n">
         <v>2</v>
       </c>
-      <c r="K22" t="n">
+      <c r="K23" t="n">
         <v>1</v>
       </c>
-      <c r="L22" t="n">
+      <c r="L23" t="n">
         <v>1</v>
       </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
         <v>1</v>
       </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
         <v>3</v>
       </c>
-      <c r="T22" t="n">
+      <c r="T23" t="n">
         <v>3</v>
       </c>
-      <c r="U22" t="n">
+      <c r="U23" t="n">
         <v>3</v>
       </c>
-      <c r="V22" s="2" t="inlineStr">
+      <c r="V23" s="2" t="inlineStr">
         <is>
           <t>Talltita
 Västlig hakmossa
 Lopplummer (aggregat)</t>
         </is>
       </c>
-      <c r="W22">
+      <c r="W23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1438/artfynd/A 4645-2026 artfynd.xlsx", "A 4645-2026")</f>
         <v/>
       </c>
-      <c r="X22">
+      <c r="X23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1438/kartor/A 4645-2026 karta.png", "A 4645-2026")</f>
         <v/>
       </c>
-      <c r="Y22">
+      <c r="Y23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1438/kartor_geotiff/A 4645-2026 georefererad karta.tif", "A 4645-2026")</f>
         <v/>
       </c>
-      <c r="AA22">
+      <c r="AA23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1438/klagomål/A 4645-2026 FSC-klagomål.docx", "A 4645-2026")</f>
         <v/>
       </c>
-      <c r="AB22">
+      <c r="AB23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1438/klagomålsmail/A 4645-2026 FSC-klagomål mail.docx", "A 4645-2026")</f>
         <v/>
       </c>
-      <c r="AC22">
+      <c r="AC23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1438/tillsyn/A 4645-2026 tillsynsbegäran.docx", "A 4645-2026")</f>
         <v/>
       </c>
-      <c r="AD22">
+      <c r="AD23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1438/tillsynsmail/A 4645-2026 tillsynsbegäran mail.docx", "A 4645-2026")</f>
         <v/>
       </c>
-      <c r="AE22">
+      <c r="AE23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1438/fåglar/A 4645-2026 prioriterade fågelarter.docx", "A 4645-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>A 22939-2026</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="n">
-        <v>46160</v>
-      </c>
-      <c r="E23" s="1" t="n">
-        <v>46292</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>DALS-ED</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>3</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>2</v>
-      </c>
-      <c r="M23" t="n">
-        <v>1</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>3</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3</v>
-      </c>
-      <c r="T23" t="n">
-        <v>4</v>
-      </c>
-      <c r="U23" t="n">
-        <v>4</v>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>Garnlav
-Dropptaggsvamp
-Kortskaftad ärgspik</t>
-        </is>
-      </c>
-      <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/artfynd/A 22939-2026 artfynd.xlsx", "A 22939-2026")</f>
-        <v/>
-      </c>
-      <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/kartor/A 22939-2026 karta.png", "A 22939-2026")</f>
-        <v/>
-      </c>
-      <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/kartor_geotiff/A 22939-2026 georefererad karta.tif", "A 22939-2026")</f>
-        <v/>
-      </c>
-      <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/klagomål/A 22939-2026 FSC-klagomål.docx", "A 22939-2026")</f>
-        <v/>
-      </c>
-      <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/klagomålsmail/A 22939-2026 FSC-klagomål mail.docx", "A 22939-2026")</f>
-        <v/>
-      </c>
-      <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/tillsyn/A 22939-2026 tillsynsbegäran.docx", "A 22939-2026")</f>
-        <v/>
-      </c>
-      <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/tillsynsmail/A 22939-2026 tillsynsbegäran mail.docx", "A 22939-2026")</f>
         <v/>
       </c>
     </row>
@@ -3222,7 +3243,7 @@
         <v>45151</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3337,7 +3358,7 @@
         <v>45422</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3448,7 +3469,7 @@
         <v>45937</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3562,7 +3583,7 @@
         <v>45588</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3672,7 +3693,7 @@
         <v>45569</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3778,7 +3799,7 @@
         <v>44601</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3884,7 +3905,7 @@
         <v>45572</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3994,7 +4015,7 @@
         <v>46245</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4100,7 +4121,7 @@
         <v>46251</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4210,7 +4231,7 @@
         <v>45281</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4303,7 +4324,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 24788-2025</t>
+          <t>A 51214-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4317,10 +4338,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45799</v>
+        <v>44865</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4332,17 +4353,22 @@
           <t>DALS-ED</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I34" t="n">
-        <v>4.1</v>
+        <v>3</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
@@ -4357,7 +4383,7 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
@@ -4369,46 +4395,46 @@
         <v>1</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/artfynd/A 24788-2025 artfynd.xlsx", "A 24788-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/artfynd/A 51214-2022 artfynd.xlsx", "A 51214-2022")</f>
         <v/>
       </c>
       <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/kartor/A 24788-2025 karta.png", "A 24788-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/kartor/A 51214-2022 karta.png", "A 51214-2022")</f>
         <v/>
       </c>
       <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/kartor_geotiff/A 24788-2025 georefererad karta.tif", "A 24788-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/kartor_geotiff/A 51214-2022 georefererad karta.tif", "A 51214-2022")</f>
         <v/>
       </c>
       <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/klagomål/A 24788-2025 FSC-klagomål.docx", "A 24788-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/klagomål/A 51214-2022 FSC-klagomål.docx", "A 51214-2022")</f>
         <v/>
       </c>
       <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/klagomålsmail/A 24788-2025 FSC-klagomål mail.docx", "A 24788-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/klagomålsmail/A 51214-2022 FSC-klagomål mail.docx", "A 51214-2022")</f>
         <v/>
       </c>
       <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/tillsyn/A 24788-2025 tillsynsbegäran.docx", "A 24788-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/tillsyn/A 51214-2022 tillsynsbegäran.docx", "A 51214-2022")</f>
         <v/>
       </c>
       <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/tillsynsmail/A 24788-2025 tillsynsbegäran mail.docx", "A 24788-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/tillsynsmail/A 51214-2022 tillsynsbegäran mail.docx", "A 51214-2022")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 25638-2025</t>
+          <t>A 24788-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4422,10 +4448,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45803</v>
+        <v>45799</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4438,17 +4464,17 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.2</v>
+        <v>4.1</v>
       </c>
       <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
         <v>1</v>
       </c>
-      <c r="K35" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
       <c r="M35" t="n">
         <v>0</v>
       </c>
@@ -4462,7 +4488,7 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -4478,46 +4504,42 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>Nattskärra</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/artfynd/A 25638-2025 artfynd.xlsx", "A 25638-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/artfynd/A 24788-2025 artfynd.xlsx", "A 24788-2025")</f>
         <v/>
       </c>
       <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/kartor/A 25638-2025 karta.png", "A 25638-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/kartor/A 24788-2025 karta.png", "A 24788-2025")</f>
         <v/>
       </c>
       <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/kartor_geotiff/A 25638-2025 georefererad karta.tif", "A 25638-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/kartor_geotiff/A 24788-2025 georefererad karta.tif", "A 24788-2025")</f>
         <v/>
       </c>
       <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/klagomål/A 25638-2025 FSC-klagomål.docx", "A 25638-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/klagomål/A 24788-2025 FSC-klagomål.docx", "A 24788-2025")</f>
         <v/>
       </c>
       <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/klagomålsmail/A 25638-2025 FSC-klagomål mail.docx", "A 25638-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/klagomålsmail/A 24788-2025 FSC-klagomål mail.docx", "A 24788-2025")</f>
         <v/>
       </c>
       <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/tillsyn/A 25638-2025 tillsynsbegäran.docx", "A 25638-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/tillsyn/A 24788-2025 tillsynsbegäran.docx", "A 24788-2025")</f>
         <v/>
       </c>
       <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/tillsynsmail/A 25638-2025 tillsynsbegäran mail.docx", "A 25638-2025")</f>
-        <v/>
-      </c>
-      <c r="AE35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/fåglar/A 25638-2025 prioriterade fågelarter.docx", "A 25638-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/tillsynsmail/A 24788-2025 tillsynsbegäran mail.docx", "A 24788-2025")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 47311-2025</t>
+          <t>A 25638-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4531,10 +4553,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45930</v>
+        <v>45803</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4547,10 +4569,10 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -4562,7 +4584,7 @@
         <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4571,10 +4593,10 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -4587,42 +4609,46 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>Kantlök</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="W36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/artfynd/A 47311-2025 artfynd.xlsx", "A 47311-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/artfynd/A 25638-2025 artfynd.xlsx", "A 25638-2025")</f>
         <v/>
       </c>
       <c r="X36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/kartor/A 47311-2025 karta.png", "A 47311-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/kartor/A 25638-2025 karta.png", "A 25638-2025")</f>
         <v/>
       </c>
       <c r="Y36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/kartor_geotiff/A 47311-2025 georefererad karta.tif", "A 47311-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/kartor_geotiff/A 25638-2025 georefererad karta.tif", "A 25638-2025")</f>
         <v/>
       </c>
       <c r="AA36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/klagomål/A 47311-2025 FSC-klagomål.docx", "A 47311-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/klagomål/A 25638-2025 FSC-klagomål.docx", "A 25638-2025")</f>
         <v/>
       </c>
       <c r="AB36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/klagomålsmail/A 47311-2025 FSC-klagomål mail.docx", "A 47311-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/klagomålsmail/A 25638-2025 FSC-klagomål mail.docx", "A 25638-2025")</f>
         <v/>
       </c>
       <c r="AC36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/tillsyn/A 47311-2025 tillsynsbegäran.docx", "A 47311-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/tillsyn/A 25638-2025 tillsynsbegäran.docx", "A 25638-2025")</f>
         <v/>
       </c>
       <c r="AD36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/tillsynsmail/A 47311-2025 tillsynsbegäran mail.docx", "A 47311-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/tillsynsmail/A 25638-2025 tillsynsbegäran mail.docx", "A 25638-2025")</f>
+        <v/>
+      </c>
+      <c r="AE36">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/fåglar/A 25638-2025 prioriterade fågelarter.docx", "A 25638-2025")</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 23862-2023</t>
+          <t>A 47311-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4632,14 +4658,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45075</v>
+        <v>45930</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4652,7 +4678,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4661,13 +4687,13 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
         <v>1</v>
-      </c>
-      <c r="M37" t="n">
-        <v>0</v>
-      </c>
-      <c r="N37" t="n">
-        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4679,7 +4705,7 @@
         <v>1</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
@@ -4692,42 +4718,42 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>Jungfrulin</t>
+          <t>Kantlök</t>
         </is>
       </c>
       <c r="W37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/artfynd/A 23862-2023 artfynd.xlsx", "A 23862-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/artfynd/A 47311-2025 artfynd.xlsx", "A 47311-2025")</f>
         <v/>
       </c>
       <c r="X37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/kartor/A 23862-2023 karta.png", "A 23862-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/kartor/A 47311-2025 karta.png", "A 47311-2025")</f>
         <v/>
       </c>
       <c r="Y37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/kartor_geotiff/A 23862-2023 georefererad karta.tif", "A 23862-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/kartor_geotiff/A 47311-2025 georefererad karta.tif", "A 47311-2025")</f>
         <v/>
       </c>
       <c r="AA37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/klagomål/A 23862-2023 FSC-klagomål.docx", "A 23862-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/klagomål/A 47311-2025 FSC-klagomål.docx", "A 47311-2025")</f>
         <v/>
       </c>
       <c r="AB37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/klagomålsmail/A 23862-2023 FSC-klagomål mail.docx", "A 23862-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/klagomålsmail/A 47311-2025 FSC-klagomål mail.docx", "A 47311-2025")</f>
         <v/>
       </c>
       <c r="AC37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/tillsyn/A 23862-2023 tillsynsbegäran.docx", "A 23862-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/tillsyn/A 47311-2025 tillsynsbegäran.docx", "A 47311-2025")</f>
         <v/>
       </c>
       <c r="AD37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/tillsynsmail/A 23862-2023 tillsynsbegäran mail.docx", "A 23862-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/tillsynsmail/A 47311-2025 tillsynsbegäran mail.docx", "A 47311-2025")</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 27878-2024</t>
+          <t>A 23862-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4737,14 +4763,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45475</v>
+        <v>45075</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4757,7 +4783,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>4.2</v>
+        <v>1.2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4793,46 +4819,46 @@
         <v>1</v>
       </c>
       <c r="U38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Jungfrulin</t>
         </is>
       </c>
       <c r="W38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/artfynd/A 27878-2024 artfynd.xlsx", "A 27878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/artfynd/A 23862-2023 artfynd.xlsx", "A 23862-2023")</f>
         <v/>
       </c>
       <c r="X38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/kartor/A 27878-2024 karta.png", "A 27878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/kartor/A 23862-2023 karta.png", "A 23862-2023")</f>
         <v/>
       </c>
       <c r="Y38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/kartor_geotiff/A 27878-2024 georefererad karta.tif", "A 27878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/kartor_geotiff/A 23862-2023 georefererad karta.tif", "A 23862-2023")</f>
         <v/>
       </c>
       <c r="AA38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/klagomål/A 27878-2024 FSC-klagomål.docx", "A 27878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/klagomål/A 23862-2023 FSC-klagomål.docx", "A 23862-2023")</f>
         <v/>
       </c>
       <c r="AB38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/klagomålsmail/A 27878-2024 FSC-klagomål mail.docx", "A 27878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/klagomålsmail/A 23862-2023 FSC-klagomål mail.docx", "A 23862-2023")</f>
         <v/>
       </c>
       <c r="AC38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/tillsyn/A 27878-2024 tillsynsbegäran.docx", "A 27878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/tillsyn/A 23862-2023 tillsynsbegäran.docx", "A 23862-2023")</f>
         <v/>
       </c>
       <c r="AD38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/tillsynsmail/A 27878-2024 tillsynsbegäran mail.docx", "A 27878-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/tillsynsmail/A 23862-2023 tillsynsbegäran mail.docx", "A 23862-2023")</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 14793-2023</t>
+          <t>A 27878-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4846,10 +4872,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45014</v>
+        <v>45475</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4862,7 +4888,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.6</v>
+        <v>4.2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4871,10 +4897,10 @@
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
         <v>0</v>
@@ -4889,7 +4915,7 @@
         <v>1</v>
       </c>
       <c r="R39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
@@ -4902,42 +4928,42 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>Slåttergubbe</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="W39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/artfynd/A 14793-2023 artfynd.xlsx", "A 14793-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/artfynd/A 27878-2024 artfynd.xlsx", "A 27878-2024")</f>
         <v/>
       </c>
       <c r="X39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/kartor/A 14793-2023 karta.png", "A 14793-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/kartor/A 27878-2024 karta.png", "A 27878-2024")</f>
         <v/>
       </c>
       <c r="Y39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/kartor_geotiff/A 14793-2023 georefererad karta.tif", "A 14793-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/kartor_geotiff/A 27878-2024 georefererad karta.tif", "A 27878-2024")</f>
         <v/>
       </c>
       <c r="AA39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/klagomål/A 14793-2023 FSC-klagomål.docx", "A 14793-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/klagomål/A 27878-2024 FSC-klagomål.docx", "A 27878-2024")</f>
         <v/>
       </c>
       <c r="AB39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/klagomålsmail/A 14793-2023 FSC-klagomål mail.docx", "A 14793-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/klagomålsmail/A 27878-2024 FSC-klagomål mail.docx", "A 27878-2024")</f>
         <v/>
       </c>
       <c r="AC39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/tillsyn/A 14793-2023 tillsynsbegäran.docx", "A 14793-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/tillsyn/A 27878-2024 tillsynsbegäran.docx", "A 27878-2024")</f>
         <v/>
       </c>
       <c r="AD39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/tillsynsmail/A 14793-2023 tillsynsbegäran mail.docx", "A 14793-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/tillsynsmail/A 27878-2024 tillsynsbegäran mail.docx", "A 27878-2024")</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 47656-2024</t>
+          <t>A 14793-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4951,10 +4977,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45588</v>
+        <v>45014</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4967,19 +4993,19 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>7.3</v>
+        <v>1.6</v>
       </c>
       <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
         <v>1</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0</v>
-      </c>
-      <c r="L40" t="n">
-        <v>1</v>
-      </c>
-      <c r="M40" t="n">
-        <v>0</v>
       </c>
       <c r="N40" t="n">
         <v>0</v>
@@ -4994,59 +5020,55 @@
         <v>1</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
       </c>
       <c r="T40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Slåttergubbe</t>
         </is>
       </c>
       <c r="W40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/artfynd/A 47656-2024 artfynd.xlsx", "A 47656-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/artfynd/A 14793-2023 artfynd.xlsx", "A 14793-2023")</f>
         <v/>
       </c>
       <c r="X40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/kartor/A 47656-2024 karta.png", "A 47656-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/kartor/A 14793-2023 karta.png", "A 14793-2023")</f>
         <v/>
       </c>
       <c r="Y40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/kartor_geotiff/A 47656-2024 georefererad karta.tif", "A 47656-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/kartor_geotiff/A 14793-2023 georefererad karta.tif", "A 14793-2023")</f>
         <v/>
       </c>
       <c r="AA40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/klagomål/A 47656-2024 FSC-klagomål.docx", "A 47656-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/klagomål/A 14793-2023 FSC-klagomål.docx", "A 14793-2023")</f>
         <v/>
       </c>
       <c r="AB40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/klagomålsmail/A 47656-2024 FSC-klagomål mail.docx", "A 47656-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/klagomålsmail/A 14793-2023 FSC-klagomål mail.docx", "A 14793-2023")</f>
         <v/>
       </c>
       <c r="AC40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/tillsyn/A 47656-2024 tillsynsbegäran.docx", "A 47656-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/tillsyn/A 14793-2023 tillsynsbegäran.docx", "A 14793-2023")</f>
         <v/>
       </c>
       <c r="AD40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/tillsynsmail/A 47656-2024 tillsynsbegäran mail.docx", "A 47656-2024")</f>
-        <v/>
-      </c>
-      <c r="AE40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/fåglar/A 47656-2024 prioriterade fågelarter.docx", "A 47656-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/tillsynsmail/A 14793-2023 tillsynsbegäran mail.docx", "A 14793-2023")</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 32284-2023</t>
+          <t>A 47656-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5060,10 +5082,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45120</v>
+        <v>45588</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5076,19 +5098,19 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3.9</v>
+        <v>7.3</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
         <v>0</v>
@@ -5103,55 +5125,59 @@
         <v>1</v>
       </c>
       <c r="R41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
       </c>
       <c r="T41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>Mindre bastardsvärmare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="W41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/artfynd/A 32284-2023 artfynd.xlsx", "A 32284-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/artfynd/A 47656-2024 artfynd.xlsx", "A 47656-2024")</f>
         <v/>
       </c>
       <c r="X41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/kartor/A 32284-2023 karta.png", "A 32284-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/kartor/A 47656-2024 karta.png", "A 47656-2024")</f>
         <v/>
       </c>
       <c r="Y41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/kartor_geotiff/A 32284-2023 georefererad karta.tif", "A 32284-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/kartor_geotiff/A 47656-2024 georefererad karta.tif", "A 47656-2024")</f>
         <v/>
       </c>
       <c r="AA41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/klagomål/A 32284-2023 FSC-klagomål.docx", "A 32284-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/klagomål/A 47656-2024 FSC-klagomål.docx", "A 47656-2024")</f>
         <v/>
       </c>
       <c r="AB41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/klagomålsmail/A 32284-2023 FSC-klagomål mail.docx", "A 32284-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/klagomålsmail/A 47656-2024 FSC-klagomål mail.docx", "A 47656-2024")</f>
         <v/>
       </c>
       <c r="AC41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/tillsyn/A 32284-2023 tillsynsbegäran.docx", "A 32284-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/tillsyn/A 47656-2024 tillsynsbegäran.docx", "A 47656-2024")</f>
         <v/>
       </c>
       <c r="AD41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/tillsynsmail/A 32284-2023 tillsynsbegäran mail.docx", "A 32284-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/tillsynsmail/A 47656-2024 tillsynsbegäran mail.docx", "A 47656-2024")</f>
+        <v/>
+      </c>
+      <c r="AE41">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/fåglar/A 47656-2024 prioriterade fågelarter.docx", "A 47656-2024")</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 40355-2022</t>
+          <t>A 32284-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5165,10 +5191,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44818</v>
+        <v>45120</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5180,13 +5206,8 @@
           <t>DALS-ED</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I42" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -5198,10 +5219,10 @@
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5226,42 +5247,42 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>Kantlök</t>
+          <t>Mindre bastardsvärmare</t>
         </is>
       </c>
       <c r="W42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/artfynd/A 40355-2022 artfynd.xlsx", "A 40355-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/artfynd/A 32284-2023 artfynd.xlsx", "A 32284-2023")</f>
         <v/>
       </c>
       <c r="X42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/kartor/A 40355-2022 karta.png", "A 40355-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/kartor/A 32284-2023 karta.png", "A 32284-2023")</f>
         <v/>
       </c>
       <c r="Y42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/kartor_geotiff/A 40355-2022 georefererad karta.tif", "A 40355-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/kartor_geotiff/A 32284-2023 georefererad karta.tif", "A 32284-2023")</f>
         <v/>
       </c>
       <c r="AA42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/klagomål/A 40355-2022 FSC-klagomål.docx", "A 40355-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/klagomål/A 32284-2023 FSC-klagomål.docx", "A 32284-2023")</f>
         <v/>
       </c>
       <c r="AB42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/klagomålsmail/A 40355-2022 FSC-klagomål mail.docx", "A 40355-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/klagomålsmail/A 32284-2023 FSC-klagomål mail.docx", "A 32284-2023")</f>
         <v/>
       </c>
       <c r="AC42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/tillsyn/A 40355-2022 tillsynsbegäran.docx", "A 40355-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/tillsyn/A 32284-2023 tillsynsbegäran.docx", "A 32284-2023")</f>
         <v/>
       </c>
       <c r="AD42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/tillsynsmail/A 40355-2022 tillsynsbegäran mail.docx", "A 40355-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/tillsynsmail/A 32284-2023 tillsynsbegäran mail.docx", "A 32284-2023")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 15626-2024</t>
+          <t>A 40355-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5275,10 +5296,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45402</v>
+        <v>44818</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5290,8 +5311,13 @@
           <t>DALS-ED</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>9.9</v>
+        <v>4.2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -5300,13 +5326,13 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="n">
         <v>1</v>
-      </c>
-      <c r="M43" t="n">
-        <v>0</v>
-      </c>
-      <c r="N43" t="n">
-        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5318,55 +5344,55 @@
         <v>1</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S43" t="n">
         <v>1</v>
       </c>
       <c r="T43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U43" t="n">
         <v>0</v>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>Jungfrulin</t>
+          <t>Kantlök</t>
         </is>
       </c>
       <c r="W43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/artfynd/A 15626-2024 artfynd.xlsx", "A 15626-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/artfynd/A 40355-2022 artfynd.xlsx", "A 40355-2022")</f>
         <v/>
       </c>
       <c r="X43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/kartor/A 15626-2024 karta.png", "A 15626-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/kartor/A 40355-2022 karta.png", "A 40355-2022")</f>
         <v/>
       </c>
       <c r="Y43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/kartor_geotiff/A 15626-2024 georefererad karta.tif", "A 15626-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/kartor_geotiff/A 40355-2022 georefererad karta.tif", "A 40355-2022")</f>
         <v/>
       </c>
       <c r="AA43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/klagomål/A 15626-2024 FSC-klagomål.docx", "A 15626-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/klagomål/A 40355-2022 FSC-klagomål.docx", "A 40355-2022")</f>
         <v/>
       </c>
       <c r="AB43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/klagomålsmail/A 15626-2024 FSC-klagomål mail.docx", "A 15626-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/klagomålsmail/A 40355-2022 FSC-klagomål mail.docx", "A 40355-2022")</f>
         <v/>
       </c>
       <c r="AC43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/tillsyn/A 15626-2024 tillsynsbegäran.docx", "A 15626-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/tillsyn/A 40355-2022 tillsynsbegäran.docx", "A 40355-2022")</f>
         <v/>
       </c>
       <c r="AD43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/tillsynsmail/A 15626-2024 tillsynsbegäran mail.docx", "A 15626-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/tillsynsmail/A 40355-2022 tillsynsbegäran mail.docx", "A 40355-2022")</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 56442-2023</t>
+          <t>A 15626-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5380,10 +5406,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45237</v>
+        <v>45402</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5395,13 +5421,8 @@
           <t>DALS-ED</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>8.300000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -5434,49 +5455,49 @@
         <v>1</v>
       </c>
       <c r="T44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U44" t="n">
         <v>0</v>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>Bergjohannesört</t>
+          <t>Jungfrulin</t>
         </is>
       </c>
       <c r="W44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/artfynd/A 56442-2023 artfynd.xlsx", "A 56442-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/artfynd/A 15626-2024 artfynd.xlsx", "A 15626-2024")</f>
         <v/>
       </c>
       <c r="X44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/kartor/A 56442-2023 karta.png", "A 56442-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/kartor/A 15626-2024 karta.png", "A 15626-2024")</f>
         <v/>
       </c>
       <c r="Y44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/kartor_geotiff/A 56442-2023 georefererad karta.tif", "A 56442-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/kartor_geotiff/A 15626-2024 georefererad karta.tif", "A 15626-2024")</f>
         <v/>
       </c>
       <c r="AA44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/klagomål/A 56442-2023 FSC-klagomål.docx", "A 56442-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/klagomål/A 15626-2024 FSC-klagomål.docx", "A 15626-2024")</f>
         <v/>
       </c>
       <c r="AB44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/klagomålsmail/A 56442-2023 FSC-klagomål mail.docx", "A 56442-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/klagomålsmail/A 15626-2024 FSC-klagomål mail.docx", "A 15626-2024")</f>
         <v/>
       </c>
       <c r="AC44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/tillsyn/A 56442-2023 tillsynsbegäran.docx", "A 56442-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/tillsyn/A 15626-2024 tillsynsbegäran.docx", "A 15626-2024")</f>
         <v/>
       </c>
       <c r="AD44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/tillsynsmail/A 56442-2023 tillsynsbegäran mail.docx", "A 56442-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/tillsynsmail/A 15626-2024 tillsynsbegäran mail.docx", "A 15626-2024")</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 4113-2023</t>
+          <t>A 56442-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5490,10 +5511,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44952</v>
+        <v>45237</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5505,8 +5526,13 @@
           <t>DALS-ED</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>7.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5515,10 +5541,10 @@
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
         <v>0</v>
@@ -5533,7 +5559,7 @@
         <v>1</v>
       </c>
       <c r="R45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>1</v>
@@ -5546,42 +5572,42 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>Slåttergubbe</t>
+          <t>Bergjohannesört</t>
         </is>
       </c>
       <c r="W45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/artfynd/A 4113-2023 artfynd.xlsx", "A 4113-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/artfynd/A 56442-2023 artfynd.xlsx", "A 56442-2023")</f>
         <v/>
       </c>
       <c r="X45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/kartor/A 4113-2023 karta.png", "A 4113-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/kartor/A 56442-2023 karta.png", "A 56442-2023")</f>
         <v/>
       </c>
       <c r="Y45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/kartor_geotiff/A 4113-2023 georefererad karta.tif", "A 4113-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/kartor_geotiff/A 56442-2023 georefererad karta.tif", "A 56442-2023")</f>
         <v/>
       </c>
       <c r="AA45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/klagomål/A 4113-2023 FSC-klagomål.docx", "A 4113-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/klagomål/A 56442-2023 FSC-klagomål.docx", "A 56442-2023")</f>
         <v/>
       </c>
       <c r="AB45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/klagomålsmail/A 4113-2023 FSC-klagomål mail.docx", "A 4113-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/klagomålsmail/A 56442-2023 FSC-klagomål mail.docx", "A 56442-2023")</f>
         <v/>
       </c>
       <c r="AC45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/tillsyn/A 4113-2023 tillsynsbegäran.docx", "A 4113-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/tillsyn/A 56442-2023 tillsynsbegäran.docx", "A 56442-2023")</f>
         <v/>
       </c>
       <c r="AD45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/tillsynsmail/A 4113-2023 tillsynsbegäran mail.docx", "A 4113-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/tillsynsmail/A 56442-2023 tillsynsbegäran mail.docx", "A 56442-2023")</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 43216-2023</t>
+          <t>A 4113-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5595,10 +5621,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45183</v>
+        <v>44952</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5611,20 +5637,20 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>7.3</v>
+        <v>7.9</v>
       </c>
       <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
         <v>1</v>
       </c>
-      <c r="K46" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" t="n">
-        <v>0</v>
-      </c>
-      <c r="M46" t="n">
-        <v>0</v>
-      </c>
       <c r="N46" t="n">
         <v>0</v>
       </c>
@@ -5635,79 +5661,75 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S46" t="n">
         <v>1</v>
       </c>
       <c r="T46" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U46" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Slåttergubbe</t>
         </is>
       </c>
       <c r="W46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/artfynd/A 43216-2023 artfynd.xlsx", "A 43216-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/artfynd/A 4113-2023 artfynd.xlsx", "A 4113-2023")</f>
         <v/>
       </c>
       <c r="X46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/kartor/A 43216-2023 karta.png", "A 43216-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/kartor/A 4113-2023 karta.png", "A 4113-2023")</f>
         <v/>
       </c>
       <c r="Y46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/kartor_geotiff/A 43216-2023 georefererad karta.tif", "A 43216-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/kartor_geotiff/A 4113-2023 georefererad karta.tif", "A 4113-2023")</f>
         <v/>
       </c>
       <c r="AA46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/klagomål/A 43216-2023 FSC-klagomål.docx", "A 43216-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/klagomål/A 4113-2023 FSC-klagomål.docx", "A 4113-2023")</f>
         <v/>
       </c>
       <c r="AB46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/klagomålsmail/A 43216-2023 FSC-klagomål mail.docx", "A 43216-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/klagomålsmail/A 4113-2023 FSC-klagomål mail.docx", "A 4113-2023")</f>
         <v/>
       </c>
       <c r="AC46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/tillsyn/A 43216-2023 tillsynsbegäran.docx", "A 43216-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/tillsyn/A 4113-2023 tillsynsbegäran.docx", "A 4113-2023")</f>
         <v/>
       </c>
       <c r="AD46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/tillsynsmail/A 43216-2023 tillsynsbegäran mail.docx", "A 43216-2023")</f>
-        <v/>
-      </c>
-      <c r="AE46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/fåglar/A 43216-2023 prioriterade fågelarter.docx", "A 43216-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/tillsynsmail/A 4113-2023 tillsynsbegäran mail.docx", "A 4113-2023")</f>
         <v/>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>S 299-2025</t>
+          <t>A 43216-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45687</v>
+        <v>45183</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5720,16 +5742,16 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.5</v>
+        <v>7.3</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
         <v>0</v>
@@ -5744,7 +5766,7 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
         <v>0</v>
@@ -5753,66 +5775,70 @@
         <v>1</v>
       </c>
       <c r="T47" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/artfynd/S 299-2025 artfynd.xlsx", "S 299-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/artfynd/A 43216-2023 artfynd.xlsx", "A 43216-2023")</f>
         <v/>
       </c>
       <c r="X47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/kartor/S 299-2025 karta.png", "S 299-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/kartor/A 43216-2023 karta.png", "A 43216-2023")</f>
         <v/>
       </c>
       <c r="Y47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/kartor_geotiff/S 299-2025 georefererad karta.tif", "S 299-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/kartor_geotiff/A 43216-2023 georefererad karta.tif", "A 43216-2023")</f>
         <v/>
       </c>
       <c r="AA47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/klagomål/S 299-2025 FSC-klagomål.docx", "S 299-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/klagomål/A 43216-2023 FSC-klagomål.docx", "A 43216-2023")</f>
         <v/>
       </c>
       <c r="AB47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/klagomålsmail/S 299-2025 FSC-klagomål mail.docx", "S 299-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/klagomålsmail/A 43216-2023 FSC-klagomål mail.docx", "A 43216-2023")</f>
         <v/>
       </c>
       <c r="AC47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/tillsyn/S 299-2025 tillsynsbegäran.docx", "S 299-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/tillsyn/A 43216-2023 tillsynsbegäran.docx", "A 43216-2023")</f>
         <v/>
       </c>
       <c r="AD47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1438/tillsynsmail/S 299-2025 tillsynsbegäran mail.docx", "S 299-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/tillsynsmail/A 43216-2023 tillsynsbegäran mail.docx", "A 43216-2023")</f>
+        <v/>
+      </c>
+      <c r="AE47">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/fåglar/A 43216-2023 prioriterade fågelarter.docx", "A 43216-2023")</f>
         <v/>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 32317-2022</t>
+          <t>S 299-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44781</v>
+        <v>45687</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5825,7 +5851,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5834,7 +5860,7 @@
         <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M48" t="n">
         <v>0</v>
@@ -5849,26 +5875,58 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R48" t="n">
         <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U48" t="n">
         <v>0</v>
       </c>
-      <c r="V48" s="2" t="inlineStr"/>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>Slåtterfibbla</t>
+        </is>
+      </c>
+      <c r="W48">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/artfynd/S 299-2025 artfynd.xlsx", "S 299-2025")</f>
+        <v/>
+      </c>
+      <c r="X48">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/kartor/S 299-2025 karta.png", "S 299-2025")</f>
+        <v/>
+      </c>
+      <c r="Y48">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/kartor_geotiff/S 299-2025 georefererad karta.tif", "S 299-2025")</f>
+        <v/>
+      </c>
+      <c r="AA48">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/klagomål/S 299-2025 FSC-klagomål.docx", "S 299-2025")</f>
+        <v/>
+      </c>
+      <c r="AB48">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/klagomålsmail/S 299-2025 FSC-klagomål mail.docx", "S 299-2025")</f>
+        <v/>
+      </c>
+      <c r="AC48">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/tillsyn/S 299-2025 tillsynsbegäran.docx", "S 299-2025")</f>
+        <v/>
+      </c>
+      <c r="AD48">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1438/tillsynsmail/S 299-2025 tillsynsbegäran mail.docx", "S 299-2025")</f>
+        <v/>
+      </c>
     </row>
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 70027-2021</t>
+          <t>A 32317-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5882,10 +5940,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44533</v>
+        <v>44781</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5898,7 +5956,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>7.6</v>
+        <v>0.5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5941,7 +5999,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 70367-2021</t>
+          <t>A 70027-2021</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5955,10 +6013,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44536</v>
+        <v>44533</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5971,7 +6029,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3.2</v>
+        <v>7.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -6014,7 +6072,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 9153-2022</t>
+          <t>A 70367-2021</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -6028,10 +6086,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44615</v>
+        <v>44536</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6044,7 +6102,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.8</v>
+        <v>3.2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -6087,7 +6145,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 70374-2021</t>
+          <t>A 9153-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -6101,10 +6159,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44536</v>
+        <v>44615</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6117,7 +6175,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>7.8</v>
+        <v>0.8</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -6160,7 +6218,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 4121-2022</t>
+          <t>A 70374-2021</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -6174,10 +6232,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44588</v>
+        <v>44536</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6190,7 +6248,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.5</v>
+        <v>7.8</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -6233,7 +6291,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 18837-2022</t>
+          <t>A 4121-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6247,10 +6305,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44690</v>
+        <v>44588</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6263,7 +6321,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>4.7</v>
+        <v>0.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -6306,7 +6364,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 58213-2021</t>
+          <t>A 18837-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6320,10 +6378,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44487</v>
+        <v>44690</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6336,7 +6394,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>5.7</v>
+        <v>4.7</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -6379,7 +6437,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 51214-2022</t>
+          <t>A 58213-2021</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6393,10 +6451,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44865</v>
+        <v>44487</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6408,13 +6466,8 @@
           <t>DALS-ED</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>3</v>
+        <v>5.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -6474,7 +6527,7 @@
         <v>44733</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6547,7 +6600,7 @@
         <v>44781</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6620,7 +6673,7 @@
         <v>44676</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6693,7 +6746,7 @@
         <v>44578</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6766,7 +6819,7 @@
         <v>44799</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6839,7 +6892,7 @@
         <v>44705</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6912,7 +6965,7 @@
         <v>44743</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6985,7 +7038,7 @@
         <v>44615</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7058,7 +7111,7 @@
         <v>44608</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7131,7 +7184,7 @@
         <v>44823</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7204,7 +7257,7 @@
         <v>44837</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7277,7 +7330,7 @@
         <v>44657</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7355,7 +7408,7 @@
         <v>44685</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7428,7 +7481,7 @@
         <v>44685</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7501,7 +7554,7 @@
         <v>44705</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7574,7 +7627,7 @@
         <v>44705</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7647,7 +7700,7 @@
         <v>45702</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7720,7 +7773,7 @@
         <v>44825</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7793,7 +7846,7 @@
         <v>45257</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7866,7 +7919,7 @@
         <v>45187</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7939,7 +7992,7 @@
         <v>45412</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8012,7 +8065,7 @@
         <v>45531</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8085,7 +8138,7 @@
         <v>45412</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8158,7 +8211,7 @@
         <v>45359</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8231,7 +8284,7 @@
         <v>45393</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8304,7 +8357,7 @@
         <v>45440</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8377,7 +8430,7 @@
         <v>45440</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8450,7 +8503,7 @@
         <v>45217</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8528,7 +8581,7 @@
         <v>45428</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8601,7 +8654,7 @@
         <v>44895</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8679,7 +8732,7 @@
         <v>44823</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8752,7 +8805,7 @@
         <v>45119</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8825,7 +8878,7 @@
         <v>45400</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8898,7 +8951,7 @@
         <v>45478</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8971,7 +9024,7 @@
         <v>45796</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9044,7 +9097,7 @@
         <v>45279</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9122,7 +9175,7 @@
         <v>45346</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9195,7 +9248,7 @@
         <v>44855</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9268,7 +9321,7 @@
         <v>45796</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9341,7 +9394,7 @@
         <v>45883</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9414,7 +9467,7 @@
         <v>46028</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9487,7 +9540,7 @@
         <v>44942</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9560,7 +9613,7 @@
         <v>45342</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9633,7 +9686,7 @@
         <v>45798</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9706,7 +9759,7 @@
         <v>44659</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9779,7 +9832,7 @@
         <v>44895</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9852,7 +9905,7 @@
         <v>45666</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9925,7 +9978,7 @@
         <v>45798</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9998,7 +10051,7 @@
         <v>45328</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10071,7 +10124,7 @@
         <v>45671</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10144,7 +10197,7 @@
         <v>45887</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10217,7 +10270,7 @@
         <v>46031</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10290,7 +10343,7 @@
         <v>46031</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10363,7 +10416,7 @@
         <v>46035</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10436,7 +10489,7 @@
         <v>46035</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10509,7 +10562,7 @@
         <v>45773</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10582,7 +10635,7 @@
         <v>45475</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10655,7 +10708,7 @@
         <v>45246</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10728,7 +10781,7 @@
         <v>44601</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10801,7 +10854,7 @@
         <v>45895</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10874,7 +10927,7 @@
         <v>44875</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10947,7 +11000,7 @@
         <v>44902</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11020,7 +11073,7 @@
         <v>44901</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11093,7 +11146,7 @@
         <v>45833</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11166,7 +11219,7 @@
         <v>44909</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11239,7 +11292,7 @@
         <v>45597</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11312,7 +11365,7 @@
         <v>44648</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11385,7 +11438,7 @@
         <v>45902</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11458,7 +11511,7 @@
         <v>46048</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11531,7 +11584,7 @@
         <v>45903</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11604,7 +11657,7 @@
         <v>45904</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11677,7 +11730,7 @@
         <v>45904</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11750,7 +11803,7 @@
         <v>45902</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11823,7 +11876,7 @@
         <v>45908</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11901,7 +11954,7 @@
         <v>45646</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11974,7 +12027,7 @@
         <v>45908</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12052,7 +12105,7 @@
         <v>45202</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12125,7 +12178,7 @@
         <v>45909</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12198,7 +12251,7 @@
         <v>46056</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12271,7 +12324,7 @@
         <v>45909</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12349,7 +12402,7 @@
         <v>46055</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12422,7 +12475,7 @@
         <v>46056</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12495,7 +12548,7 @@
         <v>45603</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12568,7 +12621,7 @@
         <v>46060</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12641,7 +12694,7 @@
         <v>45922</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12714,7 +12767,7 @@
         <v>44952</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12787,7 +12840,7 @@
         <v>45803</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12860,7 +12913,7 @@
         <v>45804</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12933,7 +12986,7 @@
         <v>44600</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13011,7 +13064,7 @@
         <v>45118</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13084,7 +13137,7 @@
         <v>45925</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13157,7 +13210,7 @@
         <v>46073</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13230,7 +13283,7 @@
         <v>46073</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13303,7 +13356,7 @@
         <v>46073</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13376,7 +13429,7 @@
         <v>46073</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13449,7 +13502,7 @@
         <v>45925</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13527,7 +13580,7 @@
         <v>45358</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13605,7 +13658,7 @@
         <v>45047</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13678,7 +13731,7 @@
         <v>45929</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13751,7 +13804,7 @@
         <v>45929</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13824,7 +13877,7 @@
         <v>46080</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13902,7 +13955,7 @@
         <v>45541</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13975,7 +14028,7 @@
         <v>46083</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14048,7 +14101,7 @@
         <v>45470</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14121,7 +14174,7 @@
         <v>45632</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14194,7 +14247,7 @@
         <v>44705</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14267,7 +14320,7 @@
         <v>45932</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14340,7 +14393,7 @@
         <v>46087</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14413,7 +14466,7 @@
         <v>45932</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14486,7 +14539,7 @@
         <v>45150</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14559,7 +14612,7 @@
         <v>45595</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14632,7 +14685,7 @@
         <v>46093</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14705,7 +14758,7 @@
         <v>45940</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14778,7 +14831,7 @@
         <v>46101</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14851,7 +14904,7 @@
         <v>45946</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14924,7 +14977,7 @@
         <v>45588</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14997,7 +15050,7 @@
         <v>46100</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15070,7 +15123,7 @@
         <v>45189</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15143,7 +15196,7 @@
         <v>45951</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15216,7 +15269,7 @@
         <v>45951</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15294,7 +15347,7 @@
         <v>45812</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15367,7 +15420,7 @@
         <v>45624</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15440,7 +15493,7 @@
         <v>45951</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15518,7 +15571,7 @@
         <v>45762</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15591,7 +15644,7 @@
         <v>46113</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15664,7 +15717,7 @@
         <v>45958</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15737,7 +15790,7 @@
         <v>45811</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15810,7 +15863,7 @@
         <v>46113</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15883,7 +15936,7 @@
         <v>45624</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15956,7 +16009,7 @@
         <v>45006</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16029,7 +16082,7 @@
         <v>45037</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16102,7 +16155,7 @@
         <v>44952</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16175,7 +16228,7 @@
         <v>44958</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16248,7 +16301,7 @@
         <v>46126</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16321,7 +16374,7 @@
         <v>44952</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16394,7 +16447,7 @@
         <v>45974</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16472,7 +16525,7 @@
         <v>45973</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16545,7 +16598,7 @@
         <v>45974</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16618,7 +16671,7 @@
         <v>45974</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16691,7 +16744,7 @@
         <v>46126</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16764,7 +16817,7 @@
         <v>45973</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16837,7 +16890,7 @@
         <v>45974</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16910,7 +16963,7 @@
         <v>45761</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16983,7 +17036,7 @@
         <v>45978</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17056,7 +17109,7 @@
         <v>45978</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17129,7 +17182,7 @@
         <v>45161</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17207,7 +17260,7 @@
         <v>45162</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17280,7 +17333,7 @@
         <v>45590</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17353,7 +17406,7 @@
         <v>45981</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17426,7 +17479,7 @@
         <v>45615</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17499,7 +17552,7 @@
         <v>45002</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17572,7 +17625,7 @@
         <v>45986</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17645,7 +17698,7 @@
         <v>45982</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17718,7 +17771,7 @@
         <v>45825</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17791,7 +17844,7 @@
         <v>45621</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17864,7 +17917,7 @@
         <v>45590</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17937,7 +17990,7 @@
         <v>45062</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18010,7 +18063,7 @@
         <v>45632</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18083,7 +18136,7 @@
         <v>45698</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18156,7 +18209,7 @@
         <v>45994</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18229,7 +18282,7 @@
         <v>45693</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18302,7 +18355,7 @@
         <v>45189</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18375,7 +18428,7 @@
         <v>45995</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18448,7 +18501,7 @@
         <v>45995</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18521,7 +18574,7 @@
         <v>45995</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18594,7 +18647,7 @@
         <v>45915</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18667,7 +18720,7 @@
         <v>45181</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18740,7 +18793,7 @@
         <v>45832</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18818,7 +18871,7 @@
         <v>45150</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18891,7 +18944,7 @@
         <v>45929</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18964,7 +19017,7 @@
         <v>46000</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19037,7 +19090,7 @@
         <v>44720</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19110,7 +19163,7 @@
         <v>46003</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19183,7 +19236,7 @@
         <v>46003</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19256,7 +19309,7 @@
         <v>45896</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19329,7 +19382,7 @@
         <v>45530</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19402,7 +19455,7 @@
         <v>45825</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19475,7 +19528,7 @@
         <v>45994</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19548,7 +19601,7 @@
         <v>45217</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19626,7 +19679,7 @@
         <v>45966</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19699,7 +19752,7 @@
         <v>45443</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19777,7 +19830,7 @@
         <v>45197</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19850,7 +19903,7 @@
         <v>45904</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19928,7 +19981,7 @@
         <v>45845</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20001,7 +20054,7 @@
         <v>45547</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20074,7 +20127,7 @@
         <v>45348</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20147,7 +20200,7 @@
         <v>45734</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20220,7 +20273,7 @@
         <v>45834</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20293,7 +20346,7 @@
         <v>45825</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20366,7 +20419,7 @@
         <v>45602</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20439,7 +20492,7 @@
         <v>46080</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20517,7 +20570,7 @@
         <v>45825</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20590,7 +20643,7 @@
         <v>44511</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20663,7 +20716,7 @@
         <v>45825</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20736,7 +20789,7 @@
         <v>45418</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20809,7 +20862,7 @@
         <v>45911</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20882,7 +20935,7 @@
         <v>45644</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20955,7 +21008,7 @@
         <v>45831</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21028,7 +21081,7 @@
         <v>45425</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21101,7 +21154,7 @@
         <v>46148</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21174,7 +21227,7 @@
         <v>45467</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21247,7 +21300,7 @@
         <v>46153</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21320,7 +21373,7 @@
         <v>45272</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21393,7 +21446,7 @@
         <v>46153</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21466,7 +21519,7 @@
         <v>46153</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21539,7 +21592,7 @@
         <v>44858</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21612,7 +21665,7 @@
         <v>45092</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21685,7 +21738,7 @@
         <v>46160</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21758,7 +21811,7 @@
         <v>44468</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21831,7 +21884,7 @@
         <v>45273</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21904,7 +21957,7 @@
         <v>45546</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21977,7 +22030,7 @@
         <v>45737</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22050,7 +22103,7 @@
         <v>45940</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22123,7 +22176,7 @@
         <v>45015</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22196,7 +22249,7 @@
         <v>44959</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22269,7 +22322,7 @@
         <v>44902</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22342,7 +22395,7 @@
         <v>44959</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22415,7 +22468,7 @@
         <v>45994</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22488,7 +22541,7 @@
         <v>45103</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22561,7 +22614,7 @@
         <v>45842</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22634,7 +22687,7 @@
         <v>45121</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22707,7 +22760,7 @@
         <v>44545</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22780,7 +22833,7 @@
         <v>45075</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22853,7 +22906,7 @@
         <v>46167</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22931,7 +22984,7 @@
         <v>45355</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23004,7 +23057,7 @@
         <v>45713</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23077,7 +23130,7 @@
         <v>45849</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23150,7 +23203,7 @@
         <v>45994</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23223,7 +23276,7 @@
         <v>46006</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23296,7 +23349,7 @@
         <v>44949</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23369,7 +23422,7 @@
         <v>45254</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23442,7 +23495,7 @@
         <v>44776</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23515,7 +23568,7 @@
         <v>44621</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23593,7 +23646,7 @@
         <v>44781</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23666,7 +23719,7 @@
         <v>45348</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23739,7 +23792,7 @@
         <v>46177</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23812,7 +23865,7 @@
         <v>45384</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23885,7 +23938,7 @@
         <v>45734</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23958,7 +24011,7 @@
         <v>46177</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24031,7 +24084,7 @@
         <v>46177</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24104,7 +24157,7 @@
         <v>45404</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24177,7 +24230,7 @@
         <v>45104</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24250,7 +24303,7 @@
         <v>45566</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24323,7 +24376,7 @@
         <v>44621</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24401,7 +24454,7 @@
         <v>45162</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24474,7 +24527,7 @@
         <v>46184</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24547,7 +24600,7 @@
         <v>46188</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24620,7 +24673,7 @@
         <v>45621</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24693,7 +24746,7 @@
         <v>46184</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24766,7 +24819,7 @@
         <v>45587</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24839,7 +24892,7 @@
         <v>45616</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24912,7 +24965,7 @@
         <v>46198</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24985,7 +25038,7 @@
         <v>45636</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25058,7 +25111,7 @@
         <v>46048</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25131,7 +25184,7 @@
         <v>45639</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25204,7 +25257,7 @@
         <v>45639</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25277,7 +25330,7 @@
         <v>45162</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25350,7 +25403,7 @@
         <v>45882</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25428,7 +25481,7 @@
         <v>45078</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25501,7 +25554,7 @@
         <v>44743</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25574,7 +25627,7 @@
         <v>45182</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25647,7 +25700,7 @@
         <v>45674</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25720,7 +25773,7 @@
         <v>46205</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25793,7 +25846,7 @@
         <v>44601</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25866,7 +25919,7 @@
         <v>45763</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25939,7 +25992,7 @@
         <v>44643</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26012,7 +26065,7 @@
         <v>45196</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26090,7 +26143,7 @@
         <v>45609</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26163,7 +26216,7 @@
         <v>44858</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26236,7 +26289,7 @@
         <v>44701</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26309,7 +26362,7 @@
         <v>45162</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26382,7 +26435,7 @@
         <v>46254</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26460,7 +26513,7 @@
         <v>45755</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26533,7 +26586,7 @@
         <v>45686</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26606,7 +26659,7 @@
         <v>44743</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26679,7 +26732,7 @@
         <v>45773</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26752,7 +26805,7 @@
         <v>46212</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26825,7 +26878,7 @@
         <v>44614</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26898,7 +26951,7 @@
         <v>46260</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26971,7 +27024,7 @@
         <v>44659</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27044,7 +27097,7 @@
         <v>44823</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27117,7 +27170,7 @@
         <v>45705</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27190,7 +27243,7 @@
         <v>45201</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27263,7 +27316,7 @@
         <v>46265</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27341,7 +27394,7 @@
         <v>44823</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27414,7 +27467,7 @@
         <v>46265</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27492,7 +27545,7 @@
         <v>45272</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27565,7 +27618,7 @@
         <v>44742</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27638,7 +27691,7 @@
         <v>46272</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27711,7 +27764,7 @@
         <v>46274</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27789,7 +27842,7 @@
         <v>45763</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27862,7 +27915,7 @@
         <v>45763</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27935,7 +27988,7 @@
         <v>44952</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28008,7 +28061,7 @@
         <v>44952</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28081,7 +28134,7 @@
         <v>44952</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28154,7 +28207,7 @@
         <v>45326</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28227,7 +28280,7 @@
         <v>46276</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28300,7 +28353,7 @@
         <v>45609</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28373,7 +28426,7 @@
         <v>46279</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28446,7 +28499,7 @@
         <v>44504</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28519,7 +28572,7 @@
         <v>46279</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28592,7 +28645,7 @@
         <v>45538</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28665,7 +28718,7 @@
         <v>46239</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28738,7 +28791,7 @@
         <v>45446</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28811,7 +28864,7 @@
         <v>45533</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28884,7 +28937,7 @@
         <v>44966</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28957,7 +29010,7 @@
         <v>44627</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29030,7 +29083,7 @@
         <v>46244</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29103,7 +29156,7 @@
         <v>44952</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29176,7 +29229,7 @@
         <v>45561</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29249,7 +29302,7 @@
         <v>45443</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29327,7 +29380,7 @@
         <v>44592</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29400,7 +29453,7 @@
         <v>46252</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29473,7 +29526,7 @@
         <v>45387</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29546,7 +29599,7 @@
         <v>44970</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29624,7 +29677,7 @@
         <v>45593</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29697,7 +29750,7 @@
         <v>44916</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29770,7 +29823,7 @@
         <v>44823</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29843,7 +29896,7 @@
         <v>45600</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29916,7 +29969,7 @@
         <v>45600</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29989,7 +30042,7 @@
         <v>44685</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30062,7 +30115,7 @@
         <v>45151</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30135,7 +30188,7 @@
         <v>45049</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30208,7 +30261,7 @@
         <v>44942</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30281,7 +30334,7 @@
         <v>45327</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30354,7 +30407,7 @@
         <v>45351</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30432,7 +30485,7 @@
         <v>45762</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30505,7 +30558,7 @@
         <v>45609</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30578,7 +30631,7 @@
         <v>44952</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30651,7 +30704,7 @@
         <v>44952</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30724,7 +30777,7 @@
         <v>45675</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30797,7 +30850,7 @@
         <v>45672</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30870,7 +30923,7 @@
         <v>45561</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30943,7 +30996,7 @@
         <v>45152</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31016,7 +31069,7 @@
         <v>45085</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31089,7 +31142,7 @@
         <v>45415</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31162,7 +31215,7 @@
         <v>44901</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31235,7 +31288,7 @@
         <v>45326</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31308,7 +31361,7 @@
         <v>45673</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31381,7 +31434,7 @@
         <v>45068</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31454,7 +31507,7 @@
         <v>45139</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31527,7 +31580,7 @@
         <v>45112</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31600,7 +31653,7 @@
         <v>44592</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31673,7 +31726,7 @@
         <v>44960</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31746,7 +31799,7 @@
         <v>44503</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31824,7 +31877,7 @@
         <v>45008</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31897,7 +31950,7 @@
         <v>45182</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31970,7 +32023,7 @@
         <v>45124</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32043,7 +32096,7 @@
         <v>45103</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32116,7 +32169,7 @@
         <v>45544</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32189,7 +32242,7 @@
         <v>45616</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32262,7 +32315,7 @@
         <v>44907</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32335,7 +32388,7 @@
         <v>45384</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32408,7 +32461,7 @@
         <v>45265</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32481,7 +32534,7 @@
         <v>45198</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32554,7 +32607,7 @@
         <v>44812</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32627,7 +32680,7 @@
         <v>45151</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32700,7 +32753,7 @@
         <v>45731</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32773,7 +32826,7 @@
         <v>45566</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32846,7 +32899,7 @@
         <v>45777</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32919,7 +32972,7 @@
         <v>44910</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32997,7 +33050,7 @@
         <v>45782</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33070,7 +33123,7 @@
         <v>45786</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33143,7 +33196,7 @@
         <v>45000</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33216,7 +33269,7 @@
         <v>45785</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33289,7 +33342,7 @@
         <v>45785</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33367,7 +33420,7 @@
         <v>45790</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33440,7 +33493,7 @@
         <v>45790</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33513,7 +33566,7 @@
         <v>45713</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33586,7 +33639,7 @@
         <v>45743</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33659,7 +33712,7 @@
         <v>45723</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33732,7 +33785,7 @@
         <v>45792</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33805,7 +33858,7 @@
         <v>45719</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33878,7 +33931,7 @@
         <v>45713</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33951,7 +34004,7 @@
         <v>45743</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34024,7 +34077,7 @@
         <v>44613</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34102,7 +34155,7 @@
         <v>44812</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34180,7 +34233,7 @@
         <v>45670</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34253,7 +34306,7 @@
         <v>45483</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34326,7 +34379,7 @@
         <v>45717</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>

--- a/Översikt DALS-ED.xlsx
+++ b/Översikt DALS-ED.xlsx
@@ -601,7 +601,7 @@
         <v>44601</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>45954</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
         <v>46153</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>45897</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         <v>46160</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>46160</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
         <v>45331</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
         <v>44907</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         <v>46160</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>45790</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
         <v>44833</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1990,7 +1990,7 @@
         <v>45643</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>45833</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>46160</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>46160</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         <v>44835</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
         <v>45817</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>45422</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2796,7 +2796,7 @@
         <v>44494</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>45188</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
         <v>45265</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
         <v>45151</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3248,7 +3248,7 @@
         <v>46048</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         <v>45422</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3470,7 +3470,7 @@
         <v>45569</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3576,7 +3576,7 @@
         <v>45937</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3690,7 +3690,7 @@
         <v>45572</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
         <v>45588</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3910,7 +3910,7 @@
         <v>46245</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4016,7 +4016,7 @@
         <v>46251</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
         <v>44601</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4232,7 +4232,7 @@
         <v>45281</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4342,7 +4342,7 @@
         <v>44865</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4452,7 +4452,7 @@
         <v>45120</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4557,7 +4557,7 @@
         <v>45183</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4666,7 +4666,7 @@
         <v>44952</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4771,7 +4771,7 @@
         <v>45799</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4876,7 +4876,7 @@
         <v>45803</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4985,7 +4985,7 @@
         <v>45930</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5090,7 +5090,7 @@
         <v>45402</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5195,7 +5195,7 @@
         <v>45075</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5300,7 +5300,7 @@
         <v>45475</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5405,7 +5405,7 @@
         <v>45588</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5514,7 +5514,7 @@
         <v>44818</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5624,7 +5624,7 @@
         <v>45237</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5734,7 +5734,7 @@
         <v>45014</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5839,7 +5839,7 @@
         <v>45687</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5944,7 +5944,7 @@
         <v>44781</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6017,7 +6017,7 @@
         <v>44533</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6090,7 +6090,7 @@
         <v>44536</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         <v>44615</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6236,7 +6236,7 @@
         <v>44536</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6309,7 +6309,7 @@
         <v>44588</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6382,7 +6382,7 @@
         <v>44690</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6455,7 +6455,7 @@
         <v>44487</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6528,7 +6528,7 @@
         <v>44733</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6601,7 +6601,7 @@
         <v>44781</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6674,7 +6674,7 @@
         <v>44676</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6747,7 +6747,7 @@
         <v>44578</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6820,7 +6820,7 @@
         <v>44799</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6893,7 +6893,7 @@
         <v>44705</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6966,7 +6966,7 @@
         <v>44743</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7039,7 +7039,7 @@
         <v>44615</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7112,7 +7112,7 @@
         <v>44608</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7185,7 +7185,7 @@
         <v>44823</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7258,7 +7258,7 @@
         <v>44837</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7331,7 +7331,7 @@
         <v>44657</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7409,7 +7409,7 @@
         <v>44685</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7482,7 +7482,7 @@
         <v>44685</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7555,7 +7555,7 @@
         <v>44705</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7628,7 +7628,7 @@
         <v>44705</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7701,7 +7701,7 @@
         <v>45632</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7774,7 +7774,7 @@
         <v>45348</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7847,7 +7847,7 @@
         <v>45673</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7920,7 +7920,7 @@
         <v>45103</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7993,7 +7993,7 @@
         <v>45621</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8066,7 +8066,7 @@
         <v>45118</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8139,7 +8139,7 @@
         <v>45062</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8212,7 +8212,7 @@
         <v>45196</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8290,7 +8290,7 @@
         <v>44858</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8363,7 +8363,7 @@
         <v>45182</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8436,7 +8436,7 @@
         <v>44659</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8509,7 +8509,7 @@
         <v>45189</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8582,7 +8582,7 @@
         <v>45201</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8655,7 +8655,7 @@
         <v>45590</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8728,7 +8728,7 @@
         <v>45198</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8801,7 +8801,7 @@
         <v>45384</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8874,7 +8874,7 @@
         <v>45161</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8952,7 +8952,7 @@
         <v>44901</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9025,7 +9025,7 @@
         <v>44952</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9098,7 +9098,7 @@
         <v>44895</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9171,7 +9171,7 @@
         <v>45786</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9244,7 +9244,7 @@
         <v>46000</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9317,7 +9317,7 @@
         <v>46003</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9390,7 +9390,7 @@
         <v>44659</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9463,7 +9463,7 @@
         <v>44823</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9536,7 +9536,7 @@
         <v>44823</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9609,7 +9609,7 @@
         <v>45674</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9682,7 +9682,7 @@
         <v>46003</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9755,7 +9755,7 @@
         <v>45326</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9828,7 +9828,7 @@
         <v>45773</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9901,7 +9901,7 @@
         <v>45723</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9974,7 +9974,7 @@
         <v>45887</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10047,7 +10047,7 @@
         <v>45358</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10125,7 +10125,7 @@
         <v>45743</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10198,7 +10198,7 @@
         <v>45790</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10271,7 +10271,7 @@
         <v>45790</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10344,7 +10344,7 @@
         <v>45743</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10417,7 +10417,7 @@
         <v>45719</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10490,7 +10490,7 @@
         <v>45346</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10563,7 +10563,7 @@
         <v>45384</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10636,7 +10636,7 @@
         <v>45713</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10709,7 +10709,7 @@
         <v>45895</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10782,7 +10782,7 @@
         <v>45713</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10855,7 +10855,7 @@
         <v>46031</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10928,7 +10928,7 @@
         <v>46031</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11001,7 +11001,7 @@
         <v>46028</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11074,7 +11074,7 @@
         <v>45412</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11147,7 +11147,7 @@
         <v>45833</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11220,7 +11220,7 @@
         <v>46035</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11293,7 +11293,7 @@
         <v>46035</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11366,7 +11366,7 @@
         <v>45902</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11439,7 +11439,7 @@
         <v>45902</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11512,7 +11512,7 @@
         <v>45903</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11585,7 +11585,7 @@
         <v>45151</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11658,7 +11658,7 @@
         <v>45904</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11731,7 +11731,7 @@
         <v>45904</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11804,7 +11804,7 @@
         <v>45197</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11877,7 +11877,7 @@
         <v>45792</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11950,7 +11950,7 @@
         <v>45908</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12028,7 +12028,7 @@
         <v>45646</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12101,7 +12101,7 @@
         <v>45909</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12179,7 +12179,7 @@
         <v>45908</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12257,7 +12257,7 @@
         <v>45909</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12330,7 +12330,7 @@
         <v>45796</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12403,7 +12403,7 @@
         <v>44504</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12476,7 +12476,7 @@
         <v>44895</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12554,7 +12554,7 @@
         <v>45796</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12627,7 +12627,7 @@
         <v>45671</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12700,7 +12700,7 @@
         <v>45328</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12773,7 +12773,7 @@
         <v>45666</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12846,7 +12846,7 @@
         <v>46048</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12919,7 +12919,7 @@
         <v>45798</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12992,7 +12992,7 @@
         <v>45798</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13065,7 +13065,7 @@
         <v>45803</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13138,7 +13138,7 @@
         <v>45804</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13211,7 +13211,7 @@
         <v>46055</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13284,7 +13284,7 @@
         <v>45162</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13357,7 +13357,7 @@
         <v>45922</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13430,7 +13430,7 @@
         <v>45925</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13503,7 +13503,7 @@
         <v>46056</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13576,7 +13576,7 @@
         <v>45925</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13654,7 +13654,7 @@
         <v>46056</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13727,7 +13727,7 @@
         <v>45929</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13800,7 +13800,7 @@
         <v>45929</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13873,7 +13873,7 @@
         <v>46060</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13946,7 +13946,7 @@
         <v>45002</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14019,7 +14019,7 @@
         <v>45348</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14092,7 +14092,7 @@
         <v>45932</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14165,7 +14165,7 @@
         <v>45811</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14238,7 +14238,7 @@
         <v>45544</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14311,7 +14311,7 @@
         <v>45932</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14384,7 +14384,7 @@
         <v>45470</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14457,7 +14457,7 @@
         <v>46073</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14530,7 +14530,7 @@
         <v>46073</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14603,7 +14603,7 @@
         <v>45940</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14676,7 +14676,7 @@
         <v>45418</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14749,7 +14749,7 @@
         <v>46073</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14822,7 +14822,7 @@
         <v>46073</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14895,7 +14895,7 @@
         <v>45597</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14968,7 +14968,7 @@
         <v>45946</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15041,7 +15041,7 @@
         <v>45202</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15114,7 +15114,7 @@
         <v>44545</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15187,7 +15187,7 @@
         <v>45693</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15260,7 +15260,7 @@
         <v>46080</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15338,7 +15338,7 @@
         <v>44949</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15411,7 +15411,7 @@
         <v>45951</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15489,7 +15489,7 @@
         <v>45951</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15562,7 +15562,7 @@
         <v>45951</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15640,7 +15640,7 @@
         <v>45150</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15713,7 +15713,7 @@
         <v>46083</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15786,7 +15786,7 @@
         <v>45812</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15859,7 +15859,7 @@
         <v>46087</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15932,7 +15932,7 @@
         <v>45958</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16005,7 +16005,7 @@
         <v>46093</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16078,7 +16078,7 @@
         <v>44743</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16151,7 +16151,7 @@
         <v>44942</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16224,7 +16224,7 @@
         <v>45015</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16297,7 +16297,7 @@
         <v>45973</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16370,7 +16370,7 @@
         <v>45359</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16443,7 +16443,7 @@
         <v>46100</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16516,7 +16516,7 @@
         <v>45973</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16589,7 +16589,7 @@
         <v>45974</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16662,7 +16662,7 @@
         <v>45974</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16735,7 +16735,7 @@
         <v>45974</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16808,7 +16808,7 @@
         <v>46101</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16881,7 +16881,7 @@
         <v>45974</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16959,7 +16959,7 @@
         <v>45446</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17032,7 +17032,7 @@
         <v>45978</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17105,7 +17105,7 @@
         <v>44601</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17178,7 +17178,7 @@
         <v>45978</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17251,7 +17251,7 @@
         <v>44743</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17324,7 +17324,7 @@
         <v>45981</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17397,7 +17397,7 @@
         <v>45982</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17470,7 +17470,7 @@
         <v>45068</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17543,7 +17543,7 @@
         <v>46113</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17616,7 +17616,7 @@
         <v>45986</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17689,7 +17689,7 @@
         <v>45825</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17762,7 +17762,7 @@
         <v>46113</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17835,7 +17835,7 @@
         <v>45773</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17908,7 +17908,7 @@
         <v>45825</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17981,7 +17981,7 @@
         <v>46126</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18054,7 +18054,7 @@
         <v>45995</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18127,7 +18127,7 @@
         <v>45995</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18200,7 +18200,7 @@
         <v>46126</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18273,7 +18273,7 @@
         <v>45995</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18346,7 +18346,7 @@
         <v>45994</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18419,7 +18419,7 @@
         <v>45639</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18492,7 +18492,7 @@
         <v>45639</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18565,7 +18565,7 @@
         <v>45831</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18638,7 +18638,7 @@
         <v>45440</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18711,7 +18711,7 @@
         <v>45440</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18784,7 +18784,7 @@
         <v>45257</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18857,7 +18857,7 @@
         <v>44720</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18930,7 +18930,7 @@
         <v>45845</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19003,7 +19003,7 @@
         <v>45590</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19076,7 +19076,7 @@
         <v>45915</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19149,7 +19149,7 @@
         <v>44592</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19222,7 +19222,7 @@
         <v>45896</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19295,7 +19295,7 @@
         <v>45825</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19368,7 +19368,7 @@
         <v>45698</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19441,7 +19441,7 @@
         <v>45478</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19514,7 +19514,7 @@
         <v>44823</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19587,7 +19587,7 @@
         <v>45139</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19660,7 +19660,7 @@
         <v>44970</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19738,7 +19738,7 @@
         <v>45842</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19811,7 +19811,7 @@
         <v>45547</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19884,7 +19884,7 @@
         <v>45825</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19957,7 +19957,7 @@
         <v>45632</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20030,7 +20030,7 @@
         <v>45834</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20103,7 +20103,7 @@
         <v>45966</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20176,7 +20176,7 @@
         <v>45832</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20254,7 +20254,7 @@
         <v>44901</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20327,7 +20327,7 @@
         <v>45849</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20400,7 +20400,7 @@
         <v>45265</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20473,7 +20473,7 @@
         <v>45713</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20546,7 +20546,7 @@
         <v>44952</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20619,7 +20619,7 @@
         <v>46080</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20697,7 +20697,7 @@
         <v>45705</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20770,7 +20770,7 @@
         <v>45443</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20848,7 +20848,7 @@
         <v>45246</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20921,7 +20921,7 @@
         <v>45929</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20994,7 +20994,7 @@
         <v>45602</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21067,7 +21067,7 @@
         <v>45994</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21140,7 +21140,7 @@
         <v>44958</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21213,7 +21213,7 @@
         <v>45387</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21286,7 +21286,7 @@
         <v>45037</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21359,7 +21359,7 @@
         <v>44776</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21432,7 +21432,7 @@
         <v>44952</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21505,7 +21505,7 @@
         <v>45904</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21583,7 +21583,7 @@
         <v>45825</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21656,7 +21656,7 @@
         <v>44511</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21729,7 +21729,7 @@
         <v>45734</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21802,7 +21802,7 @@
         <v>45672</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21875,7 +21875,7 @@
         <v>45911</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21948,7 +21948,7 @@
         <v>45075</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22021,7 +22021,7 @@
         <v>45734</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22094,7 +22094,7 @@
         <v>45644</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22167,7 +22167,7 @@
         <v>45008</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22240,7 +22240,7 @@
         <v>44742</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22313,7 +22313,7 @@
         <v>44942</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22386,7 +22386,7 @@
         <v>45162</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22459,7 +22459,7 @@
         <v>45272</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22532,7 +22532,7 @@
         <v>46148</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22605,7 +22605,7 @@
         <v>45085</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22678,7 +22678,7 @@
         <v>46153</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22751,7 +22751,7 @@
         <v>46153</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22824,7 +22824,7 @@
         <v>46153</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22897,7 +22897,7 @@
         <v>44907</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22970,7 +22970,7 @@
         <v>45561</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23043,7 +23043,7 @@
         <v>45428</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23116,7 +23116,7 @@
         <v>45327</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23189,7 +23189,7 @@
         <v>45546</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23262,7 +23262,7 @@
         <v>45737</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23335,7 +23335,7 @@
         <v>45994</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23408,7 +23408,7 @@
         <v>46160</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23481,7 +23481,7 @@
         <v>45940</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23554,7 +23554,7 @@
         <v>44855</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23627,7 +23627,7 @@
         <v>45393</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23700,7 +23700,7 @@
         <v>45342</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23773,7 +23773,7 @@
         <v>46167</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23851,7 +23851,7 @@
         <v>45994</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23924,7 +23924,7 @@
         <v>46006</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23997,7 +23997,7 @@
         <v>45882</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24075,7 +24075,7 @@
         <v>45883</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24148,7 +24148,7 @@
         <v>45326</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24221,7 +24221,7 @@
         <v>46177</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24294,7 +24294,7 @@
         <v>46177</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24367,7 +24367,7 @@
         <v>46177</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24440,7 +24440,7 @@
         <v>45755</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24513,7 +24513,7 @@
         <v>45566</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24586,7 +24586,7 @@
         <v>44503</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24664,7 +24664,7 @@
         <v>45561</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24737,7 +24737,7 @@
         <v>46184</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24810,7 +24810,7 @@
         <v>45624</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24883,7 +24883,7 @@
         <v>46184</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24956,7 +24956,7 @@
         <v>45279</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25034,7 +25034,7 @@
         <v>46188</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25107,7 +25107,7 @@
         <v>44621</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25185,7 +25185,7 @@
         <v>45616</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25258,7 +25258,7 @@
         <v>45351</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25336,7 +25336,7 @@
         <v>45609</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25409,7 +25409,7 @@
         <v>46048</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25482,7 +25482,7 @@
         <v>45443</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25560,7 +25560,7 @@
         <v>45121</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25633,7 +25633,7 @@
         <v>45112</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25706,7 +25706,7 @@
         <v>46198</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25779,7 +25779,7 @@
         <v>44909</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25852,7 +25852,7 @@
         <v>44648</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25925,7 +25925,7 @@
         <v>44825</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25998,7 +25998,7 @@
         <v>45588</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26071,7 +26071,7 @@
         <v>44966</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26144,7 +26144,7 @@
         <v>46205</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26217,7 +26217,7 @@
         <v>44875</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26290,7 +26290,7 @@
         <v>45078</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26363,7 +26363,7 @@
         <v>45162</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26436,7 +26436,7 @@
         <v>44781</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26509,7 +26509,7 @@
         <v>45538</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26582,7 +26582,7 @@
         <v>46212</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26655,7 +26655,7 @@
         <v>45152</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26728,7 +26728,7 @@
         <v>45621</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26801,7 +26801,7 @@
         <v>44823</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26874,7 +26874,7 @@
         <v>46260</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26947,7 +26947,7 @@
         <v>45475</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27020,7 +27020,7 @@
         <v>45636</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27093,7 +27093,7 @@
         <v>46265</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27171,7 +27171,7 @@
         <v>44592</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27244,7 +27244,7 @@
         <v>45217</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27322,7 +27322,7 @@
         <v>45762</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27395,7 +27395,7 @@
         <v>45763</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27468,7 +27468,7 @@
         <v>45763</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27541,7 +27541,7 @@
         <v>45675</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27614,7 +27614,7 @@
         <v>45104</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27687,7 +27687,7 @@
         <v>46265</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27765,7 +27765,7 @@
         <v>44643</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27838,7 +27838,7 @@
         <v>45761</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27911,7 +27911,7 @@
         <v>45624</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27984,7 +27984,7 @@
         <v>45355</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28057,7 +28057,7 @@
         <v>46272</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28130,7 +28130,7 @@
         <v>45609</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28203,7 +28203,7 @@
         <v>45609</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28276,7 +28276,7 @@
         <v>45616</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28349,7 +28349,7 @@
         <v>46274</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28427,7 +28427,7 @@
         <v>46276</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28500,7 +28500,7 @@
         <v>45412</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28573,7 +28573,7 @@
         <v>46279</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28646,7 +28646,7 @@
         <v>46279</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28719,7 +28719,7 @@
         <v>44705</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28792,7 +28792,7 @@
         <v>46239</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28865,7 +28865,7 @@
         <v>45615</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28938,7 +28938,7 @@
         <v>44600</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29016,7 +29016,7 @@
         <v>44701</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29089,7 +29089,7 @@
         <v>45425</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29162,7 +29162,7 @@
         <v>44960</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29235,7 +29235,7 @@
         <v>45467</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29308,7 +29308,7 @@
         <v>46244</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29381,7 +29381,7 @@
         <v>44614</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29454,7 +29454,7 @@
         <v>44601</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29527,7 +29527,7 @@
         <v>45531</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29600,7 +29600,7 @@
         <v>45103</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29673,7 +29673,7 @@
         <v>44952</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29746,7 +29746,7 @@
         <v>44952</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29819,7 +29819,7 @@
         <v>44952</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29892,7 +29892,7 @@
         <v>45404</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29965,7 +29965,7 @@
         <v>44952</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30038,7 +30038,7 @@
         <v>44916</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30111,7 +30111,7 @@
         <v>45182</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30184,7 +30184,7 @@
         <v>45763</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30257,7 +30257,7 @@
         <v>44952</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30330,7 +30330,7 @@
         <v>44952</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30403,7 +30403,7 @@
         <v>44959</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30476,7 +30476,7 @@
         <v>45762</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30549,7 +30549,7 @@
         <v>44902</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30622,7 +30622,7 @@
         <v>45533</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30695,7 +30695,7 @@
         <v>45587</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30768,7 +30768,7 @@
         <v>45702</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30841,7 +30841,7 @@
         <v>46293</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30914,7 +30914,7 @@
         <v>45187</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30987,7 +30987,7 @@
         <v>45686</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31060,7 +31060,7 @@
         <v>44621</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31138,7 +31138,7 @@
         <v>45150</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31211,7 +31211,7 @@
         <v>44858</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31284,7 +31284,7 @@
         <v>45119</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31357,7 +31357,7 @@
         <v>45415</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31430,7 +31430,7 @@
         <v>45162</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31503,7 +31503,7 @@
         <v>46254</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31581,7 +31581,7 @@
         <v>45047</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31654,7 +31654,7 @@
         <v>45600</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31727,7 +31727,7 @@
         <v>45600</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31800,7 +31800,7 @@
         <v>45181</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31873,7 +31873,7 @@
         <v>45217</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31951,7 +31951,7 @@
         <v>45092</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32024,7 +32024,7 @@
         <v>44959</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32097,7 +32097,7 @@
         <v>45273</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32170,7 +32170,7 @@
         <v>44685</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32243,7 +32243,7 @@
         <v>45530</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32316,7 +32316,7 @@
         <v>45595</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32389,7 +32389,7 @@
         <v>45189</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32462,7 +32462,7 @@
         <v>44902</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32535,7 +32535,7 @@
         <v>45541</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32608,7 +32608,7 @@
         <v>45151</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         <v>45006</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32754,7 +32754,7 @@
         <v>44627</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32827,7 +32827,7 @@
         <v>45603</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32900,7 +32900,7 @@
         <v>45049</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32973,7 +32973,7 @@
         <v>45254</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33046,7 +33046,7 @@
         <v>44812</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33119,7 +33119,7 @@
         <v>45400</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33192,7 +33192,7 @@
         <v>45272</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33265,7 +33265,7 @@
         <v>45124</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33338,7 +33338,7 @@
         <v>45593</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33411,7 +33411,7 @@
         <v>45566</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33484,7 +33484,7 @@
         <v>45777</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33557,7 +33557,7 @@
         <v>45731</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33630,7 +33630,7 @@
         <v>44910</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33708,7 +33708,7 @@
         <v>45782</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33781,7 +33781,7 @@
         <v>45785</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33859,7 +33859,7 @@
         <v>45785</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33932,7 +33932,7 @@
         <v>45000</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34005,7 +34005,7 @@
         <v>44812</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34083,7 +34083,7 @@
         <v>45670</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34156,7 +34156,7 @@
         <v>44613</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34234,7 +34234,7 @@
         <v>45483</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34307,7 +34307,7 @@
         <v>45717</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>

--- a/Översikt DALS-ED.xlsx
+++ b/Översikt DALS-ED.xlsx
@@ -601,7 +601,7 @@
         <v>44601</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>45954</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
         <v>46153</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>45897</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         <v>46160</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>46160</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
         <v>45331</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
         <v>44907</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         <v>46160</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>45790</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
         <v>44833</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1990,7 +1990,7 @@
         <v>45643</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>45833</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>46160</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>46160</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         <v>44835</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
         <v>45817</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>45422</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2796,7 +2796,7 @@
         <v>44494</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>45188</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
         <v>45265</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
         <v>45151</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3248,7 +3248,7 @@
         <v>46048</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         <v>45422</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3470,7 +3470,7 @@
         <v>45569</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3576,7 +3576,7 @@
         <v>45937</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3690,7 +3690,7 @@
         <v>45572</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
         <v>45588</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3910,7 +3910,7 @@
         <v>46245</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4016,7 +4016,7 @@
         <v>46251</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
         <v>44601</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4232,7 +4232,7 @@
         <v>45281</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4342,7 +4342,7 @@
         <v>44865</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4452,7 +4452,7 @@
         <v>45120</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4557,7 +4557,7 @@
         <v>45183</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4666,7 +4666,7 @@
         <v>44952</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4771,7 +4771,7 @@
         <v>45799</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4876,7 +4876,7 @@
         <v>45803</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4985,7 +4985,7 @@
         <v>45930</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5090,7 +5090,7 @@
         <v>45402</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5195,7 +5195,7 @@
         <v>45075</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5300,7 +5300,7 @@
         <v>45475</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5405,7 +5405,7 @@
         <v>45588</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5514,7 +5514,7 @@
         <v>44818</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5624,7 +5624,7 @@
         <v>45237</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5734,7 +5734,7 @@
         <v>45014</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5839,7 +5839,7 @@
         <v>45687</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5944,7 +5944,7 @@
         <v>44781</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6017,7 +6017,7 @@
         <v>44533</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6090,7 +6090,7 @@
         <v>44536</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         <v>44615</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6236,7 +6236,7 @@
         <v>44536</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6309,7 +6309,7 @@
         <v>44588</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6382,7 +6382,7 @@
         <v>44690</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6455,7 +6455,7 @@
         <v>44487</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6528,7 +6528,7 @@
         <v>44733</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6601,7 +6601,7 @@
         <v>44781</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6674,7 +6674,7 @@
         <v>44676</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6747,7 +6747,7 @@
         <v>44578</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6820,7 +6820,7 @@
         <v>44799</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6893,7 +6893,7 @@
         <v>44705</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6966,7 +6966,7 @@
         <v>44743</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7039,7 +7039,7 @@
         <v>44615</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7112,7 +7112,7 @@
         <v>44608</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7185,7 +7185,7 @@
         <v>44823</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7258,7 +7258,7 @@
         <v>44837</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7331,7 +7331,7 @@
         <v>44657</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7409,7 +7409,7 @@
         <v>44685</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7482,7 +7482,7 @@
         <v>44685</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7555,7 +7555,7 @@
         <v>44705</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7628,7 +7628,7 @@
         <v>44705</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7701,7 +7701,7 @@
         <v>45632</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7774,7 +7774,7 @@
         <v>45348</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7847,7 +7847,7 @@
         <v>45673</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7920,7 +7920,7 @@
         <v>45103</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7993,7 +7993,7 @@
         <v>45621</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8066,7 +8066,7 @@
         <v>45118</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8139,7 +8139,7 @@
         <v>45062</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8212,7 +8212,7 @@
         <v>45196</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8290,7 +8290,7 @@
         <v>44858</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8363,7 +8363,7 @@
         <v>45182</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8436,7 +8436,7 @@
         <v>44659</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8509,7 +8509,7 @@
         <v>45189</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8582,7 +8582,7 @@
         <v>45201</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8655,7 +8655,7 @@
         <v>45590</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8728,7 +8728,7 @@
         <v>45198</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8801,7 +8801,7 @@
         <v>45384</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8874,7 +8874,7 @@
         <v>45161</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8952,7 +8952,7 @@
         <v>44901</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9025,7 +9025,7 @@
         <v>44952</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9098,7 +9098,7 @@
         <v>44895</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9171,7 +9171,7 @@
         <v>45786</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9244,7 +9244,7 @@
         <v>46000</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9317,7 +9317,7 @@
         <v>46003</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9390,7 +9390,7 @@
         <v>44659</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9463,7 +9463,7 @@
         <v>44823</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9536,7 +9536,7 @@
         <v>44823</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9609,7 +9609,7 @@
         <v>45674</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9682,7 +9682,7 @@
         <v>46003</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9755,7 +9755,7 @@
         <v>45326</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9828,7 +9828,7 @@
         <v>45773</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9901,7 +9901,7 @@
         <v>45723</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9974,7 +9974,7 @@
         <v>45887</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10047,7 +10047,7 @@
         <v>45358</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10125,7 +10125,7 @@
         <v>45743</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10198,7 +10198,7 @@
         <v>45790</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10271,7 +10271,7 @@
         <v>45790</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10344,7 +10344,7 @@
         <v>45743</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10417,7 +10417,7 @@
         <v>45719</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10490,7 +10490,7 @@
         <v>45346</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10563,7 +10563,7 @@
         <v>45384</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10636,7 +10636,7 @@
         <v>45713</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10709,7 +10709,7 @@
         <v>45895</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10782,7 +10782,7 @@
         <v>45713</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10855,7 +10855,7 @@
         <v>46031</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10928,7 +10928,7 @@
         <v>46031</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11001,7 +11001,7 @@
         <v>46028</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11074,7 +11074,7 @@
         <v>45412</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11147,7 +11147,7 @@
         <v>45833</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11220,7 +11220,7 @@
         <v>46035</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11293,7 +11293,7 @@
         <v>46035</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11366,7 +11366,7 @@
         <v>45902</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11439,7 +11439,7 @@
         <v>45902</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11512,7 +11512,7 @@
         <v>45903</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11585,7 +11585,7 @@
         <v>45151</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11658,7 +11658,7 @@
         <v>45904</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11731,7 +11731,7 @@
         <v>45904</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11804,7 +11804,7 @@
         <v>45197</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11877,7 +11877,7 @@
         <v>45792</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11950,7 +11950,7 @@
         <v>45908</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12028,7 +12028,7 @@
         <v>45646</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12101,7 +12101,7 @@
         <v>45909</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12179,7 +12179,7 @@
         <v>45908</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12257,7 +12257,7 @@
         <v>45909</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12330,7 +12330,7 @@
         <v>45796</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12403,7 +12403,7 @@
         <v>44504</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12476,7 +12476,7 @@
         <v>44895</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12554,7 +12554,7 @@
         <v>45796</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12627,7 +12627,7 @@
         <v>45671</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12700,7 +12700,7 @@
         <v>45328</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12773,7 +12773,7 @@
         <v>45666</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12846,7 +12846,7 @@
         <v>46048</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12919,7 +12919,7 @@
         <v>45798</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12992,7 +12992,7 @@
         <v>45798</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13065,7 +13065,7 @@
         <v>45803</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13138,7 +13138,7 @@
         <v>45804</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13211,7 +13211,7 @@
         <v>46055</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13284,7 +13284,7 @@
         <v>45162</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13357,7 +13357,7 @@
         <v>45922</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13430,7 +13430,7 @@
         <v>45925</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13503,7 +13503,7 @@
         <v>46056</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13576,7 +13576,7 @@
         <v>45925</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13654,7 +13654,7 @@
         <v>46056</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13727,7 +13727,7 @@
         <v>45929</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13800,7 +13800,7 @@
         <v>45929</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13873,7 +13873,7 @@
         <v>46060</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13946,7 +13946,7 @@
         <v>45002</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14019,7 +14019,7 @@
         <v>45348</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14092,7 +14092,7 @@
         <v>45932</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14165,7 +14165,7 @@
         <v>45811</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14238,7 +14238,7 @@
         <v>45544</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14311,7 +14311,7 @@
         <v>45932</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14384,7 +14384,7 @@
         <v>45470</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14457,7 +14457,7 @@
         <v>46073</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14530,7 +14530,7 @@
         <v>46073</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14603,7 +14603,7 @@
         <v>45940</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14676,7 +14676,7 @@
         <v>45418</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14749,7 +14749,7 @@
         <v>46073</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14822,7 +14822,7 @@
         <v>46073</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14895,7 +14895,7 @@
         <v>45597</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14968,7 +14968,7 @@
         <v>45946</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15041,7 +15041,7 @@
         <v>45202</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15114,7 +15114,7 @@
         <v>44545</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15187,7 +15187,7 @@
         <v>45693</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15260,7 +15260,7 @@
         <v>46080</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15338,7 +15338,7 @@
         <v>44949</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15411,7 +15411,7 @@
         <v>45951</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15489,7 +15489,7 @@
         <v>45951</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15562,7 +15562,7 @@
         <v>45951</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15640,7 +15640,7 @@
         <v>45150</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15713,7 +15713,7 @@
         <v>46083</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15786,7 +15786,7 @@
         <v>45812</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15859,7 +15859,7 @@
         <v>46087</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15932,7 +15932,7 @@
         <v>45958</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16005,7 +16005,7 @@
         <v>46093</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16078,7 +16078,7 @@
         <v>44743</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16151,7 +16151,7 @@
         <v>44942</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16224,7 +16224,7 @@
         <v>45015</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16297,7 +16297,7 @@
         <v>45973</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16370,7 +16370,7 @@
         <v>45359</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16443,7 +16443,7 @@
         <v>46100</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16516,7 +16516,7 @@
         <v>45973</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16589,7 +16589,7 @@
         <v>45974</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16662,7 +16662,7 @@
         <v>45974</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16735,7 +16735,7 @@
         <v>45974</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16808,7 +16808,7 @@
         <v>46101</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16881,7 +16881,7 @@
         <v>45974</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16959,7 +16959,7 @@
         <v>45446</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17032,7 +17032,7 @@
         <v>45978</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17105,7 +17105,7 @@
         <v>44601</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17178,7 +17178,7 @@
         <v>45978</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17251,7 +17251,7 @@
         <v>44743</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17324,7 +17324,7 @@
         <v>45981</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17397,7 +17397,7 @@
         <v>45982</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17470,7 +17470,7 @@
         <v>45068</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17543,7 +17543,7 @@
         <v>46113</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17616,7 +17616,7 @@
         <v>45986</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17689,7 +17689,7 @@
         <v>45825</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17762,7 +17762,7 @@
         <v>46113</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17835,7 +17835,7 @@
         <v>45773</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17908,7 +17908,7 @@
         <v>45825</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17981,7 +17981,7 @@
         <v>46126</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18054,7 +18054,7 @@
         <v>45995</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18127,7 +18127,7 @@
         <v>45995</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18200,7 +18200,7 @@
         <v>46126</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18273,7 +18273,7 @@
         <v>45995</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18346,7 +18346,7 @@
         <v>45994</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18419,7 +18419,7 @@
         <v>45639</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18492,7 +18492,7 @@
         <v>45639</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18565,7 +18565,7 @@
         <v>45831</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18638,7 +18638,7 @@
         <v>45440</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18711,7 +18711,7 @@
         <v>45440</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18784,7 +18784,7 @@
         <v>45257</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18857,7 +18857,7 @@
         <v>44720</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18930,7 +18930,7 @@
         <v>45845</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19003,7 +19003,7 @@
         <v>45590</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19076,7 +19076,7 @@
         <v>45915</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19149,7 +19149,7 @@
         <v>44592</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19222,7 +19222,7 @@
         <v>45896</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19295,7 +19295,7 @@
         <v>45825</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19368,7 +19368,7 @@
         <v>45698</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19441,7 +19441,7 @@
         <v>45478</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19514,7 +19514,7 @@
         <v>44823</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19587,7 +19587,7 @@
         <v>45139</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19660,7 +19660,7 @@
         <v>44970</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19738,7 +19738,7 @@
         <v>45842</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19811,7 +19811,7 @@
         <v>45547</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19884,7 +19884,7 @@
         <v>45825</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19957,7 +19957,7 @@
         <v>45632</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20030,7 +20030,7 @@
         <v>45834</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20103,7 +20103,7 @@
         <v>45966</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20176,7 +20176,7 @@
         <v>45832</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20254,7 +20254,7 @@
         <v>44901</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20327,7 +20327,7 @@
         <v>45849</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20400,7 +20400,7 @@
         <v>45265</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20473,7 +20473,7 @@
         <v>45713</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20546,7 +20546,7 @@
         <v>44952</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20619,7 +20619,7 @@
         <v>46080</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20697,7 +20697,7 @@
         <v>45705</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20770,7 +20770,7 @@
         <v>45443</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20848,7 +20848,7 @@
         <v>45246</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20921,7 +20921,7 @@
         <v>45929</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20994,7 +20994,7 @@
         <v>45602</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21067,7 +21067,7 @@
         <v>45994</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21140,7 +21140,7 @@
         <v>44958</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21213,7 +21213,7 @@
         <v>45387</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21286,7 +21286,7 @@
         <v>45037</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21359,7 +21359,7 @@
         <v>44776</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21432,7 +21432,7 @@
         <v>44952</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21505,7 +21505,7 @@
         <v>45904</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21583,7 +21583,7 @@
         <v>45825</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21656,7 +21656,7 @@
         <v>44511</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21729,7 +21729,7 @@
         <v>45734</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21802,7 +21802,7 @@
         <v>45672</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21875,7 +21875,7 @@
         <v>45911</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21948,7 +21948,7 @@
         <v>45075</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22021,7 +22021,7 @@
         <v>45734</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22094,7 +22094,7 @@
         <v>45644</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22167,7 +22167,7 @@
         <v>45008</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22240,7 +22240,7 @@
         <v>44742</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22313,7 +22313,7 @@
         <v>44942</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22386,7 +22386,7 @@
         <v>45162</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22459,7 +22459,7 @@
         <v>45272</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22532,7 +22532,7 @@
         <v>46148</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22605,7 +22605,7 @@
         <v>45085</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22678,7 +22678,7 @@
         <v>46153</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22751,7 +22751,7 @@
         <v>46153</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22824,7 +22824,7 @@
         <v>46153</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22897,7 +22897,7 @@
         <v>44907</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22970,7 +22970,7 @@
         <v>45561</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23043,7 +23043,7 @@
         <v>45428</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23116,7 +23116,7 @@
         <v>45327</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23189,7 +23189,7 @@
         <v>45546</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23262,7 +23262,7 @@
         <v>45737</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23335,7 +23335,7 @@
         <v>45994</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23408,7 +23408,7 @@
         <v>46160</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23481,7 +23481,7 @@
         <v>45940</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23554,7 +23554,7 @@
         <v>44855</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23627,7 +23627,7 @@
         <v>45393</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23700,7 +23700,7 @@
         <v>45342</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23773,7 +23773,7 @@
         <v>46167</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23851,7 +23851,7 @@
         <v>45994</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23924,7 +23924,7 @@
         <v>46006</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23997,7 +23997,7 @@
         <v>45882</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24075,7 +24075,7 @@
         <v>45883</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24148,7 +24148,7 @@
         <v>45326</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24221,7 +24221,7 @@
         <v>46177</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24294,7 +24294,7 @@
         <v>46177</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24367,7 +24367,7 @@
         <v>46177</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24440,7 +24440,7 @@
         <v>45755</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24513,7 +24513,7 @@
         <v>45566</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24586,7 +24586,7 @@
         <v>44503</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24664,7 +24664,7 @@
         <v>45561</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24737,7 +24737,7 @@
         <v>46184</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24810,7 +24810,7 @@
         <v>45624</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24883,7 +24883,7 @@
         <v>46184</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24956,7 +24956,7 @@
         <v>45279</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25034,7 +25034,7 @@
         <v>46188</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25107,7 +25107,7 @@
         <v>44621</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25185,7 +25185,7 @@
         <v>45616</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25258,7 +25258,7 @@
         <v>45351</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25336,7 +25336,7 @@
         <v>45609</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25409,7 +25409,7 @@
         <v>46048</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25482,7 +25482,7 @@
         <v>45443</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25560,7 +25560,7 @@
         <v>45121</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25633,7 +25633,7 @@
         <v>45112</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25706,7 +25706,7 @@
         <v>46198</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25779,7 +25779,7 @@
         <v>44909</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25852,7 +25852,7 @@
         <v>44648</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25925,7 +25925,7 @@
         <v>44825</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25998,7 +25998,7 @@
         <v>45588</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26071,7 +26071,7 @@
         <v>44966</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26144,7 +26144,7 @@
         <v>46205</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26217,7 +26217,7 @@
         <v>44875</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26290,7 +26290,7 @@
         <v>45078</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26363,7 +26363,7 @@
         <v>45162</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26436,7 +26436,7 @@
         <v>44781</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26509,7 +26509,7 @@
         <v>45538</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26582,7 +26582,7 @@
         <v>46212</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26655,7 +26655,7 @@
         <v>45152</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26728,7 +26728,7 @@
         <v>45621</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26801,7 +26801,7 @@
         <v>44823</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26874,7 +26874,7 @@
         <v>46260</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26947,7 +26947,7 @@
         <v>45475</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27020,7 +27020,7 @@
         <v>45636</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27093,7 +27093,7 @@
         <v>46265</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27171,7 +27171,7 @@
         <v>44592</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27244,7 +27244,7 @@
         <v>45217</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27322,7 +27322,7 @@
         <v>45762</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27395,7 +27395,7 @@
         <v>45763</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27468,7 +27468,7 @@
         <v>45763</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27541,7 +27541,7 @@
         <v>45675</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27614,7 +27614,7 @@
         <v>45104</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27687,7 +27687,7 @@
         <v>46265</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27765,7 +27765,7 @@
         <v>44643</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27838,7 +27838,7 @@
         <v>45761</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27911,7 +27911,7 @@
         <v>45624</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27984,7 +27984,7 @@
         <v>45355</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28057,7 +28057,7 @@
         <v>46272</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28130,7 +28130,7 @@
         <v>45609</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28203,7 +28203,7 @@
         <v>45609</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28276,7 +28276,7 @@
         <v>45616</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28349,7 +28349,7 @@
         <v>46274</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28427,7 +28427,7 @@
         <v>46276</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28500,7 +28500,7 @@
         <v>45412</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28573,7 +28573,7 @@
         <v>46279</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28646,7 +28646,7 @@
         <v>46279</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28719,7 +28719,7 @@
         <v>44705</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28792,7 +28792,7 @@
         <v>46239</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28865,7 +28865,7 @@
         <v>45615</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28938,7 +28938,7 @@
         <v>44600</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29016,7 +29016,7 @@
         <v>44701</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29089,7 +29089,7 @@
         <v>45425</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29162,7 +29162,7 @@
         <v>44960</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29235,7 +29235,7 @@
         <v>45467</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29308,7 +29308,7 @@
         <v>46244</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29381,7 +29381,7 @@
         <v>44614</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29454,7 +29454,7 @@
         <v>44601</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29527,7 +29527,7 @@
         <v>45531</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29600,7 +29600,7 @@
         <v>45103</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29673,7 +29673,7 @@
         <v>44952</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29746,7 +29746,7 @@
         <v>44952</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29819,7 +29819,7 @@
         <v>44952</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29892,7 +29892,7 @@
         <v>45404</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29965,7 +29965,7 @@
         <v>44952</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30038,7 +30038,7 @@
         <v>44916</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30111,7 +30111,7 @@
         <v>45182</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30184,7 +30184,7 @@
         <v>45763</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30257,7 +30257,7 @@
         <v>44952</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30330,7 +30330,7 @@
         <v>44952</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30403,7 +30403,7 @@
         <v>44959</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30476,7 +30476,7 @@
         <v>45762</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30549,7 +30549,7 @@
         <v>44902</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30622,7 +30622,7 @@
         <v>45533</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30695,7 +30695,7 @@
         <v>45587</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30768,7 +30768,7 @@
         <v>45702</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30841,7 +30841,7 @@
         <v>46293</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30914,7 +30914,7 @@
         <v>45187</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30987,7 +30987,7 @@
         <v>45686</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31060,7 +31060,7 @@
         <v>44621</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31138,7 +31138,7 @@
         <v>45150</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31211,7 +31211,7 @@
         <v>44858</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31284,7 +31284,7 @@
         <v>45119</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31357,7 +31357,7 @@
         <v>45415</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31430,7 +31430,7 @@
         <v>45162</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31503,7 +31503,7 @@
         <v>46254</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31581,7 +31581,7 @@
         <v>45047</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31654,7 +31654,7 @@
         <v>45600</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31727,7 +31727,7 @@
         <v>45600</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31800,7 +31800,7 @@
         <v>45181</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31873,7 +31873,7 @@
         <v>45217</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31951,7 +31951,7 @@
         <v>45092</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32024,7 +32024,7 @@
         <v>44959</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32097,7 +32097,7 @@
         <v>45273</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32170,7 +32170,7 @@
         <v>44685</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32243,7 +32243,7 @@
         <v>45530</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32316,7 +32316,7 @@
         <v>45595</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32389,7 +32389,7 @@
         <v>45189</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32462,7 +32462,7 @@
         <v>44902</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32535,7 +32535,7 @@
         <v>45541</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32608,7 +32608,7 @@
         <v>45151</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         <v>45006</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32754,7 +32754,7 @@
         <v>44627</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32827,7 +32827,7 @@
         <v>45603</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32900,7 +32900,7 @@
         <v>45049</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32973,7 +32973,7 @@
         <v>45254</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33046,7 +33046,7 @@
         <v>44812</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33119,7 +33119,7 @@
         <v>45400</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33192,7 +33192,7 @@
         <v>45272</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33265,7 +33265,7 @@
         <v>45124</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33338,7 +33338,7 @@
         <v>45593</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33411,7 +33411,7 @@
         <v>45566</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33484,7 +33484,7 @@
         <v>45777</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33557,7 +33557,7 @@
         <v>45731</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33630,7 +33630,7 @@
         <v>44910</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33708,7 +33708,7 @@
         <v>45782</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33781,7 +33781,7 @@
         <v>45785</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33859,7 +33859,7 @@
         <v>45785</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33932,7 +33932,7 @@
         <v>45000</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34005,7 +34005,7 @@
         <v>44812</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34083,7 +34083,7 @@
         <v>45670</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34156,7 +34156,7 @@
         <v>44613</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34234,7 +34234,7 @@
         <v>45483</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34307,7 +34307,7 @@
         <v>45717</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>

--- a/Översikt DALS-ED.xlsx
+++ b/Översikt DALS-ED.xlsx
@@ -601,7 +601,7 @@
         <v>44601</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>45954</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
         <v>46153</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>45897</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         <v>46160</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>45331</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>46160</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
         <v>44907</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         <v>46160</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>44833</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
         <v>45790</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1990,7 +1990,7 @@
         <v>45643</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>45833</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>46160</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>46160</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         <v>44835</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
         <v>45422</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>45817</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2796,7 +2796,7 @@
         <v>44494</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>45188</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
         <v>45265</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
         <v>45151</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3248,7 +3248,7 @@
         <v>45422</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         <v>46048</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3470,7 +3470,7 @@
         <v>45281</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3580,7 +3580,7 @@
         <v>45588</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3690,7 +3690,7 @@
         <v>45937</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         <v>45569</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3910,7 +3910,7 @@
         <v>44601</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4016,7 +4016,7 @@
         <v>45572</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
         <v>46245</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4232,7 +4232,7 @@
         <v>46251</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4342,7 +4342,7 @@
         <v>44865</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4452,7 +4452,7 @@
         <v>45120</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4557,7 +4557,7 @@
         <v>44952</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4662,7 +4662,7 @@
         <v>45183</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4771,7 +4771,7 @@
         <v>45930</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4876,7 +4876,7 @@
         <v>45799</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4981,7 +4981,7 @@
         <v>45803</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5090,7 +5090,7 @@
         <v>45075</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5195,7 +5195,7 @@
         <v>45014</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5300,7 +5300,7 @@
         <v>44818</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5410,7 +5410,7 @@
         <v>45402</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5515,7 +5515,7 @@
         <v>45475</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5620,7 +5620,7 @@
         <v>45237</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5730,7 +5730,7 @@
         <v>45588</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5839,7 +5839,7 @@
         <v>45687</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5944,7 +5944,7 @@
         <v>44781</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6017,7 +6017,7 @@
         <v>44533</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6090,7 +6090,7 @@
         <v>44536</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         <v>44615</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6236,7 +6236,7 @@
         <v>44536</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6309,7 +6309,7 @@
         <v>44588</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6382,7 +6382,7 @@
         <v>44690</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6455,7 +6455,7 @@
         <v>44487</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6528,7 +6528,7 @@
         <v>44733</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6601,7 +6601,7 @@
         <v>44781</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6674,7 +6674,7 @@
         <v>44837</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6747,7 +6747,7 @@
         <v>44657</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         <v>44676</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6898,7 +6898,7 @@
         <v>44578</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6971,7 +6971,7 @@
         <v>44685</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7044,7 +7044,7 @@
         <v>44685</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7117,7 +7117,7 @@
         <v>44799</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7190,7 +7190,7 @@
         <v>44705</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7263,7 +7263,7 @@
         <v>44743</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7336,7 +7336,7 @@
         <v>44615</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7409,7 +7409,7 @@
         <v>44608</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7482,7 +7482,7 @@
         <v>44823</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7555,7 +7555,7 @@
         <v>44705</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7628,7 +7628,7 @@
         <v>44705</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7701,7 +7701,7 @@
         <v>45412</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7774,7 +7774,7 @@
         <v>45531</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7847,7 +7847,7 @@
         <v>45393</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7920,7 +7920,7 @@
         <v>45217</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7998,7 +7998,7 @@
         <v>45467</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8071,7 +8071,7 @@
         <v>45609</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8144,7 +8144,7 @@
         <v>45272</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8217,7 +8217,7 @@
         <v>44952</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8290,7 +8290,7 @@
         <v>44952</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8363,7 +8363,7 @@
         <v>45440</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8436,7 +8436,7 @@
         <v>45440</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8509,7 +8509,7 @@
         <v>45702</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8582,7 +8582,7 @@
         <v>45675</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8655,7 +8655,7 @@
         <v>45672</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8728,7 +8728,7 @@
         <v>45187</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8801,7 +8801,7 @@
         <v>44858</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8874,7 +8874,7 @@
         <v>45561</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8947,7 +8947,7 @@
         <v>45428</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9020,7 +9020,7 @@
         <v>45092</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9093,7 +9093,7 @@
         <v>45152</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9166,7 +9166,7 @@
         <v>45085</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9239,7 +9239,7 @@
         <v>45415</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9312,7 +9312,7 @@
         <v>45273</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9385,7 +9385,7 @@
         <v>44901</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9458,7 +9458,7 @@
         <v>45326</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         <v>44825</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9604,7 +9604,7 @@
         <v>45673</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9677,7 +9677,7 @@
         <v>45015</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9750,7 +9750,7 @@
         <v>45068</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9823,7 +9823,7 @@
         <v>44959</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9896,7 +9896,7 @@
         <v>44895</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9974,7 +9974,7 @@
         <v>45139</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10047,7 +10047,7 @@
         <v>45112</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10120,7 +10120,7 @@
         <v>44902</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10193,7 +10193,7 @@
         <v>44959</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10266,7 +10266,7 @@
         <v>44592</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10339,7 +10339,7 @@
         <v>44960</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10412,7 +10412,7 @@
         <v>45103</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10485,7 +10485,7 @@
         <v>44503</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10563,7 +10563,7 @@
         <v>45121</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10636,7 +10636,7 @@
         <v>45257</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10709,7 +10709,7 @@
         <v>44545</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10782,7 +10782,7 @@
         <v>44823</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10855,7 +10855,7 @@
         <v>45075</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10928,7 +10928,7 @@
         <v>45359</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11001,7 +11001,7 @@
         <v>45412</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11074,7 +11074,7 @@
         <v>45355</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11147,7 +11147,7 @@
         <v>44949</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11220,7 +11220,7 @@
         <v>45478</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11293,7 +11293,7 @@
         <v>45119</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11366,7 +11366,7 @@
         <v>45400</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11439,7 +11439,7 @@
         <v>45008</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11512,7 +11512,7 @@
         <v>45279</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11590,7 +11590,7 @@
         <v>45883</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11663,7 +11663,7 @@
         <v>45182</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11736,7 +11736,7 @@
         <v>45124</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11809,7 +11809,7 @@
         <v>44659</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11882,7 +11882,7 @@
         <v>45103</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11955,7 +11955,7 @@
         <v>44855</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12028,7 +12028,7 @@
         <v>45254</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12101,7 +12101,7 @@
         <v>45544</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12174,7 +12174,7 @@
         <v>44621</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12252,7 +12252,7 @@
         <v>45887</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12325,7 +12325,7 @@
         <v>44781</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12398,7 +12398,7 @@
         <v>45773</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12471,7 +12471,7 @@
         <v>44942</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12544,7 +12544,7 @@
         <v>45616</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12617,7 +12617,7 @@
         <v>45342</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12690,7 +12690,7 @@
         <v>44907</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12763,7 +12763,7 @@
         <v>45384</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12836,7 +12836,7 @@
         <v>45348</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12909,7 +12909,7 @@
         <v>44895</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12982,7 +12982,7 @@
         <v>45895</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13055,7 +13055,7 @@
         <v>45833</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13128,7 +13128,7 @@
         <v>45902</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13201,7 +13201,7 @@
         <v>45475</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13274,7 +13274,7 @@
         <v>45246</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13347,7 +13347,7 @@
         <v>45903</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13420,7 +13420,7 @@
         <v>45904</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13493,7 +13493,7 @@
         <v>44601</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13566,7 +13566,7 @@
         <v>45904</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13639,7 +13639,7 @@
         <v>45384</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13712,7 +13712,7 @@
         <v>44875</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13785,7 +13785,7 @@
         <v>45902</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13858,7 +13858,7 @@
         <v>44902</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13931,7 +13931,7 @@
         <v>44901</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14004,7 +14004,7 @@
         <v>45908</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14082,7 +14082,7 @@
         <v>45646</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14155,7 +14155,7 @@
         <v>45908</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14233,7 +14233,7 @@
         <v>44909</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14306,7 +14306,7 @@
         <v>45265</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14379,7 +14379,7 @@
         <v>45198</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14452,7 +14452,7 @@
         <v>44812</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14525,7 +14525,7 @@
         <v>45404</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14598,7 +14598,7 @@
         <v>45151</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14671,7 +14671,7 @@
         <v>45909</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14744,7 +14744,7 @@
         <v>45597</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14817,7 +14817,7 @@
         <v>44648</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14890,7 +14890,7 @@
         <v>45909</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14968,7 +14968,7 @@
         <v>45731</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15041,7 +15041,7 @@
         <v>45104</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15114,7 +15114,7 @@
         <v>45566</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15187,7 +15187,7 @@
         <v>45777</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15260,7 +15260,7 @@
         <v>45566</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15333,7 +15333,7 @@
         <v>44621</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15411,7 +15411,7 @@
         <v>45162</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15484,7 +15484,7 @@
         <v>45202</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15557,7 +15557,7 @@
         <v>44910</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15635,7 +15635,7 @@
         <v>45782</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15708,7 +15708,7 @@
         <v>45786</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15781,7 +15781,7 @@
         <v>45000</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15854,7 +15854,7 @@
         <v>45621</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15927,7 +15927,7 @@
         <v>45785</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16000,7 +16000,7 @@
         <v>45922</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16073,7 +16073,7 @@
         <v>45603</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16146,7 +16146,7 @@
         <v>45785</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16224,7 +16224,7 @@
         <v>45587</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16297,7 +16297,7 @@
         <v>44952</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16370,7 +16370,7 @@
         <v>45790</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16443,7 +16443,7 @@
         <v>44600</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16521,7 +16521,7 @@
         <v>45790</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16594,7 +16594,7 @@
         <v>45925</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16667,7 +16667,7 @@
         <v>45713</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16740,7 +16740,7 @@
         <v>45616</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16813,7 +16813,7 @@
         <v>45743</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16886,7 +16886,7 @@
         <v>45118</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16959,7 +16959,7 @@
         <v>45723</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17032,7 +17032,7 @@
         <v>45792</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17105,7 +17105,7 @@
         <v>45719</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17178,7 +17178,7 @@
         <v>45713</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17251,7 +17251,7 @@
         <v>45925</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17329,7 +17329,7 @@
         <v>45743</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17402,7 +17402,7 @@
         <v>45929</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17475,7 +17475,7 @@
         <v>45358</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17553,7 +17553,7 @@
         <v>45047</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17626,7 +17626,7 @@
         <v>45796</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17699,7 +17699,7 @@
         <v>45929</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17772,7 +17772,7 @@
         <v>45636</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17845,7 +17845,7 @@
         <v>45796</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17918,7 +17918,7 @@
         <v>45541</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17991,7 +17991,7 @@
         <v>45632</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18064,7 +18064,7 @@
         <v>44705</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18137,7 +18137,7 @@
         <v>45639</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18210,7 +18210,7 @@
         <v>45639</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18283,7 +18283,7 @@
         <v>45162</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18356,7 +18356,7 @@
         <v>45798</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18429,7 +18429,7 @@
         <v>45666</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18502,7 +18502,7 @@
         <v>45798</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18575,7 +18575,7 @@
         <v>45328</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18648,7 +18648,7 @@
         <v>45150</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18721,7 +18721,7 @@
         <v>45595</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18794,7 +18794,7 @@
         <v>45671</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18867,7 +18867,7 @@
         <v>45078</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18940,7 +18940,7 @@
         <v>45932</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19013,7 +19013,7 @@
         <v>44743</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19086,7 +19086,7 @@
         <v>45932</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19159,7 +19159,7 @@
         <v>45182</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19232,7 +19232,7 @@
         <v>45674</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19305,7 +19305,7 @@
         <v>45803</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19378,7 +19378,7 @@
         <v>45804</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19451,7 +19451,7 @@
         <v>44601</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19524,7 +19524,7 @@
         <v>45763</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19597,7 +19597,7 @@
         <v>45588</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19670,7 +19670,7 @@
         <v>45470</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19743,7 +19743,7 @@
         <v>44643</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19816,7 +19816,7 @@
         <v>45189</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19889,7 +19889,7 @@
         <v>45196</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19967,7 +19967,7 @@
         <v>45940</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20040,7 +20040,7 @@
         <v>45812</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20113,7 +20113,7 @@
         <v>45609</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20186,7 +20186,7 @@
         <v>45624</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20259,7 +20259,7 @@
         <v>45811</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20332,7 +20332,7 @@
         <v>45946</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20405,7 +20405,7 @@
         <v>45762</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20478,7 +20478,7 @@
         <v>44858</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20551,7 +20551,7 @@
         <v>44701</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20624,7 +20624,7 @@
         <v>45162</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20697,7 +20697,7 @@
         <v>45624</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20770,7 +20770,7 @@
         <v>45006</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20843,7 +20843,7 @@
         <v>45755</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20916,7 +20916,7 @@
         <v>45037</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20989,7 +20989,7 @@
         <v>45686</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21062,7 +21062,7 @@
         <v>44743</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21135,7 +21135,7 @@
         <v>45773</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21208,7 +21208,7 @@
         <v>45825</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21281,7 +21281,7 @@
         <v>44614</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21354,7 +21354,7 @@
         <v>44952</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21427,7 +21427,7 @@
         <v>45951</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21500,7 +21500,7 @@
         <v>45951</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21578,7 +21578,7 @@
         <v>45825</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21651,7 +21651,7 @@
         <v>44958</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21724,7 +21724,7 @@
         <v>44952</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21797,7 +21797,7 @@
         <v>45831</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21870,7 +21870,7 @@
         <v>45951</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21948,7 +21948,7 @@
         <v>45958</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22021,7 +22021,7 @@
         <v>45761</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22094,7 +22094,7 @@
         <v>44659</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22167,7 +22167,7 @@
         <v>44823</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22240,7 +22240,7 @@
         <v>45161</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22318,7 +22318,7 @@
         <v>45705</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22391,7 +22391,7 @@
         <v>45162</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22464,7 +22464,7 @@
         <v>45590</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22537,7 +22537,7 @@
         <v>45201</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22610,7 +22610,7 @@
         <v>45615</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22683,7 +22683,7 @@
         <v>45002</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22756,7 +22756,7 @@
         <v>45621</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22829,7 +22829,7 @@
         <v>45590</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22902,7 +22902,7 @@
         <v>45842</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22975,7 +22975,7 @@
         <v>45974</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23053,7 +23053,7 @@
         <v>44823</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23126,7 +23126,7 @@
         <v>45062</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23199,7 +23199,7 @@
         <v>45973</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23272,7 +23272,7 @@
         <v>45713</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23345,7 +23345,7 @@
         <v>45849</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23418,7 +23418,7 @@
         <v>45974</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23491,7 +23491,7 @@
         <v>45974</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23564,7 +23564,7 @@
         <v>45973</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23637,7 +23637,7 @@
         <v>45974</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23710,7 +23710,7 @@
         <v>45693</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23783,7 +23783,7 @@
         <v>45189</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23856,7 +23856,7 @@
         <v>44776</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23929,7 +23929,7 @@
         <v>45272</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24002,7 +24002,7 @@
         <v>45978</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24075,7 +24075,7 @@
         <v>45978</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24148,7 +24148,7 @@
         <v>45181</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24221,7 +24221,7 @@
         <v>44742</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24294,7 +24294,7 @@
         <v>45150</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24367,7 +24367,7 @@
         <v>45734</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24440,7 +24440,7 @@
         <v>45530</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24513,7 +24513,7 @@
         <v>45217</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24591,7 +24591,7 @@
         <v>45197</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24664,7 +24664,7 @@
         <v>45763</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24737,7 +24737,7 @@
         <v>45763</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24810,7 +24810,7 @@
         <v>44952</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24883,7 +24883,7 @@
         <v>44952</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24956,7 +24956,7 @@
         <v>44952</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25029,7 +25029,7 @@
         <v>45547</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25102,7 +25102,7 @@
         <v>45326</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25175,7 +25175,7 @@
         <v>45348</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25248,7 +25248,7 @@
         <v>45981</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25321,7 +25321,7 @@
         <v>45882</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25399,7 +25399,7 @@
         <v>45609</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25472,7 +25472,7 @@
         <v>44504</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25545,7 +25545,7 @@
         <v>46101</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25618,7 +25618,7 @@
         <v>46100</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25691,7 +25691,7 @@
         <v>45986</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25764,7 +25764,7 @@
         <v>45982</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25837,7 +25837,7 @@
         <v>45418</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25910,7 +25910,7 @@
         <v>45538</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25983,7 +25983,7 @@
         <v>45446</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26056,7 +26056,7 @@
         <v>45533</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26129,7 +26129,7 @@
         <v>45425</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26202,7 +26202,7 @@
         <v>46113</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26275,7 +26275,7 @@
         <v>46113</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26348,7 +26348,7 @@
         <v>45994</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26421,7 +26421,7 @@
         <v>44966</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26494,7 +26494,7 @@
         <v>45995</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26567,7 +26567,7 @@
         <v>45995</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26640,7 +26640,7 @@
         <v>45995</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26713,7 +26713,7 @@
         <v>44627</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26786,7 +26786,7 @@
         <v>46126</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26859,7 +26859,7 @@
         <v>46126</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26932,7 +26932,7 @@
         <v>46000</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27005,7 +27005,7 @@
         <v>44952</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27078,7 +27078,7 @@
         <v>45561</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27151,7 +27151,7 @@
         <v>45443</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27229,7 +27229,7 @@
         <v>44592</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27302,7 +27302,7 @@
         <v>46003</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27375,7 +27375,7 @@
         <v>46003</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27448,7 +27448,7 @@
         <v>45387</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27521,7 +27521,7 @@
         <v>44970</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27599,7 +27599,7 @@
         <v>45825</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27672,7 +27672,7 @@
         <v>45593</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27745,7 +27745,7 @@
         <v>44916</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27818,7 +27818,7 @@
         <v>44823</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27891,7 +27891,7 @@
         <v>45632</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27964,7 +27964,7 @@
         <v>45698</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28037,7 +28037,7 @@
         <v>45600</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28110,7 +28110,7 @@
         <v>45600</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28183,7 +28183,7 @@
         <v>45346</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28256,7 +28256,7 @@
         <v>45915</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28329,7 +28329,7 @@
         <v>44685</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28402,7 +28402,7 @@
         <v>45832</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28480,7 +28480,7 @@
         <v>46028</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28553,7 +28553,7 @@
         <v>45929</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28626,7 +28626,7 @@
         <v>44720</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28699,7 +28699,7 @@
         <v>45151</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28772,7 +28772,7 @@
         <v>45896</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28845,7 +28845,7 @@
         <v>46031</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28918,7 +28918,7 @@
         <v>46031</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28991,7 +28991,7 @@
         <v>46035</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29064,7 +29064,7 @@
         <v>46035</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29137,7 +29137,7 @@
         <v>45825</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29210,7 +29210,7 @@
         <v>45994</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29283,7 +29283,7 @@
         <v>45966</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29356,7 +29356,7 @@
         <v>45443</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29434,7 +29434,7 @@
         <v>45904</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29512,7 +29512,7 @@
         <v>45845</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29585,7 +29585,7 @@
         <v>45049</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29658,7 +29658,7 @@
         <v>45734</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29731,7 +29731,7 @@
         <v>45834</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29804,7 +29804,7 @@
         <v>45825</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29877,7 +29877,7 @@
         <v>45602</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29950,7 +29950,7 @@
         <v>46080</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30028,7 +30028,7 @@
         <v>44942</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30101,7 +30101,7 @@
         <v>45327</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30174,7 +30174,7 @@
         <v>45351</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30252,7 +30252,7 @@
         <v>46048</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30325,7 +30325,7 @@
         <v>45762</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30398,7 +30398,7 @@
         <v>44511</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30471,7 +30471,7 @@
         <v>46056</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30544,7 +30544,7 @@
         <v>46055</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30617,7 +30617,7 @@
         <v>46056</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30690,7 +30690,7 @@
         <v>45911</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30763,7 +30763,7 @@
         <v>45644</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30836,7 +30836,7 @@
         <v>46060</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30909,7 +30909,7 @@
         <v>46148</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30982,7 +30982,7 @@
         <v>46153</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31055,7 +31055,7 @@
         <v>46073</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31128,7 +31128,7 @@
         <v>46073</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31201,7 +31201,7 @@
         <v>46073</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31274,7 +31274,7 @@
         <v>46073</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31347,7 +31347,7 @@
         <v>46153</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31420,7 +31420,7 @@
         <v>46153</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31493,7 +31493,7 @@
         <v>46080</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31571,7 +31571,7 @@
         <v>46083</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31644,7 +31644,7 @@
         <v>46087</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31717,7 +31717,7 @@
         <v>46160</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31790,7 +31790,7 @@
         <v>45546</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31863,7 +31863,7 @@
         <v>45737</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31936,7 +31936,7 @@
         <v>45940</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32009,7 +32009,7 @@
         <v>46093</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32082,7 +32082,7 @@
         <v>45994</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32155,7 +32155,7 @@
         <v>46167</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32233,7 +32233,7 @@
         <v>45994</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32306,7 +32306,7 @@
         <v>46006</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32379,7 +32379,7 @@
         <v>46177</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32452,7 +32452,7 @@
         <v>46177</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32525,7 +32525,7 @@
         <v>46177</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32598,7 +32598,7 @@
         <v>46184</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32671,7 +32671,7 @@
         <v>46188</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32744,7 +32744,7 @@
         <v>46184</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32817,7 +32817,7 @@
         <v>46198</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32890,7 +32890,7 @@
         <v>46048</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32963,7 +32963,7 @@
         <v>46205</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33036,7 +33036,7 @@
         <v>46212</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33109,7 +33109,7 @@
         <v>46265</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33187,7 +33187,7 @@
         <v>46265</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33265,7 +33265,7 @@
         <v>46272</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33338,7 +33338,7 @@
         <v>46274</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33416,7 +33416,7 @@
         <v>46276</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33489,7 +33489,7 @@
         <v>46279</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33562,7 +33562,7 @@
         <v>46279</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33635,7 +33635,7 @@
         <v>46239</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33708,7 +33708,7 @@
         <v>46244</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33781,7 +33781,7 @@
         <v>46293</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33854,7 +33854,7 @@
         <v>46254</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33932,7 +33932,7 @@
         <v>46260</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34005,7 +34005,7 @@
         <v>46304</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34083,7 +34083,7 @@
         <v>44613</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34161,7 +34161,7 @@
         <v>44812</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34239,7 +34239,7 @@
         <v>45670</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34312,7 +34312,7 @@
         <v>45483</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34385,7 +34385,7 @@
         <v>45717</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>

--- a/Översikt DALS-ED.xlsx
+++ b/Översikt DALS-ED.xlsx
@@ -601,7 +601,7 @@
         <v>44601</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>45954</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
         <v>46153</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>45897</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         <v>46160</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>45331</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>46160</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
         <v>44907</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         <v>46160</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>44833</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
         <v>45790</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1990,7 +1990,7 @@
         <v>45643</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>45833</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>46160</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>46160</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         <v>44835</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
         <v>45422</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>45817</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2796,7 +2796,7 @@
         <v>44494</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>45188</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
         <v>45265</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
         <v>45151</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3248,7 +3248,7 @@
         <v>45422</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         <v>46048</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3470,7 +3470,7 @@
         <v>45281</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3580,7 +3580,7 @@
         <v>45588</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3690,7 +3690,7 @@
         <v>45937</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         <v>45569</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3910,7 +3910,7 @@
         <v>44601</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4016,7 +4016,7 @@
         <v>45572</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
         <v>46245</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4232,7 +4232,7 @@
         <v>46251</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4342,7 +4342,7 @@
         <v>44865</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4452,7 +4452,7 @@
         <v>45120</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4557,7 +4557,7 @@
         <v>44952</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4662,7 +4662,7 @@
         <v>45183</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4771,7 +4771,7 @@
         <v>45930</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4876,7 +4876,7 @@
         <v>45799</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4981,7 +4981,7 @@
         <v>45803</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5090,7 +5090,7 @@
         <v>45075</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5195,7 +5195,7 @@
         <v>45014</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5300,7 +5300,7 @@
         <v>44818</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5410,7 +5410,7 @@
         <v>45402</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5515,7 +5515,7 @@
         <v>45475</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5620,7 +5620,7 @@
         <v>45237</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5730,7 +5730,7 @@
         <v>45588</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5839,7 +5839,7 @@
         <v>45687</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5944,7 +5944,7 @@
         <v>44781</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6017,7 +6017,7 @@
         <v>44533</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6090,7 +6090,7 @@
         <v>44536</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         <v>44615</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6236,7 +6236,7 @@
         <v>44536</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6309,7 +6309,7 @@
         <v>44588</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6382,7 +6382,7 @@
         <v>44690</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6455,7 +6455,7 @@
         <v>44487</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6528,7 +6528,7 @@
         <v>44733</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6601,7 +6601,7 @@
         <v>44781</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6674,7 +6674,7 @@
         <v>44837</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6747,7 +6747,7 @@
         <v>44657</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         <v>44676</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6898,7 +6898,7 @@
         <v>44578</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6971,7 +6971,7 @@
         <v>44685</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7044,7 +7044,7 @@
         <v>44685</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7117,7 +7117,7 @@
         <v>44799</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7190,7 +7190,7 @@
         <v>44705</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7263,7 +7263,7 @@
         <v>44743</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7336,7 +7336,7 @@
         <v>44615</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7409,7 +7409,7 @@
         <v>44608</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7482,7 +7482,7 @@
         <v>44823</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7555,7 +7555,7 @@
         <v>44705</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7628,7 +7628,7 @@
         <v>44705</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7701,7 +7701,7 @@
         <v>45412</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7774,7 +7774,7 @@
         <v>45531</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7847,7 +7847,7 @@
         <v>45393</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7920,7 +7920,7 @@
         <v>45217</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7998,7 +7998,7 @@
         <v>45467</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8071,7 +8071,7 @@
         <v>45609</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8144,7 +8144,7 @@
         <v>45272</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8217,7 +8217,7 @@
         <v>44952</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8290,7 +8290,7 @@
         <v>44952</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8363,7 +8363,7 @@
         <v>45440</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8436,7 +8436,7 @@
         <v>45440</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8509,7 +8509,7 @@
         <v>45702</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8582,7 +8582,7 @@
         <v>45675</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8655,7 +8655,7 @@
         <v>45672</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8728,7 +8728,7 @@
         <v>45187</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8801,7 +8801,7 @@
         <v>44858</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8874,7 +8874,7 @@
         <v>45561</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8947,7 +8947,7 @@
         <v>45428</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9020,7 +9020,7 @@
         <v>45092</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9093,7 +9093,7 @@
         <v>45152</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9166,7 +9166,7 @@
         <v>45085</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9239,7 +9239,7 @@
         <v>45415</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9312,7 +9312,7 @@
         <v>45273</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9385,7 +9385,7 @@
         <v>44901</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9458,7 +9458,7 @@
         <v>45326</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         <v>44825</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9604,7 +9604,7 @@
         <v>45673</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9677,7 +9677,7 @@
         <v>45015</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9750,7 +9750,7 @@
         <v>45068</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9823,7 +9823,7 @@
         <v>44959</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9896,7 +9896,7 @@
         <v>44895</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9974,7 +9974,7 @@
         <v>45139</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10047,7 +10047,7 @@
         <v>45112</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10120,7 +10120,7 @@
         <v>44902</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10193,7 +10193,7 @@
         <v>44959</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10266,7 +10266,7 @@
         <v>44592</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10339,7 +10339,7 @@
         <v>44960</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10412,7 +10412,7 @@
         <v>45103</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10485,7 +10485,7 @@
         <v>44503</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10563,7 +10563,7 @@
         <v>45121</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10636,7 +10636,7 @@
         <v>45257</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10709,7 +10709,7 @@
         <v>44545</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10782,7 +10782,7 @@
         <v>44823</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10855,7 +10855,7 @@
         <v>45075</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10928,7 +10928,7 @@
         <v>45359</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11001,7 +11001,7 @@
         <v>45412</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11074,7 +11074,7 @@
         <v>45355</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11147,7 +11147,7 @@
         <v>44949</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11220,7 +11220,7 @@
         <v>45478</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11293,7 +11293,7 @@
         <v>45119</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11366,7 +11366,7 @@
         <v>45400</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11439,7 +11439,7 @@
         <v>45008</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11512,7 +11512,7 @@
         <v>45279</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11590,7 +11590,7 @@
         <v>45883</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11663,7 +11663,7 @@
         <v>45182</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11736,7 +11736,7 @@
         <v>45124</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11809,7 +11809,7 @@
         <v>44659</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11882,7 +11882,7 @@
         <v>45103</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11955,7 +11955,7 @@
         <v>44855</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12028,7 +12028,7 @@
         <v>45254</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12101,7 +12101,7 @@
         <v>45544</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12174,7 +12174,7 @@
         <v>44621</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12252,7 +12252,7 @@
         <v>45887</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12325,7 +12325,7 @@
         <v>44781</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12398,7 +12398,7 @@
         <v>45773</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12471,7 +12471,7 @@
         <v>44942</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12544,7 +12544,7 @@
         <v>45616</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12617,7 +12617,7 @@
         <v>45342</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12690,7 +12690,7 @@
         <v>44907</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12763,7 +12763,7 @@
         <v>45384</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12836,7 +12836,7 @@
         <v>45348</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12909,7 +12909,7 @@
         <v>44895</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12982,7 +12982,7 @@
         <v>45895</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13055,7 +13055,7 @@
         <v>45833</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13128,7 +13128,7 @@
         <v>45902</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13201,7 +13201,7 @@
         <v>45475</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13274,7 +13274,7 @@
         <v>45246</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13347,7 +13347,7 @@
         <v>45903</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13420,7 +13420,7 @@
         <v>45904</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13493,7 +13493,7 @@
         <v>44601</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13566,7 +13566,7 @@
         <v>45904</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13639,7 +13639,7 @@
         <v>45384</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13712,7 +13712,7 @@
         <v>44875</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13785,7 +13785,7 @@
         <v>45902</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13858,7 +13858,7 @@
         <v>44902</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13931,7 +13931,7 @@
         <v>44901</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14004,7 +14004,7 @@
         <v>45908</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14082,7 +14082,7 @@
         <v>45646</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14155,7 +14155,7 @@
         <v>45908</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14233,7 +14233,7 @@
         <v>44909</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14306,7 +14306,7 @@
         <v>45265</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14379,7 +14379,7 @@
         <v>45198</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14452,7 +14452,7 @@
         <v>44812</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14525,7 +14525,7 @@
         <v>45404</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14598,7 +14598,7 @@
         <v>45151</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14671,7 +14671,7 @@
         <v>45909</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14744,7 +14744,7 @@
         <v>45597</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14817,7 +14817,7 @@
         <v>44648</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14890,7 +14890,7 @@
         <v>45909</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14968,7 +14968,7 @@
         <v>45731</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15041,7 +15041,7 @@
         <v>45104</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15114,7 +15114,7 @@
         <v>45566</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15187,7 +15187,7 @@
         <v>45777</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15260,7 +15260,7 @@
         <v>45566</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15333,7 +15333,7 @@
         <v>44621</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15411,7 +15411,7 @@
         <v>45162</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15484,7 +15484,7 @@
         <v>45202</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15557,7 +15557,7 @@
         <v>44910</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15635,7 +15635,7 @@
         <v>45782</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15708,7 +15708,7 @@
         <v>45786</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15781,7 +15781,7 @@
         <v>45000</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15854,7 +15854,7 @@
         <v>45621</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15927,7 +15927,7 @@
         <v>45785</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16000,7 +16000,7 @@
         <v>45922</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16073,7 +16073,7 @@
         <v>45603</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16146,7 +16146,7 @@
         <v>45785</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16224,7 +16224,7 @@
         <v>45587</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16297,7 +16297,7 @@
         <v>44952</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16370,7 +16370,7 @@
         <v>45790</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16443,7 +16443,7 @@
         <v>44600</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16521,7 +16521,7 @@
         <v>45790</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16594,7 +16594,7 @@
         <v>45925</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16667,7 +16667,7 @@
         <v>45713</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16740,7 +16740,7 @@
         <v>45616</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16813,7 +16813,7 @@
         <v>45743</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16886,7 +16886,7 @@
         <v>45118</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16959,7 +16959,7 @@
         <v>45723</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17032,7 +17032,7 @@
         <v>45792</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17105,7 +17105,7 @@
         <v>45719</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17178,7 +17178,7 @@
         <v>45713</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17251,7 +17251,7 @@
         <v>45925</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17329,7 +17329,7 @@
         <v>45743</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17402,7 +17402,7 @@
         <v>45929</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17475,7 +17475,7 @@
         <v>45358</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17553,7 +17553,7 @@
         <v>45047</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17626,7 +17626,7 @@
         <v>45796</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17699,7 +17699,7 @@
         <v>45929</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17772,7 +17772,7 @@
         <v>45636</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17845,7 +17845,7 @@
         <v>45796</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17918,7 +17918,7 @@
         <v>45541</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17991,7 +17991,7 @@
         <v>45632</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18064,7 +18064,7 @@
         <v>44705</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18137,7 +18137,7 @@
         <v>45639</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18210,7 +18210,7 @@
         <v>45639</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18283,7 +18283,7 @@
         <v>45162</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18356,7 +18356,7 @@
         <v>45798</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18429,7 +18429,7 @@
         <v>45666</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18502,7 +18502,7 @@
         <v>45798</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18575,7 +18575,7 @@
         <v>45328</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18648,7 +18648,7 @@
         <v>45150</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18721,7 +18721,7 @@
         <v>45595</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18794,7 +18794,7 @@
         <v>45671</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18867,7 +18867,7 @@
         <v>45078</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18940,7 +18940,7 @@
         <v>45932</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19013,7 +19013,7 @@
         <v>44743</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19086,7 +19086,7 @@
         <v>45932</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19159,7 +19159,7 @@
         <v>45182</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19232,7 +19232,7 @@
         <v>45674</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19305,7 +19305,7 @@
         <v>45803</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19378,7 +19378,7 @@
         <v>45804</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19451,7 +19451,7 @@
         <v>44601</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19524,7 +19524,7 @@
         <v>45763</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19597,7 +19597,7 @@
         <v>45588</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19670,7 +19670,7 @@
         <v>45470</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19743,7 +19743,7 @@
         <v>44643</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19816,7 +19816,7 @@
         <v>45189</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19889,7 +19889,7 @@
         <v>45196</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19967,7 +19967,7 @@
         <v>45940</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20040,7 +20040,7 @@
         <v>45812</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20113,7 +20113,7 @@
         <v>45609</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20186,7 +20186,7 @@
         <v>45624</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20259,7 +20259,7 @@
         <v>45811</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20332,7 +20332,7 @@
         <v>45946</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20405,7 +20405,7 @@
         <v>45762</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20478,7 +20478,7 @@
         <v>44858</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20551,7 +20551,7 @@
         <v>44701</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20624,7 +20624,7 @@
         <v>45162</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20697,7 +20697,7 @@
         <v>45624</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20770,7 +20770,7 @@
         <v>45006</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20843,7 +20843,7 @@
         <v>45755</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20916,7 +20916,7 @@
         <v>45037</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20989,7 +20989,7 @@
         <v>45686</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21062,7 +21062,7 @@
         <v>44743</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21135,7 +21135,7 @@
         <v>45773</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21208,7 +21208,7 @@
         <v>45825</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21281,7 +21281,7 @@
         <v>44614</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21354,7 +21354,7 @@
         <v>44952</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21427,7 +21427,7 @@
         <v>45951</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21500,7 +21500,7 @@
         <v>45951</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21578,7 +21578,7 @@
         <v>45825</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21651,7 +21651,7 @@
         <v>44958</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21724,7 +21724,7 @@
         <v>44952</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21797,7 +21797,7 @@
         <v>45831</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21870,7 +21870,7 @@
         <v>45951</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21948,7 +21948,7 @@
         <v>45958</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22021,7 +22021,7 @@
         <v>45761</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22094,7 +22094,7 @@
         <v>44659</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22167,7 +22167,7 @@
         <v>44823</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22240,7 +22240,7 @@
         <v>45161</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22318,7 +22318,7 @@
         <v>45705</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22391,7 +22391,7 @@
         <v>45162</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22464,7 +22464,7 @@
         <v>45590</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22537,7 +22537,7 @@
         <v>45201</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22610,7 +22610,7 @@
         <v>45615</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22683,7 +22683,7 @@
         <v>45002</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22756,7 +22756,7 @@
         <v>45621</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22829,7 +22829,7 @@
         <v>45590</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22902,7 +22902,7 @@
         <v>45842</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22975,7 +22975,7 @@
         <v>45974</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23053,7 +23053,7 @@
         <v>44823</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23126,7 +23126,7 @@
         <v>45062</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23199,7 +23199,7 @@
         <v>45973</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23272,7 +23272,7 @@
         <v>45713</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23345,7 +23345,7 @@
         <v>45849</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23418,7 +23418,7 @@
         <v>45974</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23491,7 +23491,7 @@
         <v>45974</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23564,7 +23564,7 @@
         <v>45973</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23637,7 +23637,7 @@
         <v>45974</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23710,7 +23710,7 @@
         <v>45693</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23783,7 +23783,7 @@
         <v>45189</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23856,7 +23856,7 @@
         <v>44776</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23929,7 +23929,7 @@
         <v>45272</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24002,7 +24002,7 @@
         <v>45978</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24075,7 +24075,7 @@
         <v>45978</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24148,7 +24148,7 @@
         <v>45181</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24221,7 +24221,7 @@
         <v>44742</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24294,7 +24294,7 @@
         <v>45150</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24367,7 +24367,7 @@
         <v>45734</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24440,7 +24440,7 @@
         <v>45530</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24513,7 +24513,7 @@
         <v>45217</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24591,7 +24591,7 @@
         <v>45197</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24664,7 +24664,7 @@
         <v>45763</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24737,7 +24737,7 @@
         <v>45763</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24810,7 +24810,7 @@
         <v>44952</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24883,7 +24883,7 @@
         <v>44952</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24956,7 +24956,7 @@
         <v>44952</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25029,7 +25029,7 @@
         <v>45547</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25102,7 +25102,7 @@
         <v>45326</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25175,7 +25175,7 @@
         <v>45348</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25248,7 +25248,7 @@
         <v>45981</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25321,7 +25321,7 @@
         <v>45882</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25399,7 +25399,7 @@
         <v>45609</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25472,7 +25472,7 @@
         <v>44504</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25545,7 +25545,7 @@
         <v>46101</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25618,7 +25618,7 @@
         <v>46100</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25691,7 +25691,7 @@
         <v>45986</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25764,7 +25764,7 @@
         <v>45982</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25837,7 +25837,7 @@
         <v>45418</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25910,7 +25910,7 @@
         <v>45538</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25983,7 +25983,7 @@
         <v>45446</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26056,7 +26056,7 @@
         <v>45533</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26129,7 +26129,7 @@
         <v>45425</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26202,7 +26202,7 @@
         <v>46113</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26275,7 +26275,7 @@
         <v>46113</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26348,7 +26348,7 @@
         <v>45994</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26421,7 +26421,7 @@
         <v>44966</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26494,7 +26494,7 @@
         <v>45995</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26567,7 +26567,7 @@
         <v>45995</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26640,7 +26640,7 @@
         <v>45995</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26713,7 +26713,7 @@
         <v>44627</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26786,7 +26786,7 @@
         <v>46126</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26859,7 +26859,7 @@
         <v>46126</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26932,7 +26932,7 @@
         <v>46000</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27005,7 +27005,7 @@
         <v>44952</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27078,7 +27078,7 @@
         <v>45561</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27151,7 +27151,7 @@
         <v>45443</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27229,7 +27229,7 @@
         <v>44592</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27302,7 +27302,7 @@
         <v>46003</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27375,7 +27375,7 @@
         <v>46003</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27448,7 +27448,7 @@
         <v>45387</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27521,7 +27521,7 @@
         <v>44970</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27599,7 +27599,7 @@
         <v>45825</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27672,7 +27672,7 @@
         <v>45593</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27745,7 +27745,7 @@
         <v>44916</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27818,7 +27818,7 @@
         <v>44823</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27891,7 +27891,7 @@
         <v>45632</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27964,7 +27964,7 @@
         <v>45698</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28037,7 +28037,7 @@
         <v>45600</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28110,7 +28110,7 @@
         <v>45600</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28183,7 +28183,7 @@
         <v>45346</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28256,7 +28256,7 @@
         <v>45915</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28329,7 +28329,7 @@
         <v>44685</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28402,7 +28402,7 @@
         <v>45832</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28480,7 +28480,7 @@
         <v>46028</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28553,7 +28553,7 @@
         <v>45929</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28626,7 +28626,7 @@
         <v>44720</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28699,7 +28699,7 @@
         <v>45151</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28772,7 +28772,7 @@
         <v>45896</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28845,7 +28845,7 @@
         <v>46031</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28918,7 +28918,7 @@
         <v>46031</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28991,7 +28991,7 @@
         <v>46035</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29064,7 +29064,7 @@
         <v>46035</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29137,7 +29137,7 @@
         <v>45825</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29210,7 +29210,7 @@
         <v>45994</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29283,7 +29283,7 @@
         <v>45966</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29356,7 +29356,7 @@
         <v>45443</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29434,7 +29434,7 @@
         <v>45904</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29512,7 +29512,7 @@
         <v>45845</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29585,7 +29585,7 @@
         <v>45049</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29658,7 +29658,7 @@
         <v>45734</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29731,7 +29731,7 @@
         <v>45834</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29804,7 +29804,7 @@
         <v>45825</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29877,7 +29877,7 @@
         <v>45602</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29950,7 +29950,7 @@
         <v>46080</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30028,7 +30028,7 @@
         <v>44942</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30101,7 +30101,7 @@
         <v>45327</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30174,7 +30174,7 @@
         <v>45351</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30252,7 +30252,7 @@
         <v>46048</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30325,7 +30325,7 @@
         <v>45762</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30398,7 +30398,7 @@
         <v>44511</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30471,7 +30471,7 @@
         <v>46056</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30544,7 +30544,7 @@
         <v>46055</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30617,7 +30617,7 @@
         <v>46056</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30690,7 +30690,7 @@
         <v>45911</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30763,7 +30763,7 @@
         <v>45644</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30836,7 +30836,7 @@
         <v>46060</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30909,7 +30909,7 @@
         <v>46148</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30982,7 +30982,7 @@
         <v>46153</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31055,7 +31055,7 @@
         <v>46073</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31128,7 +31128,7 @@
         <v>46073</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31201,7 +31201,7 @@
         <v>46073</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31274,7 +31274,7 @@
         <v>46073</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31347,7 +31347,7 @@
         <v>46153</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31420,7 +31420,7 @@
         <v>46153</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31493,7 +31493,7 @@
         <v>46080</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31571,7 +31571,7 @@
         <v>46083</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31644,7 +31644,7 @@
         <v>46087</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31717,7 +31717,7 @@
         <v>46160</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31790,7 +31790,7 @@
         <v>45546</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31863,7 +31863,7 @@
         <v>45737</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31936,7 +31936,7 @@
         <v>45940</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32009,7 +32009,7 @@
         <v>46093</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32082,7 +32082,7 @@
         <v>45994</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32155,7 +32155,7 @@
         <v>46167</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32233,7 +32233,7 @@
         <v>45994</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32306,7 +32306,7 @@
         <v>46006</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32379,7 +32379,7 @@
         <v>46177</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32452,7 +32452,7 @@
         <v>46177</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32525,7 +32525,7 @@
         <v>46177</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32598,7 +32598,7 @@
         <v>46184</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32671,7 +32671,7 @@
         <v>46188</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32744,7 +32744,7 @@
         <v>46184</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32817,7 +32817,7 @@
         <v>46198</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32890,7 +32890,7 @@
         <v>46048</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32963,7 +32963,7 @@
         <v>46205</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33036,7 +33036,7 @@
         <v>46212</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33109,7 +33109,7 @@
         <v>46265</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33187,7 +33187,7 @@
         <v>46265</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33265,7 +33265,7 @@
         <v>46272</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33338,7 +33338,7 @@
         <v>46274</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33416,7 +33416,7 @@
         <v>46276</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33489,7 +33489,7 @@
         <v>46279</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33562,7 +33562,7 @@
         <v>46279</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33635,7 +33635,7 @@
         <v>46239</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33708,7 +33708,7 @@
         <v>46244</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33781,7 +33781,7 @@
         <v>46293</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33854,7 +33854,7 @@
         <v>46254</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33932,7 +33932,7 @@
         <v>46260</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34005,7 +34005,7 @@
         <v>46304</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34083,7 +34083,7 @@
         <v>44613</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34161,7 +34161,7 @@
         <v>44812</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34239,7 +34239,7 @@
         <v>45670</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34312,7 +34312,7 @@
         <v>45483</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34385,7 +34385,7 @@
         <v>45717</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>

--- a/Översikt DALS-ED.xlsx
+++ b/Översikt DALS-ED.xlsx
@@ -601,7 +601,7 @@
         <v>44601</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>45954</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
         <v>46153</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>45897</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>46160</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>46160</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>45331</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1517,7 +1517,7 @@
         <v>44907</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>46160</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>44833</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         <v>45643</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
         <v>45790</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         <v>45833</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         <v>46160</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2339,7 +2339,7 @@
         <v>46160</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         <v>44835</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
         <v>45817</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         <v>45422</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2797,7 +2797,7 @@
         <v>44494</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2907,7 +2907,7 @@
         <v>45188</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3021,7 +3021,7 @@
         <v>45265</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3134,7 +3134,7 @@
         <v>45151</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3249,7 +3249,7 @@
         <v>46048</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3360,7 +3360,7 @@
         <v>45422</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3471,7 +3471,7 @@
         <v>45569</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3577,7 +3577,7 @@
         <v>45937</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
         <v>45588</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3801,7 +3801,7 @@
         <v>46245</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         <v>44601</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4013,7 +4013,7 @@
         <v>46251</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
         <v>45281</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4233,7 +4233,7 @@
         <v>45572</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4343,7 +4343,7 @@
         <v>44865</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4453,7 +4453,7 @@
         <v>45120</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4558,7 +4558,7 @@
         <v>44952</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4663,7 +4663,7 @@
         <v>45402</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4768,7 +4768,7 @@
         <v>45588</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4877,7 +4877,7 @@
         <v>45075</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4982,7 +4982,7 @@
         <v>45930</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5087,7 +5087,7 @@
         <v>44818</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5197,7 +5197,7 @@
         <v>45237</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5307,7 +5307,7 @@
         <v>45475</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5412,7 +5412,7 @@
         <v>45014</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5517,7 +5517,7 @@
         <v>45183</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5626,7 +5626,7 @@
         <v>45799</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5731,7 +5731,7 @@
         <v>45803</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5840,7 +5840,7 @@
         <v>45687</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5945,7 +5945,7 @@
         <v>44781</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6018,7 +6018,7 @@
         <v>44533</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6091,7 +6091,7 @@
         <v>44536</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6164,7 +6164,7 @@
         <v>44615</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6237,7 +6237,7 @@
         <v>44536</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6310,7 +6310,7 @@
         <v>44588</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6383,7 +6383,7 @@
         <v>44690</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6456,7 +6456,7 @@
         <v>44487</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6529,7 +6529,7 @@
         <v>44733</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6602,7 +6602,7 @@
         <v>44781</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6675,7 +6675,7 @@
         <v>44676</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6748,7 +6748,7 @@
         <v>44578</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6821,7 +6821,7 @@
         <v>44799</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6894,7 +6894,7 @@
         <v>44705</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6967,7 +6967,7 @@
         <v>44743</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7040,7 +7040,7 @@
         <v>44615</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7113,7 +7113,7 @@
         <v>44608</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
         <v>44823</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7259,7 +7259,7 @@
         <v>44837</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7332,7 +7332,7 @@
         <v>44657</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7410,7 +7410,7 @@
         <v>44685</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7483,7 +7483,7 @@
         <v>44685</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7556,7 +7556,7 @@
         <v>44705</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7629,7 +7629,7 @@
         <v>44705</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
         <v>45673</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7775,7 +7775,7 @@
         <v>45632</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7848,7 +7848,7 @@
         <v>45103</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7921,7 +7921,7 @@
         <v>45348</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7994,7 +7994,7 @@
         <v>45118</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8067,7 +8067,7 @@
         <v>45196</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8145,7 +8145,7 @@
         <v>44858</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8218,7 +8218,7 @@
         <v>45062</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8291,7 +8291,7 @@
         <v>45621</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8364,7 +8364,7 @@
         <v>44659</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8437,7 +8437,7 @@
         <v>45182</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8510,7 +8510,7 @@
         <v>45189</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8583,7 +8583,7 @@
         <v>45201</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8656,7 +8656,7 @@
         <v>44895</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8729,7 +8729,7 @@
         <v>45590</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8802,7 +8802,7 @@
         <v>45198</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         <v>45161</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8953,7 +8953,7 @@
         <v>45384</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9026,7 +9026,7 @@
         <v>44952</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9099,7 +9099,7 @@
         <v>44823</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9172,7 +9172,7 @@
         <v>44823</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9245,7 +9245,7 @@
         <v>44901</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9318,7 +9318,7 @@
         <v>45674</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9391,7 +9391,7 @@
         <v>45326</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9464,7 +9464,7 @@
         <v>45358</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9542,7 +9542,7 @@
         <v>45384</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9615,7 +9615,7 @@
         <v>45412</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9688,7 +9688,7 @@
         <v>45151</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9761,7 +9761,7 @@
         <v>45197</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9834,7 +9834,7 @@
         <v>44895</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9912,7 +9912,7 @@
         <v>44504</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9985,7 +9985,7 @@
         <v>45162</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10058,7 +10058,7 @@
         <v>45544</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10131,7 +10131,7 @@
         <v>45418</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10204,7 +10204,7 @@
         <v>45597</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10277,7 +10277,7 @@
         <v>45693</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10350,7 +10350,7 @@
         <v>45150</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10423,7 +10423,7 @@
         <v>45202</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10496,7 +10496,7 @@
         <v>44545</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10569,7 +10569,7 @@
         <v>45002</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10642,7 +10642,7 @@
         <v>44949</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10715,7 +10715,7 @@
         <v>44743</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10788,7 +10788,7 @@
         <v>44942</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10861,7 +10861,7 @@
         <v>45015</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10934,7 +10934,7 @@
         <v>45359</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11007,7 +11007,7 @@
         <v>45446</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11080,7 +11080,7 @@
         <v>44601</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11153,7 +11153,7 @@
         <v>44743</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11226,7 +11226,7 @@
         <v>45068</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11299,7 +11299,7 @@
         <v>45348</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11372,7 +11372,7 @@
         <v>45773</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11445,7 +11445,7 @@
         <v>45825</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11518,7 +11518,7 @@
         <v>45887</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11591,7 +11591,7 @@
         <v>45632</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11664,7 +11664,7 @@
         <v>45834</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11737,7 +11737,7 @@
         <v>45966</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11810,7 +11810,7 @@
         <v>45832</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11888,7 +11888,7 @@
         <v>45773</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11961,7 +11961,7 @@
         <v>46080</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12039,7 +12039,7 @@
         <v>45443</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12117,7 +12117,7 @@
         <v>45929</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12190,7 +12190,7 @@
         <v>45602</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12263,7 +12263,7 @@
         <v>45895</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12336,7 +12336,7 @@
         <v>45639</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12409,7 +12409,7 @@
         <v>45639</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12482,7 +12482,7 @@
         <v>45994</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12555,7 +12555,7 @@
         <v>45440</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12628,7 +12628,7 @@
         <v>45440</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12701,7 +12701,7 @@
         <v>44659</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12774,7 +12774,7 @@
         <v>45904</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12852,7 +12852,7 @@
         <v>45825</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12925,7 +12925,7 @@
         <v>44511</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12998,7 +12998,7 @@
         <v>45734</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13071,7 +13071,7 @@
         <v>45833</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13144,7 +13144,7 @@
         <v>45257</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13217,7 +13217,7 @@
         <v>45911</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13290,7 +13290,7 @@
         <v>45644</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13363,7 +13363,7 @@
         <v>45902</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13436,7 +13436,7 @@
         <v>45902</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13509,7 +13509,7 @@
         <v>45903</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13582,7 +13582,7 @@
         <v>45904</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13655,7 +13655,7 @@
         <v>45904</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13728,7 +13728,7 @@
         <v>45590</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13801,7 +13801,7 @@
         <v>45908</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13879,7 +13879,7 @@
         <v>44592</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13952,7 +13952,7 @@
         <v>45646</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14025,7 +14025,7 @@
         <v>45909</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14103,7 +14103,7 @@
         <v>45908</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14181,7 +14181,7 @@
         <v>45909</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14254,7 +14254,7 @@
         <v>45478</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14327,7 +14327,7 @@
         <v>44823</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14400,7 +14400,7 @@
         <v>45139</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14473,7 +14473,7 @@
         <v>44970</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14551,7 +14551,7 @@
         <v>45547</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14624,7 +14624,7 @@
         <v>44901</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14697,7 +14697,7 @@
         <v>45922</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14770,7 +14770,7 @@
         <v>45265</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14843,7 +14843,7 @@
         <v>44952</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14916,7 +14916,7 @@
         <v>45925</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14989,7 +14989,7 @@
         <v>45705</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15062,7 +15062,7 @@
         <v>46148</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15135,7 +15135,7 @@
         <v>45925</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15213,7 +15213,7 @@
         <v>45929</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15286,7 +15286,7 @@
         <v>45929</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15359,7 +15359,7 @@
         <v>45246</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15432,7 +15432,7 @@
         <v>45932</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15505,7 +15505,7 @@
         <v>45932</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15578,7 +15578,7 @@
         <v>46153</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15651,7 +15651,7 @@
         <v>46153</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15724,7 +15724,7 @@
         <v>46153</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15797,7 +15797,7 @@
         <v>45940</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15870,7 +15870,7 @@
         <v>44958</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15943,7 +15943,7 @@
         <v>45387</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16016,7 +16016,7 @@
         <v>45037</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16089,7 +16089,7 @@
         <v>44952</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16162,7 +16162,7 @@
         <v>45946</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16235,7 +16235,7 @@
         <v>45951</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16313,7 +16313,7 @@
         <v>45951</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16386,7 +16386,7 @@
         <v>45951</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16464,7 +16464,7 @@
         <v>45672</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16537,7 +16537,7 @@
         <v>45958</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16610,7 +16610,7 @@
         <v>45546</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16683,7 +16683,7 @@
         <v>45075</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16756,7 +16756,7 @@
         <v>45737</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16829,7 +16829,7 @@
         <v>45008</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16902,7 +16902,7 @@
         <v>44742</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16975,7 +16975,7 @@
         <v>45994</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17048,7 +17048,7 @@
         <v>46160</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17121,7 +17121,7 @@
         <v>44942</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17194,7 +17194,7 @@
         <v>45940</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17267,7 +17267,7 @@
         <v>45973</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17340,7 +17340,7 @@
         <v>45973</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17413,7 +17413,7 @@
         <v>45162</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17486,7 +17486,7 @@
         <v>45974</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17559,7 +17559,7 @@
         <v>45974</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17632,7 +17632,7 @@
         <v>45974</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17705,7 +17705,7 @@
         <v>45974</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17783,7 +17783,7 @@
         <v>45272</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17856,7 +17856,7 @@
         <v>45978</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17929,7 +17929,7 @@
         <v>45085</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18002,7 +18002,7 @@
         <v>45978</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18075,7 +18075,7 @@
         <v>45981</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18148,7 +18148,7 @@
         <v>46167</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18226,7 +18226,7 @@
         <v>45994</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18299,7 +18299,7 @@
         <v>44907</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18372,7 +18372,7 @@
         <v>45982</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18445,7 +18445,7 @@
         <v>45561</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18518,7 +18518,7 @@
         <v>45428</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18591,7 +18591,7 @@
         <v>45986</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18664,7 +18664,7 @@
         <v>45327</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18737,7 +18737,7 @@
         <v>45995</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18810,7 +18810,7 @@
         <v>45995</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18883,7 +18883,7 @@
         <v>45995</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18956,7 +18956,7 @@
         <v>44855</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19029,7 +19029,7 @@
         <v>45994</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19102,7 +19102,7 @@
         <v>45393</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19175,7 +19175,7 @@
         <v>45342</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19248,7 +19248,7 @@
         <v>46006</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19321,7 +19321,7 @@
         <v>46000</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19394,7 +19394,7 @@
         <v>46003</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19467,7 +19467,7 @@
         <v>46003</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19540,7 +19540,7 @@
         <v>45326</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19613,7 +19613,7 @@
         <v>45346</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19686,7 +19686,7 @@
         <v>45755</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19759,7 +19759,7 @@
         <v>45566</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19832,7 +19832,7 @@
         <v>46031</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19905,7 +19905,7 @@
         <v>46031</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19978,7 +19978,7 @@
         <v>46028</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20051,7 +20051,7 @@
         <v>44503</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20129,7 +20129,7 @@
         <v>45561</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20202,7 +20202,7 @@
         <v>45624</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20275,7 +20275,7 @@
         <v>46035</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20348,7 +20348,7 @@
         <v>45279</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20426,7 +20426,7 @@
         <v>46035</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20499,7 +20499,7 @@
         <v>46177</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20572,7 +20572,7 @@
         <v>46177</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20645,7 +20645,7 @@
         <v>46177</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20718,7 +20718,7 @@
         <v>44621</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20796,7 +20796,7 @@
         <v>45616</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20869,7 +20869,7 @@
         <v>46048</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20942,7 +20942,7 @@
         <v>45351</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21020,7 +21020,7 @@
         <v>46055</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21093,7 +21093,7 @@
         <v>46056</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21166,7 +21166,7 @@
         <v>45609</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21239,7 +21239,7 @@
         <v>46056</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21312,7 +21312,7 @@
         <v>45443</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21390,7 +21390,7 @@
         <v>46060</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21463,7 +21463,7 @@
         <v>45121</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21536,7 +21536,7 @@
         <v>45112</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21609,7 +21609,7 @@
         <v>46184</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21682,7 +21682,7 @@
         <v>46184</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21755,7 +21755,7 @@
         <v>44909</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21828,7 +21828,7 @@
         <v>44648</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21901,7 +21901,7 @@
         <v>44825</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21974,7 +21974,7 @@
         <v>45588</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22047,7 +22047,7 @@
         <v>46073</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22120,7 +22120,7 @@
         <v>46073</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22193,7 +22193,7 @@
         <v>46073</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22266,7 +22266,7 @@
         <v>46073</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22339,7 +22339,7 @@
         <v>44966</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22412,7 +22412,7 @@
         <v>46188</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22485,7 +22485,7 @@
         <v>46080</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22563,7 +22563,7 @@
         <v>46083</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22636,7 +22636,7 @@
         <v>44875</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22709,7 +22709,7 @@
         <v>45078</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22782,7 +22782,7 @@
         <v>45162</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22855,7 +22855,7 @@
         <v>46087</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22928,7 +22928,7 @@
         <v>44781</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23001,7 +23001,7 @@
         <v>45538</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23074,7 +23074,7 @@
         <v>46093</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23147,7 +23147,7 @@
         <v>45152</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23220,7 +23220,7 @@
         <v>45621</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23293,7 +23293,7 @@
         <v>44823</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23366,7 +23366,7 @@
         <v>46100</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23439,7 +23439,7 @@
         <v>46101</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23512,7 +23512,7 @@
         <v>45475</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23585,7 +23585,7 @@
         <v>45636</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23658,7 +23658,7 @@
         <v>44592</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23731,7 +23731,7 @@
         <v>45217</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23809,7 +23809,7 @@
         <v>46048</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23882,7 +23882,7 @@
         <v>45762</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23955,7 +23955,7 @@
         <v>45763</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24028,7 +24028,7 @@
         <v>45763</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24101,7 +24101,7 @@
         <v>45675</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24174,7 +24174,7 @@
         <v>46198</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24247,7 +24247,7 @@
         <v>46113</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24320,7 +24320,7 @@
         <v>45104</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24393,7 +24393,7 @@
         <v>46113</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24466,7 +24466,7 @@
         <v>44643</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24539,7 +24539,7 @@
         <v>45761</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24612,7 +24612,7 @@
         <v>46126</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24685,7 +24685,7 @@
         <v>46126</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24758,7 +24758,7 @@
         <v>45624</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24831,7 +24831,7 @@
         <v>45355</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24904,7 +24904,7 @@
         <v>45609</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24977,7 +24977,7 @@
         <v>45609</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25050,7 +25050,7 @@
         <v>45616</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25123,7 +25123,7 @@
         <v>44720</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25196,7 +25196,7 @@
         <v>45845</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25269,7 +25269,7 @@
         <v>45412</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25342,7 +25342,7 @@
         <v>45915</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25415,7 +25415,7 @@
         <v>45896</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25488,7 +25488,7 @@
         <v>45825</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25561,7 +25561,7 @@
         <v>46205</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25634,7 +25634,7 @@
         <v>45698</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25707,7 +25707,7 @@
         <v>44705</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25780,7 +25780,7 @@
         <v>45615</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25853,7 +25853,7 @@
         <v>44600</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25931,7 +25931,7 @@
         <v>44701</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26004,7 +26004,7 @@
         <v>45425</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26077,7 +26077,7 @@
         <v>46212</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26150,7 +26150,7 @@
         <v>44960</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26223,7 +26223,7 @@
         <v>45467</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26296,7 +26296,7 @@
         <v>44614</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26369,7 +26369,7 @@
         <v>44601</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26442,7 +26442,7 @@
         <v>45531</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26515,7 +26515,7 @@
         <v>45103</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26588,7 +26588,7 @@
         <v>44952</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26661,7 +26661,7 @@
         <v>44952</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26734,7 +26734,7 @@
         <v>44952</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26807,7 +26807,7 @@
         <v>45404</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26880,7 +26880,7 @@
         <v>44952</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26953,7 +26953,7 @@
         <v>44916</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27026,7 +27026,7 @@
         <v>45182</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27099,7 +27099,7 @@
         <v>45763</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27172,7 +27172,7 @@
         <v>44952</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27245,7 +27245,7 @@
         <v>44952</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27318,7 +27318,7 @@
         <v>46272</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27391,7 +27391,7 @@
         <v>44959</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27464,7 +27464,7 @@
         <v>45762</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27537,7 +27537,7 @@
         <v>44902</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27610,7 +27610,7 @@
         <v>46274</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27688,7 +27688,7 @@
         <v>45533</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27761,7 +27761,7 @@
         <v>45587</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27834,7 +27834,7 @@
         <v>45702</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27907,7 +27907,7 @@
         <v>45187</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27980,7 +27980,7 @@
         <v>45686</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28053,7 +28053,7 @@
         <v>44621</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28131,7 +28131,7 @@
         <v>45150</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28204,7 +28204,7 @@
         <v>44858</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28277,7 +28277,7 @@
         <v>45119</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28350,7 +28350,7 @@
         <v>46276</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28423,7 +28423,7 @@
         <v>45415</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28496,7 +28496,7 @@
         <v>46279</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28569,7 +28569,7 @@
         <v>46279</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28642,7 +28642,7 @@
         <v>46239</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28715,7 +28715,7 @@
         <v>45162</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28788,7 +28788,7 @@
         <v>45047</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28861,7 +28861,7 @@
         <v>45600</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28934,7 +28934,7 @@
         <v>45600</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29007,7 +29007,7 @@
         <v>45181</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29080,7 +29080,7 @@
         <v>45217</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29158,7 +29158,7 @@
         <v>45092</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29231,7 +29231,7 @@
         <v>46244</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29304,7 +29304,7 @@
         <v>44959</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29377,7 +29377,7 @@
         <v>45273</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29450,7 +29450,7 @@
         <v>44685</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29523,7 +29523,7 @@
         <v>45530</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29596,7 +29596,7 @@
         <v>45595</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29669,7 +29669,7 @@
         <v>45189</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29742,7 +29742,7 @@
         <v>44902</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29815,7 +29815,7 @@
         <v>45541</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29888,7 +29888,7 @@
         <v>46293</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29961,7 +29961,7 @@
         <v>45151</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30034,7 +30034,7 @@
         <v>45006</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30107,7 +30107,7 @@
         <v>44627</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30180,7 +30180,7 @@
         <v>45603</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30253,7 +30253,7 @@
         <v>45049</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30326,7 +30326,7 @@
         <v>45254</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30399,7 +30399,7 @@
         <v>44812</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30472,7 +30472,7 @@
         <v>45400</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30545,7 +30545,7 @@
         <v>45272</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30618,7 +30618,7 @@
         <v>45124</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30691,7 +30691,7 @@
         <v>45593</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30764,7 +30764,7 @@
         <v>46254</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30842,7 +30842,7 @@
         <v>45566</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30915,7 +30915,7 @@
         <v>45777</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30988,7 +30988,7 @@
         <v>45731</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31061,7 +31061,7 @@
         <v>44910</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31139,7 +31139,7 @@
         <v>45782</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31212,7 +31212,7 @@
         <v>45785</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31290,7 +31290,7 @@
         <v>45785</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31363,7 +31363,7 @@
         <v>45000</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31436,7 +31436,7 @@
         <v>45786</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31509,7 +31509,7 @@
         <v>46260</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31582,7 +31582,7 @@
         <v>45723</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31655,7 +31655,7 @@
         <v>45743</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31728,7 +31728,7 @@
         <v>45790</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31801,7 +31801,7 @@
         <v>45790</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31874,7 +31874,7 @@
         <v>45743</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31947,7 +31947,7 @@
         <v>45719</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32020,7 +32020,7 @@
         <v>45713</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32093,7 +32093,7 @@
         <v>45713</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32166,7 +32166,7 @@
         <v>45792</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32239,7 +32239,7 @@
         <v>45796</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32312,7 +32312,7 @@
         <v>46265</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32390,7 +32390,7 @@
         <v>45796</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32463,7 +32463,7 @@
         <v>46304</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32541,7 +32541,7 @@
         <v>45671</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32614,7 +32614,7 @@
         <v>45328</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32687,7 +32687,7 @@
         <v>45666</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32760,7 +32760,7 @@
         <v>45798</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32833,7 +32833,7 @@
         <v>46265</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32911,7 +32911,7 @@
         <v>45798</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32984,7 +32984,7 @@
         <v>46309</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33062,7 +33062,7 @@
         <v>45803</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33135,7 +33135,7 @@
         <v>45804</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33208,7 +33208,7 @@
         <v>45811</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33281,7 +33281,7 @@
         <v>45470</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33354,7 +33354,7 @@
         <v>45812</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33427,7 +33427,7 @@
         <v>45825</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33500,7 +33500,7 @@
         <v>45825</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33573,7 +33573,7 @@
         <v>45831</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33646,7 +33646,7 @@
         <v>45842</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33719,7 +33719,7 @@
         <v>45849</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33792,7 +33792,7 @@
         <v>45713</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33865,7 +33865,7 @@
         <v>44776</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33938,7 +33938,7 @@
         <v>45734</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34011,7 +34011,7 @@
         <v>45882</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34089,7 +34089,7 @@
         <v>45883</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34162,7 +34162,7 @@
         <v>44812</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34240,7 +34240,7 @@
         <v>45670</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34313,7 +34313,7 @@
         <v>44613</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34391,7 +34391,7 @@
         <v>45483</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34464,7 +34464,7 @@
         <v>45717</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>

--- a/Översikt DALS-ED.xlsx
+++ b/Översikt DALS-ED.xlsx
@@ -601,7 +601,7 @@
         <v>44601</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>45954</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
         <v>46153</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>45897</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>46160</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>46160</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>45331</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1517,7 +1517,7 @@
         <v>44907</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>46160</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>44833</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         <v>45643</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
         <v>45790</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         <v>45833</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         <v>46160</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2339,7 +2339,7 @@
         <v>46160</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         <v>44835</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
         <v>45817</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         <v>45422</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2797,7 +2797,7 @@
         <v>44494</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2907,7 +2907,7 @@
         <v>45188</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3021,7 +3021,7 @@
         <v>45265</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3134,7 +3134,7 @@
         <v>45151</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3249,7 +3249,7 @@
         <v>46048</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3360,7 +3360,7 @@
         <v>45422</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3471,7 +3471,7 @@
         <v>45569</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3577,7 +3577,7 @@
         <v>45937</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
         <v>45588</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3801,7 +3801,7 @@
         <v>46245</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         <v>44601</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4013,7 +4013,7 @@
         <v>46251</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
         <v>45281</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4233,7 +4233,7 @@
         <v>45572</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4343,7 +4343,7 @@
         <v>44865</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4453,7 +4453,7 @@
         <v>45120</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4558,7 +4558,7 @@
         <v>44952</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4663,7 +4663,7 @@
         <v>45402</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4768,7 +4768,7 @@
         <v>45588</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4877,7 +4877,7 @@
         <v>45075</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4982,7 +4982,7 @@
         <v>45930</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5087,7 +5087,7 @@
         <v>44818</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5197,7 +5197,7 @@
         <v>45237</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5307,7 +5307,7 @@
         <v>45475</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5412,7 +5412,7 @@
         <v>45014</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5517,7 +5517,7 @@
         <v>45183</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5626,7 +5626,7 @@
         <v>45799</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5731,7 +5731,7 @@
         <v>45803</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5840,7 +5840,7 @@
         <v>45687</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5945,7 +5945,7 @@
         <v>44781</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6018,7 +6018,7 @@
         <v>44533</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6091,7 +6091,7 @@
         <v>44536</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6164,7 +6164,7 @@
         <v>44615</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6237,7 +6237,7 @@
         <v>44536</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6310,7 +6310,7 @@
         <v>44588</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6383,7 +6383,7 @@
         <v>44690</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6456,7 +6456,7 @@
         <v>44487</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6529,7 +6529,7 @@
         <v>44733</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6602,7 +6602,7 @@
         <v>44781</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6675,7 +6675,7 @@
         <v>44676</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6748,7 +6748,7 @@
         <v>44578</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6821,7 +6821,7 @@
         <v>44799</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6894,7 +6894,7 @@
         <v>44705</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6967,7 +6967,7 @@
         <v>44743</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7040,7 +7040,7 @@
         <v>44615</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7113,7 +7113,7 @@
         <v>44608</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
         <v>44823</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7259,7 +7259,7 @@
         <v>44837</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7332,7 +7332,7 @@
         <v>44657</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7410,7 +7410,7 @@
         <v>44685</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7483,7 +7483,7 @@
         <v>44685</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7556,7 +7556,7 @@
         <v>44705</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7629,7 +7629,7 @@
         <v>44705</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
         <v>45673</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7775,7 +7775,7 @@
         <v>45632</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7848,7 +7848,7 @@
         <v>45103</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7921,7 +7921,7 @@
         <v>45348</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7994,7 +7994,7 @@
         <v>45118</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8067,7 +8067,7 @@
         <v>45196</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8145,7 +8145,7 @@
         <v>44858</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8218,7 +8218,7 @@
         <v>45062</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8291,7 +8291,7 @@
         <v>45621</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8364,7 +8364,7 @@
         <v>44659</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8437,7 +8437,7 @@
         <v>45182</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8510,7 +8510,7 @@
         <v>45189</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8583,7 +8583,7 @@
         <v>45201</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8656,7 +8656,7 @@
         <v>44895</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8729,7 +8729,7 @@
         <v>45590</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8802,7 +8802,7 @@
         <v>45198</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         <v>45161</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8953,7 +8953,7 @@
         <v>45384</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9026,7 +9026,7 @@
         <v>44952</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9099,7 +9099,7 @@
         <v>44823</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9172,7 +9172,7 @@
         <v>44823</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9245,7 +9245,7 @@
         <v>44901</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9318,7 +9318,7 @@
         <v>45674</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9391,7 +9391,7 @@
         <v>45326</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9464,7 +9464,7 @@
         <v>45358</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9542,7 +9542,7 @@
         <v>45384</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9615,7 +9615,7 @@
         <v>45412</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9688,7 +9688,7 @@
         <v>45151</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9761,7 +9761,7 @@
         <v>45197</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9834,7 +9834,7 @@
         <v>44895</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9912,7 +9912,7 @@
         <v>44504</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9985,7 +9985,7 @@
         <v>45162</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10058,7 +10058,7 @@
         <v>45544</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10131,7 +10131,7 @@
         <v>45418</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10204,7 +10204,7 @@
         <v>45597</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10277,7 +10277,7 @@
         <v>45693</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10350,7 +10350,7 @@
         <v>45150</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10423,7 +10423,7 @@
         <v>45202</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10496,7 +10496,7 @@
         <v>44545</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10569,7 +10569,7 @@
         <v>45002</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10642,7 +10642,7 @@
         <v>44949</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10715,7 +10715,7 @@
         <v>44743</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10788,7 +10788,7 @@
         <v>44942</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10861,7 +10861,7 @@
         <v>45015</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10934,7 +10934,7 @@
         <v>45359</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11007,7 +11007,7 @@
         <v>45446</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11080,7 +11080,7 @@
         <v>44601</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11153,7 +11153,7 @@
         <v>44743</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11226,7 +11226,7 @@
         <v>45068</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11299,7 +11299,7 @@
         <v>45348</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11372,7 +11372,7 @@
         <v>45773</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11445,7 +11445,7 @@
         <v>45825</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11518,7 +11518,7 @@
         <v>45887</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11591,7 +11591,7 @@
         <v>45632</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11664,7 +11664,7 @@
         <v>45834</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11737,7 +11737,7 @@
         <v>45966</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11810,7 +11810,7 @@
         <v>45832</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11888,7 +11888,7 @@
         <v>45773</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11961,7 +11961,7 @@
         <v>46080</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12039,7 +12039,7 @@
         <v>45443</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12117,7 +12117,7 @@
         <v>45929</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12190,7 +12190,7 @@
         <v>45602</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12263,7 +12263,7 @@
         <v>45895</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12336,7 +12336,7 @@
         <v>45639</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12409,7 +12409,7 @@
         <v>45639</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12482,7 +12482,7 @@
         <v>45994</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12555,7 +12555,7 @@
         <v>45440</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12628,7 +12628,7 @@
         <v>45440</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12701,7 +12701,7 @@
         <v>44659</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12774,7 +12774,7 @@
         <v>45904</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12852,7 +12852,7 @@
         <v>45825</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12925,7 +12925,7 @@
         <v>44511</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12998,7 +12998,7 @@
         <v>45734</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13071,7 +13071,7 @@
         <v>45833</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13144,7 +13144,7 @@
         <v>45257</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13217,7 +13217,7 @@
         <v>45911</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13290,7 +13290,7 @@
         <v>45644</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13363,7 +13363,7 @@
         <v>45902</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13436,7 +13436,7 @@
         <v>45902</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13509,7 +13509,7 @@
         <v>45903</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13582,7 +13582,7 @@
         <v>45904</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13655,7 +13655,7 @@
         <v>45904</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13728,7 +13728,7 @@
         <v>45590</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13801,7 +13801,7 @@
         <v>45908</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13879,7 +13879,7 @@
         <v>44592</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13952,7 +13952,7 @@
         <v>45646</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14025,7 +14025,7 @@
         <v>45909</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14103,7 +14103,7 @@
         <v>45908</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14181,7 +14181,7 @@
         <v>45909</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14254,7 +14254,7 @@
         <v>45478</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14327,7 +14327,7 @@
         <v>44823</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14400,7 +14400,7 @@
         <v>45139</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14473,7 +14473,7 @@
         <v>44970</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14551,7 +14551,7 @@
         <v>45547</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14624,7 +14624,7 @@
         <v>44901</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14697,7 +14697,7 @@
         <v>45922</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14770,7 +14770,7 @@
         <v>45265</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14843,7 +14843,7 @@
         <v>44952</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14916,7 +14916,7 @@
         <v>45925</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14989,7 +14989,7 @@
         <v>45705</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15062,7 +15062,7 @@
         <v>46148</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15135,7 +15135,7 @@
         <v>45925</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15213,7 +15213,7 @@
         <v>45929</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15286,7 +15286,7 @@
         <v>45929</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15359,7 +15359,7 @@
         <v>45246</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15432,7 +15432,7 @@
         <v>45932</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15505,7 +15505,7 @@
         <v>45932</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15578,7 +15578,7 @@
         <v>46153</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15651,7 +15651,7 @@
         <v>46153</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15724,7 +15724,7 @@
         <v>46153</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15797,7 +15797,7 @@
         <v>45940</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15870,7 +15870,7 @@
         <v>44958</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15943,7 +15943,7 @@
         <v>45387</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16016,7 +16016,7 @@
         <v>45037</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16089,7 +16089,7 @@
         <v>44952</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16162,7 +16162,7 @@
         <v>45946</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16235,7 +16235,7 @@
         <v>45951</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16313,7 +16313,7 @@
         <v>45951</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16386,7 +16386,7 @@
         <v>45951</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16464,7 +16464,7 @@
         <v>45672</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16537,7 +16537,7 @@
         <v>45958</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16610,7 +16610,7 @@
         <v>45546</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16683,7 +16683,7 @@
         <v>45075</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16756,7 +16756,7 @@
         <v>45737</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16829,7 +16829,7 @@
         <v>45008</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16902,7 +16902,7 @@
         <v>44742</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16975,7 +16975,7 @@
         <v>45994</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17048,7 +17048,7 @@
         <v>46160</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17121,7 +17121,7 @@
         <v>44942</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17194,7 +17194,7 @@
         <v>45940</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17267,7 +17267,7 @@
         <v>45973</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17340,7 +17340,7 @@
         <v>45973</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17413,7 +17413,7 @@
         <v>45162</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17486,7 +17486,7 @@
         <v>45974</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17559,7 +17559,7 @@
         <v>45974</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17632,7 +17632,7 @@
         <v>45974</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17705,7 +17705,7 @@
         <v>45974</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17783,7 +17783,7 @@
         <v>45272</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17856,7 +17856,7 @@
         <v>45978</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17929,7 +17929,7 @@
         <v>45085</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18002,7 +18002,7 @@
         <v>45978</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18075,7 +18075,7 @@
         <v>45981</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18148,7 +18148,7 @@
         <v>46167</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18226,7 +18226,7 @@
         <v>45994</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18299,7 +18299,7 @@
         <v>44907</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18372,7 +18372,7 @@
         <v>45982</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18445,7 +18445,7 @@
         <v>45561</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18518,7 +18518,7 @@
         <v>45428</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18591,7 +18591,7 @@
         <v>45986</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18664,7 +18664,7 @@
         <v>45327</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18737,7 +18737,7 @@
         <v>45995</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18810,7 +18810,7 @@
         <v>45995</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18883,7 +18883,7 @@
         <v>45995</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18956,7 +18956,7 @@
         <v>44855</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19029,7 +19029,7 @@
         <v>45994</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19102,7 +19102,7 @@
         <v>45393</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19175,7 +19175,7 @@
         <v>45342</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19248,7 +19248,7 @@
         <v>46006</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19321,7 +19321,7 @@
         <v>46000</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19394,7 +19394,7 @@
         <v>46003</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19467,7 +19467,7 @@
         <v>46003</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19540,7 +19540,7 @@
         <v>45326</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19613,7 +19613,7 @@
         <v>45346</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19686,7 +19686,7 @@
         <v>45755</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19759,7 +19759,7 @@
         <v>45566</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19832,7 +19832,7 @@
         <v>46031</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19905,7 +19905,7 @@
         <v>46031</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19978,7 +19978,7 @@
         <v>46028</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20051,7 +20051,7 @@
         <v>44503</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20129,7 +20129,7 @@
         <v>45561</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20202,7 +20202,7 @@
         <v>45624</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20275,7 +20275,7 @@
         <v>46035</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20348,7 +20348,7 @@
         <v>45279</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20426,7 +20426,7 @@
         <v>46035</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20499,7 +20499,7 @@
         <v>46177</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20572,7 +20572,7 @@
         <v>46177</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20645,7 +20645,7 @@
         <v>46177</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20718,7 +20718,7 @@
         <v>44621</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20796,7 +20796,7 @@
         <v>45616</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20869,7 +20869,7 @@
         <v>46048</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20942,7 +20942,7 @@
         <v>45351</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21020,7 +21020,7 @@
         <v>46055</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21093,7 +21093,7 @@
         <v>46056</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21166,7 +21166,7 @@
         <v>45609</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21239,7 +21239,7 @@
         <v>46056</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21312,7 +21312,7 @@
         <v>45443</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21390,7 +21390,7 @@
         <v>46060</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21463,7 +21463,7 @@
         <v>45121</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21536,7 +21536,7 @@
         <v>45112</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21609,7 +21609,7 @@
         <v>46184</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21682,7 +21682,7 @@
         <v>46184</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21755,7 +21755,7 @@
         <v>44909</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21828,7 +21828,7 @@
         <v>44648</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21901,7 +21901,7 @@
         <v>44825</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21974,7 +21974,7 @@
         <v>45588</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22047,7 +22047,7 @@
         <v>46073</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22120,7 +22120,7 @@
         <v>46073</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22193,7 +22193,7 @@
         <v>46073</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22266,7 +22266,7 @@
         <v>46073</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22339,7 +22339,7 @@
         <v>44966</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22412,7 +22412,7 @@
         <v>46188</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22485,7 +22485,7 @@
         <v>46080</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22563,7 +22563,7 @@
         <v>46083</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22636,7 +22636,7 @@
         <v>44875</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22709,7 +22709,7 @@
         <v>45078</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22782,7 +22782,7 @@
         <v>45162</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22855,7 +22855,7 @@
         <v>46087</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22928,7 +22928,7 @@
         <v>44781</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23001,7 +23001,7 @@
         <v>45538</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23074,7 +23074,7 @@
         <v>46093</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23147,7 +23147,7 @@
         <v>45152</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23220,7 +23220,7 @@
         <v>45621</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23293,7 +23293,7 @@
         <v>44823</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23366,7 +23366,7 @@
         <v>46100</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23439,7 +23439,7 @@
         <v>46101</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23512,7 +23512,7 @@
         <v>45475</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23585,7 +23585,7 @@
         <v>45636</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23658,7 +23658,7 @@
         <v>44592</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23731,7 +23731,7 @@
         <v>45217</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23809,7 +23809,7 @@
         <v>46048</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23882,7 +23882,7 @@
         <v>45762</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23955,7 +23955,7 @@
         <v>45763</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24028,7 +24028,7 @@
         <v>45763</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24101,7 +24101,7 @@
         <v>45675</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24174,7 +24174,7 @@
         <v>46198</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24247,7 +24247,7 @@
         <v>46113</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24320,7 +24320,7 @@
         <v>45104</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24393,7 +24393,7 @@
         <v>46113</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24466,7 +24466,7 @@
         <v>44643</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24539,7 +24539,7 @@
         <v>45761</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24612,7 +24612,7 @@
         <v>46126</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24685,7 +24685,7 @@
         <v>46126</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24758,7 +24758,7 @@
         <v>45624</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24831,7 +24831,7 @@
         <v>45355</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24904,7 +24904,7 @@
         <v>45609</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24977,7 +24977,7 @@
         <v>45609</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25050,7 +25050,7 @@
         <v>45616</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25123,7 +25123,7 @@
         <v>44720</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25196,7 +25196,7 @@
         <v>45845</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25269,7 +25269,7 @@
         <v>45412</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25342,7 +25342,7 @@
         <v>45915</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25415,7 +25415,7 @@
         <v>45896</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25488,7 +25488,7 @@
         <v>45825</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25561,7 +25561,7 @@
         <v>46205</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25634,7 +25634,7 @@
         <v>45698</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25707,7 +25707,7 @@
         <v>44705</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25780,7 +25780,7 @@
         <v>45615</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25853,7 +25853,7 @@
         <v>44600</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25931,7 +25931,7 @@
         <v>44701</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26004,7 +26004,7 @@
         <v>45425</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26077,7 +26077,7 @@
         <v>46212</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26150,7 +26150,7 @@
         <v>44960</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26223,7 +26223,7 @@
         <v>45467</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26296,7 +26296,7 @@
         <v>44614</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26369,7 +26369,7 @@
         <v>44601</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26442,7 +26442,7 @@
         <v>45531</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26515,7 +26515,7 @@
         <v>45103</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26588,7 +26588,7 @@
         <v>44952</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26661,7 +26661,7 @@
         <v>44952</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26734,7 +26734,7 @@
         <v>44952</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26807,7 +26807,7 @@
         <v>45404</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26880,7 +26880,7 @@
         <v>44952</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26953,7 +26953,7 @@
         <v>44916</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27026,7 +27026,7 @@
         <v>45182</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27099,7 +27099,7 @@
         <v>45763</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27172,7 +27172,7 @@
         <v>44952</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27245,7 +27245,7 @@
         <v>44952</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27318,7 +27318,7 @@
         <v>46272</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27391,7 +27391,7 @@
         <v>44959</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27464,7 +27464,7 @@
         <v>45762</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27537,7 +27537,7 @@
         <v>44902</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27610,7 +27610,7 @@
         <v>46274</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27688,7 +27688,7 @@
         <v>45533</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27761,7 +27761,7 @@
         <v>45587</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27834,7 +27834,7 @@
         <v>45702</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27907,7 +27907,7 @@
         <v>45187</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27980,7 +27980,7 @@
         <v>45686</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28053,7 +28053,7 @@
         <v>44621</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28131,7 +28131,7 @@
         <v>45150</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28204,7 +28204,7 @@
         <v>44858</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28277,7 +28277,7 @@
         <v>45119</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28350,7 +28350,7 @@
         <v>46276</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28423,7 +28423,7 @@
         <v>45415</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28496,7 +28496,7 @@
         <v>46279</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28569,7 +28569,7 @@
         <v>46279</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28642,7 +28642,7 @@
         <v>46239</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28715,7 +28715,7 @@
         <v>45162</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28788,7 +28788,7 @@
         <v>45047</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28861,7 +28861,7 @@
         <v>45600</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28934,7 +28934,7 @@
         <v>45600</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29007,7 +29007,7 @@
         <v>45181</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29080,7 +29080,7 @@
         <v>45217</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29158,7 +29158,7 @@
         <v>45092</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29231,7 +29231,7 @@
         <v>46244</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29304,7 +29304,7 @@
         <v>44959</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29377,7 +29377,7 @@
         <v>45273</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29450,7 +29450,7 @@
         <v>44685</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29523,7 +29523,7 @@
         <v>45530</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29596,7 +29596,7 @@
         <v>45595</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29669,7 +29669,7 @@
         <v>45189</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29742,7 +29742,7 @@
         <v>44902</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29815,7 +29815,7 @@
         <v>45541</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29888,7 +29888,7 @@
         <v>46293</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29961,7 +29961,7 @@
         <v>45151</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30034,7 +30034,7 @@
         <v>45006</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30107,7 +30107,7 @@
         <v>44627</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30180,7 +30180,7 @@
         <v>45603</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30253,7 +30253,7 @@
         <v>45049</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30326,7 +30326,7 @@
         <v>45254</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30399,7 +30399,7 @@
         <v>44812</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30472,7 +30472,7 @@
         <v>45400</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30545,7 +30545,7 @@
         <v>45272</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30618,7 +30618,7 @@
         <v>45124</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30691,7 +30691,7 @@
         <v>45593</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30764,7 +30764,7 @@
         <v>46254</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30842,7 +30842,7 @@
         <v>45566</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30915,7 +30915,7 @@
         <v>45777</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30988,7 +30988,7 @@
         <v>45731</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31061,7 +31061,7 @@
         <v>44910</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31139,7 +31139,7 @@
         <v>45782</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31212,7 +31212,7 @@
         <v>45785</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31290,7 +31290,7 @@
         <v>45785</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31363,7 +31363,7 @@
         <v>45000</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31436,7 +31436,7 @@
         <v>45786</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31509,7 +31509,7 @@
         <v>46260</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31582,7 +31582,7 @@
         <v>45723</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31655,7 +31655,7 @@
         <v>45743</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31728,7 +31728,7 @@
         <v>45790</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31801,7 +31801,7 @@
         <v>45790</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31874,7 +31874,7 @@
         <v>45743</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31947,7 +31947,7 @@
         <v>45719</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32020,7 +32020,7 @@
         <v>45713</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32093,7 +32093,7 @@
         <v>45713</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32166,7 +32166,7 @@
         <v>45792</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32239,7 +32239,7 @@
         <v>45796</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32312,7 +32312,7 @@
         <v>46265</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32390,7 +32390,7 @@
         <v>45796</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32463,7 +32463,7 @@
         <v>46304</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32541,7 +32541,7 @@
         <v>45671</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32614,7 +32614,7 @@
         <v>45328</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32687,7 +32687,7 @@
         <v>45666</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32760,7 +32760,7 @@
         <v>45798</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32833,7 +32833,7 @@
         <v>46265</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32911,7 +32911,7 @@
         <v>45798</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32984,7 +32984,7 @@
         <v>46309</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33062,7 +33062,7 @@
         <v>45803</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33135,7 +33135,7 @@
         <v>45804</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33208,7 +33208,7 @@
         <v>45811</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33281,7 +33281,7 @@
         <v>45470</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33354,7 +33354,7 @@
         <v>45812</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33427,7 +33427,7 @@
         <v>45825</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33500,7 +33500,7 @@
         <v>45825</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33573,7 +33573,7 @@
         <v>45831</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33646,7 +33646,7 @@
         <v>45842</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33719,7 +33719,7 @@
         <v>45849</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33792,7 +33792,7 @@
         <v>45713</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33865,7 +33865,7 @@
         <v>44776</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33938,7 +33938,7 @@
         <v>45734</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34011,7 +34011,7 @@
         <v>45882</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34089,7 +34089,7 @@
         <v>45883</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34162,7 +34162,7 @@
         <v>44812</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34240,7 +34240,7 @@
         <v>45670</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34313,7 +34313,7 @@
         <v>44613</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34391,7 +34391,7 @@
         <v>45483</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34464,7 +34464,7 @@
         <v>45717</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>

--- a/Översikt DALS-ED.xlsx
+++ b/Översikt DALS-ED.xlsx
@@ -601,7 +601,7 @@
         <v>44601</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>45954</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
         <v>45897</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>45331</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>46160</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>44907</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>44833</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>45790</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         <v>45643</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>45833</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>44835</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>45422</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
         <v>45817</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>45188</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         <v>44494</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2410,7 +2410,7 @@
         <v>45265</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         <v>45422</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2634,7 +2634,7 @@
         <v>46048</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2745,7 +2745,7 @@
         <v>45151</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2860,7 +2860,7 @@
         <v>45937</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>45281</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3084,7 +3084,7 @@
         <v>46245</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         <v>46251</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3300,7 +3300,7 @@
         <v>45572</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3410,7 +3410,7 @@
         <v>45588</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3520,7 +3520,7 @@
         <v>45569</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3626,7 +3626,7 @@
         <v>44601</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3732,7 +3732,7 @@
         <v>44865</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3842,7 +3842,7 @@
         <v>45402</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3947,7 +3947,7 @@
         <v>45237</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4057,7 +4057,7 @@
         <v>45930</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4162,7 +4162,7 @@
         <v>44952</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         <v>45183</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         <v>45799</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4481,7 +4481,7 @@
         <v>45803</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4590,7 +4590,7 @@
         <v>45475</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4695,7 +4695,7 @@
         <v>45588</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4804,7 +4804,7 @@
         <v>45075</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4909,7 +4909,7 @@
         <v>45014</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5014,7 +5014,7 @@
         <v>45120</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
         <v>44818</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5229,7 +5229,7 @@
         <v>45687</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5334,7 +5334,7 @@
         <v>44781</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5407,7 +5407,7 @@
         <v>44533</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5480,7 +5480,7 @@
         <v>44536</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5553,7 +5553,7 @@
         <v>44615</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5626,7 +5626,7 @@
         <v>44536</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5699,7 +5699,7 @@
         <v>44588</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5772,7 +5772,7 @@
         <v>44690</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5845,7 +5845,7 @@
         <v>44733</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5918,7 +5918,7 @@
         <v>44781</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5991,7 +5991,7 @@
         <v>44676</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6064,7 +6064,7 @@
         <v>44578</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6137,7 +6137,7 @@
         <v>44799</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6210,7 +6210,7 @@
         <v>44705</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6283,7 +6283,7 @@
         <v>44743</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6356,7 +6356,7 @@
         <v>44615</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6429,7 +6429,7 @@
         <v>44608</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6502,7 +6502,7 @@
         <v>44823</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6575,7 +6575,7 @@
         <v>44837</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6648,7 +6648,7 @@
         <v>44657</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6726,7 +6726,7 @@
         <v>44685</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6799,7 +6799,7 @@
         <v>44685</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6872,7 +6872,7 @@
         <v>44705</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6945,7 +6945,7 @@
         <v>44705</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7018,7 +7018,7 @@
         <v>44592</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7091,7 +7091,7 @@
         <v>45887</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7164,7 +7164,7 @@
         <v>45773</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7237,7 +7237,7 @@
         <v>45387</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7310,7 +7310,7 @@
         <v>45702</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7383,7 +7383,7 @@
         <v>45187</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7456,7 +7456,7 @@
         <v>44970</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7534,7 +7534,7 @@
         <v>44825</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7607,7 +7607,7 @@
         <v>45593</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7680,7 +7680,7 @@
         <v>44916</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7753,7 +7753,7 @@
         <v>45895</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7826,7 +7826,7 @@
         <v>44823</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7899,7 +7899,7 @@
         <v>45833</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7972,7 +7972,7 @@
         <v>45257</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8045,7 +8045,7 @@
         <v>45359</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8118,7 +8118,7 @@
         <v>45600</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8191,7 +8191,7 @@
         <v>45600</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8264,7 +8264,7 @@
         <v>45412</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8337,7 +8337,7 @@
         <v>45902</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8410,7 +8410,7 @@
         <v>45883</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8483,7 +8483,7 @@
         <v>45412</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8556,7 +8556,7 @@
         <v>45531</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         <v>45903</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8702,7 +8702,7 @@
         <v>45904</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         <v>45904</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8848,7 +8848,7 @@
         <v>44659</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8921,7 +8921,7 @@
         <v>45902</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8994,7 +8994,7 @@
         <v>45393</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9067,7 +9067,7 @@
         <v>44685</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9140,7 +9140,7 @@
         <v>45908</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9218,7 +9218,7 @@
         <v>45646</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9291,7 +9291,7 @@
         <v>45908</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9369,7 +9369,7 @@
         <v>45909</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9442,7 +9442,7 @@
         <v>45909</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9520,7 +9520,7 @@
         <v>45994</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9593,7 +9593,7 @@
         <v>45151</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9666,7 +9666,7 @@
         <v>45217</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9744,7 +9744,7 @@
         <v>45922</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9817,7 +9817,7 @@
         <v>46167</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9895,7 +9895,7 @@
         <v>45994</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9968,7 +9968,7 @@
         <v>46006</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10041,7 +10041,7 @@
         <v>45049</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10114,7 +10114,7 @@
         <v>45925</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10187,7 +10187,7 @@
         <v>45925</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10265,7 +10265,7 @@
         <v>45929</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10338,7 +10338,7 @@
         <v>45929</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10411,7 +10411,7 @@
         <v>44942</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10484,7 +10484,7 @@
         <v>45932</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10557,7 +10557,7 @@
         <v>45327</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10630,7 +10630,7 @@
         <v>45351</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10708,7 +10708,7 @@
         <v>45932</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10781,7 +10781,7 @@
         <v>45440</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10854,7 +10854,7 @@
         <v>45440</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10927,7 +10927,7 @@
         <v>45762</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11000,7 +11000,7 @@
         <v>45940</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11073,7 +11073,7 @@
         <v>45428</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11146,7 +11146,7 @@
         <v>46177</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11219,7 +11219,7 @@
         <v>46177</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11292,7 +11292,7 @@
         <v>45609</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11365,7 +11365,7 @@
         <v>46177</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11438,7 +11438,7 @@
         <v>44952</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11511,7 +11511,7 @@
         <v>44952</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11584,7 +11584,7 @@
         <v>45946</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11657,7 +11657,7 @@
         <v>44895</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11735,7 +11735,7 @@
         <v>45675</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11808,7 +11808,7 @@
         <v>45672</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11881,7 +11881,7 @@
         <v>45561</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11954,7 +11954,7 @@
         <v>45152</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12027,7 +12027,7 @@
         <v>45085</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12100,7 +12100,7 @@
         <v>45951</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12173,7 +12173,7 @@
         <v>45951</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12251,7 +12251,7 @@
         <v>45415</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12324,7 +12324,7 @@
         <v>45951</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12402,7 +12402,7 @@
         <v>44901</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12475,7 +12475,7 @@
         <v>45326</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12548,7 +12548,7 @@
         <v>45958</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12621,7 +12621,7 @@
         <v>45673</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12694,7 +12694,7 @@
         <v>46184</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12767,7 +12767,7 @@
         <v>44823</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12840,7 +12840,7 @@
         <v>45068</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12913,7 +12913,7 @@
         <v>46188</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12986,7 +12986,7 @@
         <v>46184</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13059,7 +13059,7 @@
         <v>45139</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13132,7 +13132,7 @@
         <v>45112</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13205,7 +13205,7 @@
         <v>44592</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13278,7 +13278,7 @@
         <v>44960</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13351,7 +13351,7 @@
         <v>44503</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13429,7 +13429,7 @@
         <v>46198</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13502,7 +13502,7 @@
         <v>45974</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13580,7 +13580,7 @@
         <v>45973</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13653,7 +13653,7 @@
         <v>45974</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13726,7 +13726,7 @@
         <v>45974</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13799,7 +13799,7 @@
         <v>46048</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13872,7 +13872,7 @@
         <v>45008</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13945,7 +13945,7 @@
         <v>45973</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14018,7 +14018,7 @@
         <v>45974</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14091,7 +14091,7 @@
         <v>45978</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14164,7 +14164,7 @@
         <v>45978</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14237,7 +14237,7 @@
         <v>45182</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14310,7 +14310,7 @@
         <v>45124</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14383,7 +14383,7 @@
         <v>45103</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14456,7 +14456,7 @@
         <v>45544</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14529,7 +14529,7 @@
         <v>45981</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14602,7 +14602,7 @@
         <v>45616</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14675,7 +14675,7 @@
         <v>44907</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14748,7 +14748,7 @@
         <v>45384</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14821,7 +14821,7 @@
         <v>46205</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14894,7 +14894,7 @@
         <v>45986</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14967,7 +14967,7 @@
         <v>45982</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15040,7 +15040,7 @@
         <v>45478</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15113,7 +15113,7 @@
         <v>45119</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15186,7 +15186,7 @@
         <v>45400</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15259,7 +15259,7 @@
         <v>45994</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15332,7 +15332,7 @@
         <v>46212</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15405,7 +15405,7 @@
         <v>45279</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15483,7 +15483,7 @@
         <v>45995</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15556,7 +15556,7 @@
         <v>45995</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15629,7 +15629,7 @@
         <v>45995</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15702,7 +15702,7 @@
         <v>45265</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15775,7 +15775,7 @@
         <v>45198</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15848,7 +15848,7 @@
         <v>44812</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15921,7 +15921,7 @@
         <v>45151</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15994,7 +15994,7 @@
         <v>46000</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16067,7 +16067,7 @@
         <v>45731</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16140,7 +16140,7 @@
         <v>45566</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16213,7 +16213,7 @@
         <v>45777</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16286,7 +16286,7 @@
         <v>46003</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16359,7 +16359,7 @@
         <v>46003</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16432,7 +16432,7 @@
         <v>44910</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16510,7 +16510,7 @@
         <v>45782</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16583,7 +16583,7 @@
         <v>45786</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16656,7 +16656,7 @@
         <v>46279</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16729,7 +16729,7 @@
         <v>45000</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16802,7 +16802,7 @@
         <v>45785</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16875,7 +16875,7 @@
         <v>46279</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16948,7 +16948,7 @@
         <v>45785</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17026,7 +17026,7 @@
         <v>44855</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17099,7 +17099,7 @@
         <v>45346</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17172,7 +17172,7 @@
         <v>45790</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17245,7 +17245,7 @@
         <v>45790</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17318,7 +17318,7 @@
         <v>46239</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17391,7 +17391,7 @@
         <v>45713</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17464,7 +17464,7 @@
         <v>45743</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17537,7 +17537,7 @@
         <v>46028</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17610,7 +17610,7 @@
         <v>45723</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17683,7 +17683,7 @@
         <v>45792</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17756,7 +17756,7 @@
         <v>45719</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17829,7 +17829,7 @@
         <v>45713</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17902,7 +17902,7 @@
         <v>45743</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17975,7 +17975,7 @@
         <v>46031</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18048,7 +18048,7 @@
         <v>46031</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18121,7 +18121,7 @@
         <v>46035</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18194,7 +18194,7 @@
         <v>46035</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18267,7 +18267,7 @@
         <v>45796</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18340,7 +18340,7 @@
         <v>45796</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18413,7 +18413,7 @@
         <v>46244</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18486,7 +18486,7 @@
         <v>45798</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18559,7 +18559,7 @@
         <v>45666</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18632,7 +18632,7 @@
         <v>45798</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18705,7 +18705,7 @@
         <v>45328</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18778,7 +18778,7 @@
         <v>45671</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18851,7 +18851,7 @@
         <v>46048</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18924,7 +18924,7 @@
         <v>45803</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18997,7 +18997,7 @@
         <v>45804</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19070,7 +19070,7 @@
         <v>46056</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19143,7 +19143,7 @@
         <v>46055</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19216,7 +19216,7 @@
         <v>46056</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19289,7 +19289,7 @@
         <v>45470</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19362,7 +19362,7 @@
         <v>46293</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19435,7 +19435,7 @@
         <v>45812</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19508,7 +19508,7 @@
         <v>46060</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19581,7 +19581,7 @@
         <v>45811</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19654,7 +19654,7 @@
         <v>44942</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19727,7 +19727,7 @@
         <v>46073</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19800,7 +19800,7 @@
         <v>45342</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19873,7 +19873,7 @@
         <v>46073</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19946,7 +19946,7 @@
         <v>46073</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20019,7 +20019,7 @@
         <v>46073</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20092,7 +20092,7 @@
         <v>46254</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20170,7 +20170,7 @@
         <v>45825</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20243,7 +20243,7 @@
         <v>45825</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20316,7 +20316,7 @@
         <v>46080</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20394,7 +20394,7 @@
         <v>45831</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20467,7 +20467,7 @@
         <v>46083</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20540,7 +20540,7 @@
         <v>46087</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20613,7 +20613,7 @@
         <v>46093</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20686,7 +20686,7 @@
         <v>44895</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20759,7 +20759,7 @@
         <v>46101</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20832,7 +20832,7 @@
         <v>45842</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20905,7 +20905,7 @@
         <v>46100</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20978,7 +20978,7 @@
         <v>45713</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21051,7 +21051,7 @@
         <v>45849</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21124,7 +21124,7 @@
         <v>44776</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21197,7 +21197,7 @@
         <v>46113</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21270,7 +21270,7 @@
         <v>45475</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21343,7 +21343,7 @@
         <v>46113</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21416,7 +21416,7 @@
         <v>45246</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21489,7 +21489,7 @@
         <v>45734</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21562,7 +21562,7 @@
         <v>46260</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21635,7 +21635,7 @@
         <v>46304</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21713,7 +21713,7 @@
         <v>46126</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21786,7 +21786,7 @@
         <v>46126</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21859,7 +21859,7 @@
         <v>44601</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21932,7 +21932,7 @@
         <v>46265</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22010,7 +22010,7 @@
         <v>46265</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22088,7 +22088,7 @@
         <v>44875</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22161,7 +22161,7 @@
         <v>45882</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22239,7 +22239,7 @@
         <v>44902</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22312,7 +22312,7 @@
         <v>44901</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22385,7 +22385,7 @@
         <v>44909</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22458,7 +22458,7 @@
         <v>45597</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22531,7 +22531,7 @@
         <v>44648</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22604,7 +22604,7 @@
         <v>45825</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22677,7 +22677,7 @@
         <v>45202</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22750,7 +22750,7 @@
         <v>46309</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22828,7 +22828,7 @@
         <v>45632</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22901,7 +22901,7 @@
         <v>45698</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22974,7 +22974,7 @@
         <v>45915</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23047,7 +23047,7 @@
         <v>45603</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23120,7 +23120,7 @@
         <v>44952</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23193,7 +23193,7 @@
         <v>45832</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23271,7 +23271,7 @@
         <v>45929</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23344,7 +23344,7 @@
         <v>44720</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23417,7 +23417,7 @@
         <v>44600</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23495,7 +23495,7 @@
         <v>46314</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23568,7 +23568,7 @@
         <v>45896</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23641,7 +23641,7 @@
         <v>45825</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23714,7 +23714,7 @@
         <v>45118</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23787,7 +23787,7 @@
         <v>45994</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23860,7 +23860,7 @@
         <v>45966</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23933,7 +23933,7 @@
         <v>46272</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24006,7 +24006,7 @@
         <v>45443</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24084,7 +24084,7 @@
         <v>45904</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24162,7 +24162,7 @@
         <v>45845</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24235,7 +24235,7 @@
         <v>45734</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24308,7 +24308,7 @@
         <v>45834</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24381,7 +24381,7 @@
         <v>45825</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24454,7 +24454,7 @@
         <v>45602</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24527,7 +24527,7 @@
         <v>45358</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24605,7 +24605,7 @@
         <v>45047</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24678,7 +24678,7 @@
         <v>46080</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24756,7 +24756,7 @@
         <v>45541</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24829,7 +24829,7 @@
         <v>45632</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24902,7 +24902,7 @@
         <v>44705</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24975,7 +24975,7 @@
         <v>44511</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25048,7 +25048,7 @@
         <v>46276</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25121,7 +25121,7 @@
         <v>45150</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25194,7 +25194,7 @@
         <v>45595</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25267,7 +25267,7 @@
         <v>45911</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25340,7 +25340,7 @@
         <v>45644</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25413,7 +25413,7 @@
         <v>46274</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25491,7 +25491,7 @@
         <v>46148</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25564,7 +25564,7 @@
         <v>45588</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25637,7 +25637,7 @@
         <v>46153</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25710,7 +25710,7 @@
         <v>45189</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25783,7 +25783,7 @@
         <v>46153</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25856,7 +25856,7 @@
         <v>46153</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25929,7 +25929,7 @@
         <v>45624</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26002,7 +26002,7 @@
         <v>45762</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26075,7 +26075,7 @@
         <v>46160</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26148,7 +26148,7 @@
         <v>45624</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26221,7 +26221,7 @@
         <v>45546</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26294,7 +26294,7 @@
         <v>45737</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26367,7 +26367,7 @@
         <v>45940</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26440,7 +26440,7 @@
         <v>45006</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26513,7 +26513,7 @@
         <v>45037</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26586,7 +26586,7 @@
         <v>44952</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26659,7 +26659,7 @@
         <v>44958</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26732,7 +26732,7 @@
         <v>44952</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26805,7 +26805,7 @@
         <v>45761</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26878,7 +26878,7 @@
         <v>45161</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26956,7 +26956,7 @@
         <v>45162</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27029,7 +27029,7 @@
         <v>45590</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27102,7 +27102,7 @@
         <v>45615</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27175,7 +27175,7 @@
         <v>45002</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27248,7 +27248,7 @@
         <v>45621</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27321,7 +27321,7 @@
         <v>45590</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27394,7 +27394,7 @@
         <v>45062</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27467,7 +27467,7 @@
         <v>45693</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27540,7 +27540,7 @@
         <v>45189</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27613,7 +27613,7 @@
         <v>45181</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27686,7 +27686,7 @@
         <v>45150</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27759,7 +27759,7 @@
         <v>45530</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27832,7 +27832,7 @@
         <v>45217</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27910,7 +27910,7 @@
         <v>45197</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27983,7 +27983,7 @@
         <v>45547</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28056,7 +28056,7 @@
         <v>45348</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28129,7 +28129,7 @@
         <v>45418</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28202,7 +28202,7 @@
         <v>45425</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28275,7 +28275,7 @@
         <v>45467</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28348,7 +28348,7 @@
         <v>45272</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28421,7 +28421,7 @@
         <v>44858</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28494,7 +28494,7 @@
         <v>45092</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28567,7 +28567,7 @@
         <v>45273</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28640,7 +28640,7 @@
         <v>45015</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28713,7 +28713,7 @@
         <v>44959</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28786,7 +28786,7 @@
         <v>44902</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28859,7 +28859,7 @@
         <v>44959</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28932,7 +28932,7 @@
         <v>45103</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29005,7 +29005,7 @@
         <v>45121</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29078,7 +29078,7 @@
         <v>44545</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29151,7 +29151,7 @@
         <v>45075</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29224,7 +29224,7 @@
         <v>45355</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29297,7 +29297,7 @@
         <v>44949</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29370,7 +29370,7 @@
         <v>45254</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29443,7 +29443,7 @@
         <v>44621</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29521,7 +29521,7 @@
         <v>44781</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29594,7 +29594,7 @@
         <v>45348</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29667,7 +29667,7 @@
         <v>45384</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29740,7 +29740,7 @@
         <v>45404</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29813,7 +29813,7 @@
         <v>45104</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29886,7 +29886,7 @@
         <v>45566</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29959,7 +29959,7 @@
         <v>44621</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30037,7 +30037,7 @@
         <v>45162</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30110,7 +30110,7 @@
         <v>45621</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30183,7 +30183,7 @@
         <v>45587</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30256,7 +30256,7 @@
         <v>45616</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30329,7 +30329,7 @@
         <v>45636</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30402,7 +30402,7 @@
         <v>45639</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30475,7 +30475,7 @@
         <v>45639</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30548,7 +30548,7 @@
         <v>45162</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30621,7 +30621,7 @@
         <v>45078</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30694,7 +30694,7 @@
         <v>44743</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30767,7 +30767,7 @@
         <v>45182</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30840,7 +30840,7 @@
         <v>45674</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30913,7 +30913,7 @@
         <v>44601</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30986,7 +30986,7 @@
         <v>45763</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31059,7 +31059,7 @@
         <v>44643</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31132,7 +31132,7 @@
         <v>45196</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31210,7 +31210,7 @@
         <v>45609</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31283,7 +31283,7 @@
         <v>44858</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31356,7 +31356,7 @@
         <v>44701</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31429,7 +31429,7 @@
         <v>45162</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31502,7 +31502,7 @@
         <v>45755</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31575,7 +31575,7 @@
         <v>45686</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31648,7 +31648,7 @@
         <v>44743</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31721,7 +31721,7 @@
         <v>45773</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31794,7 +31794,7 @@
         <v>44614</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31867,7 +31867,7 @@
         <v>44659</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31940,7 +31940,7 @@
         <v>44823</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32013,7 +32013,7 @@
         <v>45705</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32086,7 +32086,7 @@
         <v>45201</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32159,7 +32159,7 @@
         <v>44823</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32232,7 +32232,7 @@
         <v>45272</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32305,7 +32305,7 @@
         <v>44742</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32378,7 +32378,7 @@
         <v>45763</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32451,7 +32451,7 @@
         <v>45763</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32524,7 +32524,7 @@
         <v>44952</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32597,7 +32597,7 @@
         <v>44952</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32670,7 +32670,7 @@
         <v>44952</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32743,7 +32743,7 @@
         <v>45326</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32816,7 +32816,7 @@
         <v>45609</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32889,7 +32889,7 @@
         <v>44504</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32962,7 +32962,7 @@
         <v>45538</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33035,7 +33035,7 @@
         <v>45446</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33108,7 +33108,7 @@
         <v>45533</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33181,7 +33181,7 @@
         <v>44966</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33254,7 +33254,7 @@
         <v>44627</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33327,7 +33327,7 @@
         <v>44952</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33400,7 +33400,7 @@
         <v>45561</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33473,7 +33473,7 @@
         <v>45443</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33551,7 +33551,7 @@
         <v>44613</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33629,7 +33629,7 @@
         <v>44812</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33707,7 +33707,7 @@
         <v>45670</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33780,7 +33780,7 @@
         <v>45483</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33853,7 +33853,7 @@
         <v>45717</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>

--- a/Översikt DALS-ED.xlsx
+++ b/Översikt DALS-ED.xlsx
@@ -601,7 +601,7 @@
         <v>44601</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>45954</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
         <v>45897</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>45331</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>46160</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>44907</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>44833</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>45790</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         <v>45643</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>45833</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>44835</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>45422</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
         <v>45817</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>45188</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         <v>44494</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2410,7 +2410,7 @@
         <v>45265</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         <v>45422</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2634,7 +2634,7 @@
         <v>46048</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2745,7 +2745,7 @@
         <v>45151</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2860,7 +2860,7 @@
         <v>45937</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>45281</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3084,7 +3084,7 @@
         <v>46245</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         <v>46251</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3300,7 +3300,7 @@
         <v>45572</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3410,7 +3410,7 @@
         <v>45588</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3520,7 +3520,7 @@
         <v>45569</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3626,7 +3626,7 @@
         <v>44601</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3732,7 +3732,7 @@
         <v>44865</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3842,7 +3842,7 @@
         <v>45402</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3947,7 +3947,7 @@
         <v>45237</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4057,7 +4057,7 @@
         <v>45930</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4162,7 +4162,7 @@
         <v>44952</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         <v>45183</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         <v>45799</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4481,7 +4481,7 @@
         <v>45803</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4590,7 +4590,7 @@
         <v>45475</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4695,7 +4695,7 @@
         <v>45588</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4804,7 +4804,7 @@
         <v>45075</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4909,7 +4909,7 @@
         <v>45014</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5014,7 +5014,7 @@
         <v>45120</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
         <v>44818</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5229,7 +5229,7 @@
         <v>45687</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5334,7 +5334,7 @@
         <v>44781</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5407,7 +5407,7 @@
         <v>44533</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5480,7 +5480,7 @@
         <v>44536</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5553,7 +5553,7 @@
         <v>44615</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5626,7 +5626,7 @@
         <v>44536</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5699,7 +5699,7 @@
         <v>44588</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5772,7 +5772,7 @@
         <v>44690</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5845,7 +5845,7 @@
         <v>44733</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5918,7 +5918,7 @@
         <v>44781</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5991,7 +5991,7 @@
         <v>44676</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6064,7 +6064,7 @@
         <v>44578</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6137,7 +6137,7 @@
         <v>44799</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6210,7 +6210,7 @@
         <v>44705</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6283,7 +6283,7 @@
         <v>44743</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6356,7 +6356,7 @@
         <v>44615</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6429,7 +6429,7 @@
         <v>44608</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6502,7 +6502,7 @@
         <v>44823</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6575,7 +6575,7 @@
         <v>44837</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6648,7 +6648,7 @@
         <v>44657</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6726,7 +6726,7 @@
         <v>44685</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6799,7 +6799,7 @@
         <v>44685</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6872,7 +6872,7 @@
         <v>44705</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6945,7 +6945,7 @@
         <v>44705</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7018,7 +7018,7 @@
         <v>44592</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7091,7 +7091,7 @@
         <v>45887</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7164,7 +7164,7 @@
         <v>45773</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7237,7 +7237,7 @@
         <v>45387</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7310,7 +7310,7 @@
         <v>45702</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7383,7 +7383,7 @@
         <v>45187</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7456,7 +7456,7 @@
         <v>44970</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7534,7 +7534,7 @@
         <v>44825</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7607,7 +7607,7 @@
         <v>45593</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7680,7 +7680,7 @@
         <v>44916</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7753,7 +7753,7 @@
         <v>45895</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7826,7 +7826,7 @@
         <v>44823</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7899,7 +7899,7 @@
         <v>45833</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7972,7 +7972,7 @@
         <v>45257</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8045,7 +8045,7 @@
         <v>45359</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8118,7 +8118,7 @@
         <v>45600</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8191,7 +8191,7 @@
         <v>45600</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8264,7 +8264,7 @@
         <v>45412</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8337,7 +8337,7 @@
         <v>45902</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8410,7 +8410,7 @@
         <v>45883</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8483,7 +8483,7 @@
         <v>45412</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8556,7 +8556,7 @@
         <v>45531</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         <v>45903</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8702,7 +8702,7 @@
         <v>45904</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         <v>45904</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8848,7 +8848,7 @@
         <v>44659</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8921,7 +8921,7 @@
         <v>45902</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8994,7 +8994,7 @@
         <v>45393</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9067,7 +9067,7 @@
         <v>44685</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9140,7 +9140,7 @@
         <v>45908</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9218,7 +9218,7 @@
         <v>45646</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9291,7 +9291,7 @@
         <v>45908</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9369,7 +9369,7 @@
         <v>45909</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9442,7 +9442,7 @@
         <v>45909</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9520,7 +9520,7 @@
         <v>45994</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9593,7 +9593,7 @@
         <v>45151</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9666,7 +9666,7 @@
         <v>45217</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9744,7 +9744,7 @@
         <v>45922</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9817,7 +9817,7 @@
         <v>46167</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9895,7 +9895,7 @@
         <v>45994</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9968,7 +9968,7 @@
         <v>46006</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10041,7 +10041,7 @@
         <v>45049</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10114,7 +10114,7 @@
         <v>45925</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10187,7 +10187,7 @@
         <v>45925</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10265,7 +10265,7 @@
         <v>45929</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10338,7 +10338,7 @@
         <v>45929</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10411,7 +10411,7 @@
         <v>44942</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10484,7 +10484,7 @@
         <v>45932</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10557,7 +10557,7 @@
         <v>45327</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10630,7 +10630,7 @@
         <v>45351</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10708,7 +10708,7 @@
         <v>45932</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10781,7 +10781,7 @@
         <v>45440</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10854,7 +10854,7 @@
         <v>45440</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10927,7 +10927,7 @@
         <v>45762</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11000,7 +11000,7 @@
         <v>45940</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11073,7 +11073,7 @@
         <v>45428</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11146,7 +11146,7 @@
         <v>46177</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11219,7 +11219,7 @@
         <v>46177</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11292,7 +11292,7 @@
         <v>45609</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11365,7 +11365,7 @@
         <v>46177</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11438,7 +11438,7 @@
         <v>44952</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11511,7 +11511,7 @@
         <v>44952</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11584,7 +11584,7 @@
         <v>45946</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11657,7 +11657,7 @@
         <v>44895</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11735,7 +11735,7 @@
         <v>45675</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11808,7 +11808,7 @@
         <v>45672</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11881,7 +11881,7 @@
         <v>45561</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11954,7 +11954,7 @@
         <v>45152</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12027,7 +12027,7 @@
         <v>45085</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12100,7 +12100,7 @@
         <v>45951</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12173,7 +12173,7 @@
         <v>45951</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12251,7 +12251,7 @@
         <v>45415</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12324,7 +12324,7 @@
         <v>45951</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12402,7 +12402,7 @@
         <v>44901</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12475,7 +12475,7 @@
         <v>45326</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12548,7 +12548,7 @@
         <v>45958</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12621,7 +12621,7 @@
         <v>45673</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12694,7 +12694,7 @@
         <v>46184</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12767,7 +12767,7 @@
         <v>44823</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12840,7 +12840,7 @@
         <v>45068</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12913,7 +12913,7 @@
         <v>46188</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12986,7 +12986,7 @@
         <v>46184</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13059,7 +13059,7 @@
         <v>45139</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13132,7 +13132,7 @@
         <v>45112</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13205,7 +13205,7 @@
         <v>44592</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13278,7 +13278,7 @@
         <v>44960</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13351,7 +13351,7 @@
         <v>44503</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13429,7 +13429,7 @@
         <v>46198</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13502,7 +13502,7 @@
         <v>45974</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13580,7 +13580,7 @@
         <v>45973</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13653,7 +13653,7 @@
         <v>45974</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13726,7 +13726,7 @@
         <v>45974</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13799,7 +13799,7 @@
         <v>46048</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13872,7 +13872,7 @@
         <v>45008</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13945,7 +13945,7 @@
         <v>45973</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14018,7 +14018,7 @@
         <v>45974</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14091,7 +14091,7 @@
         <v>45978</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14164,7 +14164,7 @@
         <v>45978</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14237,7 +14237,7 @@
         <v>45182</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14310,7 +14310,7 @@
         <v>45124</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14383,7 +14383,7 @@
         <v>45103</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14456,7 +14456,7 @@
         <v>45544</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14529,7 +14529,7 @@
         <v>45981</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14602,7 +14602,7 @@
         <v>45616</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14675,7 +14675,7 @@
         <v>44907</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14748,7 +14748,7 @@
         <v>45384</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14821,7 +14821,7 @@
         <v>46205</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14894,7 +14894,7 @@
         <v>45986</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14967,7 +14967,7 @@
         <v>45982</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15040,7 +15040,7 @@
         <v>45478</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15113,7 +15113,7 @@
         <v>45119</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15186,7 +15186,7 @@
         <v>45400</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15259,7 +15259,7 @@
         <v>45994</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15332,7 +15332,7 @@
         <v>46212</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15405,7 +15405,7 @@
         <v>45279</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15483,7 +15483,7 @@
         <v>45995</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15556,7 +15556,7 @@
         <v>45995</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15629,7 +15629,7 @@
         <v>45995</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15702,7 +15702,7 @@
         <v>45265</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15775,7 +15775,7 @@
         <v>45198</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15848,7 +15848,7 @@
         <v>44812</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15921,7 +15921,7 @@
         <v>45151</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15994,7 +15994,7 @@
         <v>46000</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16067,7 +16067,7 @@
         <v>45731</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16140,7 +16140,7 @@
         <v>45566</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16213,7 +16213,7 @@
         <v>45777</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16286,7 +16286,7 @@
         <v>46003</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16359,7 +16359,7 @@
         <v>46003</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16432,7 +16432,7 @@
         <v>44910</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16510,7 +16510,7 @@
         <v>45782</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16583,7 +16583,7 @@
         <v>45786</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16656,7 +16656,7 @@
         <v>46279</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16729,7 +16729,7 @@
         <v>45000</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16802,7 +16802,7 @@
         <v>45785</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16875,7 +16875,7 @@
         <v>46279</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16948,7 +16948,7 @@
         <v>45785</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17026,7 +17026,7 @@
         <v>44855</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17099,7 +17099,7 @@
         <v>45346</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17172,7 +17172,7 @@
         <v>45790</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17245,7 +17245,7 @@
         <v>45790</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17318,7 +17318,7 @@
         <v>46239</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17391,7 +17391,7 @@
         <v>45713</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17464,7 +17464,7 @@
         <v>45743</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17537,7 +17537,7 @@
         <v>46028</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17610,7 +17610,7 @@
         <v>45723</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17683,7 +17683,7 @@
         <v>45792</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17756,7 +17756,7 @@
         <v>45719</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17829,7 +17829,7 @@
         <v>45713</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17902,7 +17902,7 @@
         <v>45743</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17975,7 +17975,7 @@
         <v>46031</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18048,7 +18048,7 @@
         <v>46031</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18121,7 +18121,7 @@
         <v>46035</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18194,7 +18194,7 @@
         <v>46035</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18267,7 +18267,7 @@
         <v>45796</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18340,7 +18340,7 @@
         <v>45796</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18413,7 +18413,7 @@
         <v>46244</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18486,7 +18486,7 @@
         <v>45798</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18559,7 +18559,7 @@
         <v>45666</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18632,7 +18632,7 @@
         <v>45798</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18705,7 +18705,7 @@
         <v>45328</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18778,7 +18778,7 @@
         <v>45671</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18851,7 +18851,7 @@
         <v>46048</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18924,7 +18924,7 @@
         <v>45803</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18997,7 +18997,7 @@
         <v>45804</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19070,7 +19070,7 @@
         <v>46056</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19143,7 +19143,7 @@
         <v>46055</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19216,7 +19216,7 @@
         <v>46056</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19289,7 +19289,7 @@
         <v>45470</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19362,7 +19362,7 @@
         <v>46293</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19435,7 +19435,7 @@
         <v>45812</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19508,7 +19508,7 @@
         <v>46060</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19581,7 +19581,7 @@
         <v>45811</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19654,7 +19654,7 @@
         <v>44942</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19727,7 +19727,7 @@
         <v>46073</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19800,7 +19800,7 @@
         <v>45342</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19873,7 +19873,7 @@
         <v>46073</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19946,7 +19946,7 @@
         <v>46073</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20019,7 +20019,7 @@
         <v>46073</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20092,7 +20092,7 @@
         <v>46254</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20170,7 +20170,7 @@
         <v>45825</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20243,7 +20243,7 @@
         <v>45825</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20316,7 +20316,7 @@
         <v>46080</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20394,7 +20394,7 @@
         <v>45831</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20467,7 +20467,7 @@
         <v>46083</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20540,7 +20540,7 @@
         <v>46087</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20613,7 +20613,7 @@
         <v>46093</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20686,7 +20686,7 @@
         <v>44895</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20759,7 +20759,7 @@
         <v>46101</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20832,7 +20832,7 @@
         <v>45842</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20905,7 +20905,7 @@
         <v>46100</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20978,7 +20978,7 @@
         <v>45713</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21051,7 +21051,7 @@
         <v>45849</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21124,7 +21124,7 @@
         <v>44776</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21197,7 +21197,7 @@
         <v>46113</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21270,7 +21270,7 @@
         <v>45475</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21343,7 +21343,7 @@
         <v>46113</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21416,7 +21416,7 @@
         <v>45246</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21489,7 +21489,7 @@
         <v>45734</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21562,7 +21562,7 @@
         <v>46260</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21635,7 +21635,7 @@
         <v>46304</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21713,7 +21713,7 @@
         <v>46126</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21786,7 +21786,7 @@
         <v>46126</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21859,7 +21859,7 @@
         <v>44601</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21932,7 +21932,7 @@
         <v>46265</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22010,7 +22010,7 @@
         <v>46265</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22088,7 +22088,7 @@
         <v>44875</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22161,7 +22161,7 @@
         <v>45882</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22239,7 +22239,7 @@
         <v>44902</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22312,7 +22312,7 @@
         <v>44901</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22385,7 +22385,7 @@
         <v>44909</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22458,7 +22458,7 @@
         <v>45597</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22531,7 +22531,7 @@
         <v>44648</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22604,7 +22604,7 @@
         <v>45825</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22677,7 +22677,7 @@
         <v>45202</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22750,7 +22750,7 @@
         <v>46309</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22828,7 +22828,7 @@
         <v>45632</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22901,7 +22901,7 @@
         <v>45698</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22974,7 +22974,7 @@
         <v>45915</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23047,7 +23047,7 @@
         <v>45603</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23120,7 +23120,7 @@
         <v>44952</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23193,7 +23193,7 @@
         <v>45832</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23271,7 +23271,7 @@
         <v>45929</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23344,7 +23344,7 @@
         <v>44720</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23417,7 +23417,7 @@
         <v>44600</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23495,7 +23495,7 @@
         <v>46314</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23568,7 +23568,7 @@
         <v>45896</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23641,7 +23641,7 @@
         <v>45825</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23714,7 +23714,7 @@
         <v>45118</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23787,7 +23787,7 @@
         <v>45994</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23860,7 +23860,7 @@
         <v>45966</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23933,7 +23933,7 @@
         <v>46272</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24006,7 +24006,7 @@
         <v>45443</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24084,7 +24084,7 @@
         <v>45904</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24162,7 +24162,7 @@
         <v>45845</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24235,7 +24235,7 @@
         <v>45734</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24308,7 +24308,7 @@
         <v>45834</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24381,7 +24381,7 @@
         <v>45825</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24454,7 +24454,7 @@
         <v>45602</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24527,7 +24527,7 @@
         <v>45358</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24605,7 +24605,7 @@
         <v>45047</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24678,7 +24678,7 @@
         <v>46080</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24756,7 +24756,7 @@
         <v>45541</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24829,7 +24829,7 @@
         <v>45632</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24902,7 +24902,7 @@
         <v>44705</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24975,7 +24975,7 @@
         <v>44511</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25048,7 +25048,7 @@
         <v>46276</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25121,7 +25121,7 @@
         <v>45150</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25194,7 +25194,7 @@
         <v>45595</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25267,7 +25267,7 @@
         <v>45911</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25340,7 +25340,7 @@
         <v>45644</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25413,7 +25413,7 @@
         <v>46274</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25491,7 +25491,7 @@
         <v>46148</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25564,7 +25564,7 @@
         <v>45588</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25637,7 +25637,7 @@
         <v>46153</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25710,7 +25710,7 @@
         <v>45189</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25783,7 +25783,7 @@
         <v>46153</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25856,7 +25856,7 @@
         <v>46153</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25929,7 +25929,7 @@
         <v>45624</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26002,7 +26002,7 @@
         <v>45762</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26075,7 +26075,7 @@
         <v>46160</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26148,7 +26148,7 @@
         <v>45624</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26221,7 +26221,7 @@
         <v>45546</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26294,7 +26294,7 @@
         <v>45737</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26367,7 +26367,7 @@
         <v>45940</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26440,7 +26440,7 @@
         <v>45006</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26513,7 +26513,7 @@
         <v>45037</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26586,7 +26586,7 @@
         <v>44952</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26659,7 +26659,7 @@
         <v>44958</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26732,7 +26732,7 @@
         <v>44952</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26805,7 +26805,7 @@
         <v>45761</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26878,7 +26878,7 @@
         <v>45161</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26956,7 +26956,7 @@
         <v>45162</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27029,7 +27029,7 @@
         <v>45590</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27102,7 +27102,7 @@
         <v>45615</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27175,7 +27175,7 @@
         <v>45002</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27248,7 +27248,7 @@
         <v>45621</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27321,7 +27321,7 @@
         <v>45590</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27394,7 +27394,7 @@
         <v>45062</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27467,7 +27467,7 @@
         <v>45693</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27540,7 +27540,7 @@
         <v>45189</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27613,7 +27613,7 @@
         <v>45181</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27686,7 +27686,7 @@
         <v>45150</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27759,7 +27759,7 @@
         <v>45530</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27832,7 +27832,7 @@
         <v>45217</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27910,7 +27910,7 @@
         <v>45197</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27983,7 +27983,7 @@
         <v>45547</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28056,7 +28056,7 @@
         <v>45348</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28129,7 +28129,7 @@
         <v>45418</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28202,7 +28202,7 @@
         <v>45425</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28275,7 +28275,7 @@
         <v>45467</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28348,7 +28348,7 @@
         <v>45272</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28421,7 +28421,7 @@
         <v>44858</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28494,7 +28494,7 @@
         <v>45092</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28567,7 +28567,7 @@
         <v>45273</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28640,7 +28640,7 @@
         <v>45015</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28713,7 +28713,7 @@
         <v>44959</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28786,7 +28786,7 @@
         <v>44902</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28859,7 +28859,7 @@
         <v>44959</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28932,7 +28932,7 @@
         <v>45103</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29005,7 +29005,7 @@
         <v>45121</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29078,7 +29078,7 @@
         <v>44545</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29151,7 +29151,7 @@
         <v>45075</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29224,7 +29224,7 @@
         <v>45355</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29297,7 +29297,7 @@
         <v>44949</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29370,7 +29370,7 @@
         <v>45254</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29443,7 +29443,7 @@
         <v>44621</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29521,7 +29521,7 @@
         <v>44781</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29594,7 +29594,7 @@
         <v>45348</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29667,7 +29667,7 @@
         <v>45384</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29740,7 +29740,7 @@
         <v>45404</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29813,7 +29813,7 @@
         <v>45104</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29886,7 +29886,7 @@
         <v>45566</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29959,7 +29959,7 @@
         <v>44621</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30037,7 +30037,7 @@
         <v>45162</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30110,7 +30110,7 @@
         <v>45621</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30183,7 +30183,7 @@
         <v>45587</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30256,7 +30256,7 @@
         <v>45616</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30329,7 +30329,7 @@
         <v>45636</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30402,7 +30402,7 @@
         <v>45639</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30475,7 +30475,7 @@
         <v>45639</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30548,7 +30548,7 @@
         <v>45162</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30621,7 +30621,7 @@
         <v>45078</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30694,7 +30694,7 @@
         <v>44743</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30767,7 +30767,7 @@
         <v>45182</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30840,7 +30840,7 @@
         <v>45674</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30913,7 +30913,7 @@
         <v>44601</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30986,7 +30986,7 @@
         <v>45763</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31059,7 +31059,7 @@
         <v>44643</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31132,7 +31132,7 @@
         <v>45196</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31210,7 +31210,7 @@
         <v>45609</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31283,7 +31283,7 @@
         <v>44858</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31356,7 +31356,7 @@
         <v>44701</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31429,7 +31429,7 @@
         <v>45162</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31502,7 +31502,7 @@
         <v>45755</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31575,7 +31575,7 @@
         <v>45686</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31648,7 +31648,7 @@
         <v>44743</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31721,7 +31721,7 @@
         <v>45773</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31794,7 +31794,7 @@
         <v>44614</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31867,7 +31867,7 @@
         <v>44659</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31940,7 +31940,7 @@
         <v>44823</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32013,7 +32013,7 @@
         <v>45705</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32086,7 +32086,7 @@
         <v>45201</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32159,7 +32159,7 @@
         <v>44823</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32232,7 +32232,7 @@
         <v>45272</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32305,7 +32305,7 @@
         <v>44742</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32378,7 +32378,7 @@
         <v>45763</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32451,7 +32451,7 @@
         <v>45763</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32524,7 +32524,7 @@
         <v>44952</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32597,7 +32597,7 @@
         <v>44952</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32670,7 +32670,7 @@
         <v>44952</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32743,7 +32743,7 @@
         <v>45326</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32816,7 +32816,7 @@
         <v>45609</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32889,7 +32889,7 @@
         <v>44504</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32962,7 +32962,7 @@
         <v>45538</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33035,7 +33035,7 @@
         <v>45446</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33108,7 +33108,7 @@
         <v>45533</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33181,7 +33181,7 @@
         <v>44966</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33254,7 +33254,7 @@
         <v>44627</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33327,7 +33327,7 @@
         <v>44952</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33400,7 +33400,7 @@
         <v>45561</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33473,7 +33473,7 @@
         <v>45443</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33551,7 +33551,7 @@
         <v>44613</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33629,7 +33629,7 @@
         <v>44812</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33707,7 +33707,7 @@
         <v>45670</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33780,7 +33780,7 @@
         <v>45483</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33853,7 +33853,7 @@
         <v>45717</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
